--- a/places.xlsx
+++ b/places.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hiro7\OneDrive\ドキュメント\アプリ開発\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF94E87-3327-48C9-AFEA-5A8264722427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{668A0EC2-823C-49EB-B462-29C360A1F2C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{5856E073-2BFD-4948-BC37-89DDE9F9B438}"/>
+    <workbookView xWindow="7920" yWindow="0" windowWidth="9600" windowHeight="10080" xr2:uid="{5856E073-2BFD-4948-BC37-89DDE9F9B438}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="3" r:id="rId1"/>
@@ -1437,9 +1437,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>行政TOP | 北見市</t>
-  </si>
-  <si>
     <t>道の駅みそぎの郷 きこない 観光案内所北海道上磯郡木古内町字本町338-14電話：01392-2-3161</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1461,6 +1458,10 @@
   </si>
   <si>
     <t>hokkaidou02</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.city.kitami.lg.jp/tourism/</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1989,7 +1990,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B3" t="s">
         <v>335</v>
@@ -2007,12 +2008,12 @@
         <v>340</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B4" t="s">
         <v>337</v>
@@ -2030,7 +2031,7 @@
         <v>339</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2038,10 +2039,10 @@
         <v>282</v>
       </c>
       <c r="B5" t="s">
+        <v>342</v>
+      </c>
+      <c r="C5" t="s">
         <v>343</v>
-      </c>
-      <c r="C5" t="s">
-        <v>344</v>
       </c>
       <c r="D5">
         <v>41.677958180979203</v>
@@ -2050,10 +2051,10 @@
         <v>140.43544688747201</v>
       </c>
       <c r="F5" t="s">
+        <v>344</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>345</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -2290,8 +2291,8 @@
   <phoneticPr fontId="1"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" xr:uid="{C161CA4A-6D1B-46DD-A6D8-36F98963FBBD}"/>
-    <hyperlink ref="G3" r:id="rId2" display="https://www.city.kitami.lg.jp/administration/" xr:uid="{545F60CA-AAA9-42B5-8799-42DD3AE1A4C2}"/>
-    <hyperlink ref="G4" r:id="rId3" display="https://www.city.kitami.lg.jp/administration/" xr:uid="{5EC890F3-60CB-432F-8F74-7179DAE1E6B8}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{545F60CA-AAA9-42B5-8799-42DD3AE1A4C2}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{5EC890F3-60CB-432F-8F74-7179DAE1E6B8}"/>
     <hyperlink ref="G5" r:id="rId4" xr:uid="{2B5D0AB2-28D9-4857-9575-7FF46B719C3B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3208,10 +3209,10 @@
         <v>42583</v>
       </c>
       <c r="E45" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F45" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G45" t="s">
         <v>160</v>

--- a/places.xlsx
+++ b/places.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hiro7\OneDrive\ドキュメント\アプリ開発\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{668A0EC2-823C-49EB-B462-29C360A1F2C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B34190F-581C-4757-AABD-45BC8A1F11BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7920" yWindow="0" windowWidth="9600" windowHeight="10080" xr2:uid="{5856E073-2BFD-4948-BC37-89DDE9F9B438}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{5856E073-2BFD-4948-BC37-89DDE9F9B438}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="3" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="353">
   <si>
     <t>Column1</t>
   </si>
@@ -1462,6 +1462,35 @@
   </si>
   <si>
     <t>https://www.city.kitami.lg.jp/tourism/</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>tag</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>平日は休み</t>
+    <rPh sb="0" eb="2">
+      <t>ヘイジツ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヤス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>年末年始（12/29～1/3）は休み</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>月曜日（祝休日の場合は翌日）、年末年始は休み</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>年末年始は休み</t>
+    <rPh sb="0" eb="1">
+      <t>ネン</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1931,7 +1960,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B56AA262-D896-43C4-AEBC-2C76EB52FEA4}">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="14.08203125" bestFit="1" customWidth="1"/>
@@ -1940,9 +1969,10 @@
     <col min="4" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.25" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="34.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="45.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>275</v>
       </c>
@@ -1964,8 +1994,11 @@
       <c r="G1" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="H1" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>281</v>
       </c>
@@ -1987,8 +2020,11 @@
       <c r="G2" s="3" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>346</v>
       </c>
@@ -2010,8 +2046,11 @@
       <c r="G3" s="3" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H3" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>346</v>
       </c>
@@ -2033,8 +2072,11 @@
       <c r="G4" s="3" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H4" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>282</v>
       </c>
@@ -2056,58 +2098,61 @@
       <c r="G5" s="3" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H5" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>293</v>
       </c>

--- a/places.xlsx
+++ b/places.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hiro7\OneDrive\ドキュメント\アプリ開発\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B34190F-581C-4757-AABD-45BC8A1F11BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E05642D-0FC3-4EB2-AED3-6720AC2DB66A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{5856E073-2BFD-4948-BC37-89DDE9F9B438}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{5856E073-2BFD-4948-BC37-89DDE9F9B438}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="3" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="352">
   <si>
     <t>Column1</t>
   </si>
@@ -1465,32 +1465,19 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>tag</t>
+    <t>schedule_type</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>平日は休み</t>
-    <rPh sb="0" eb="2">
-      <t>ヘイジツ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ヤス</t>
-    </rPh>
+    <t>WEEKEND</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>年末年始（12/29～1/3）は休み</t>
+    <t>OFF_YEAR_END</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>月曜日（祝休日の場合は翌日）、年末年始は休み</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>年末年始は休み</t>
-    <rPh sb="0" eb="1">
-      <t>ネン</t>
-    </rPh>
+    <t>OFF_MON,OFF_YEAR_END</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1969,7 +1956,8 @@
     <col min="4" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.25" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="34.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="45.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.4140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -2099,7 +2087,7 @@
         <v>345</v>
       </c>
       <c r="H5" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">

--- a/places.xlsx
+++ b/places.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E05642D-0FC3-4EB2-AED3-6720AC2DB66A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{5856E073-2BFD-4948-BC37-89DDE9F9B438}"/>
+    <workbookView xWindow="3500" yWindow="0" windowWidth="9600" windowHeight="10080" xr2:uid="{5856E073-2BFD-4948-BC37-89DDE9F9B438}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="3" r:id="rId1"/>

--- a/places.xlsx
+++ b/places.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hiro7\OneDrive\ドキュメント\アプリ開発\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E05642D-0FC3-4EB2-AED3-6720AC2DB66A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E702CA89-4571-4670-ABAD-F7320C3EE225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3500" yWindow="0" windowWidth="9600" windowHeight="10080" xr2:uid="{5856E073-2BFD-4948-BC37-89DDE9F9B438}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{5856E073-2BFD-4948-BC37-89DDE9F9B438}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="3" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="363">
   <si>
     <t>Column1</t>
   </si>
@@ -135,12 +135,6 @@
     <t>第03弾</t>
   </si>
   <si>
-    <t>函館市地域交流まちづくりセンター北海道函館市末広町4-19電話：0138-22-9700</t>
-  </si>
-  <si>
-    <t>9:00～21:00ただし、年末年始（12/31～1/3）はお休みですまた、器材点検のために月1回程度休館する場合があります</t>
-  </si>
-  <si>
     <t>小樽市</t>
   </si>
   <si>
@@ -423,9 +417,6 @@
   </si>
   <si>
     <t>紋別市</t>
-  </si>
-  <si>
-    <t>(平日)紋別市役所 水道部事業課 下水道施設係(休日）紋別市役所 当直室北海道紋別市幸町2-1-18電話：0158-24-2111</t>
   </si>
   <si>
     <t>8:45～17:30</t>
@@ -1478,6 +1469,61 @@
   </si>
   <si>
     <t>OFF_MON,OFF_YEAR_END</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>函館市地域交流まちづくりセンター北海道函館市末広町4-19電話：0138-22-9700</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>函館市地域交流まちづくりセンター</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>北海道函館市末広町4-19</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9:00～21:00ただし、年末年始（12/31～1/3）はお休みですまた、器材点検のために月1回程度休館する場合があります</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.city.hakodate.hokkaido.jp/docs/2016111100025/</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OFF_YEAR_END</t>
+  </si>
+  <si>
+    <t>(平日)紋別市役所 水道部事業課 下水道施設係(休日）紋別市役所 当直室北海道紋別市幸町2-1-18電話：0158-24-2111</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>hokkaidou05</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>北海道紋別市幸町2-1-18</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://mombetsu.jp/life/?content=3243</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(休日)紋別市役所《1階正面玄関》当直室前</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(平日)紋別市役所 《4階》水道部窓口</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8:45～17:30</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>WEEKDAY,OFF_YEAR_END</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1613,7 +1659,7 @@
   <autoFilter ref="A1:G80" xr:uid="{B1447BD3-2B45-4A4E-9F9F-A0081B3D29EC}">
     <filterColumn colId="2">
       <filters>
-        <filter val="第02弾"/>
+        <filter val="第03弾"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -1947,7 +1993,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B56AA262-D896-43C4-AEBC-2C76EB52FEA4}">
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="14.08203125" bestFit="1" customWidth="1"/>
@@ -1962,39 +2008,39 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1" t="s">
         <v>275</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
         <v>276</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>277</v>
       </c>
-      <c r="D1" t="s">
-        <v>278</v>
-      </c>
-      <c r="E1" t="s">
-        <v>279</v>
-      </c>
-      <c r="F1" t="s">
-        <v>280</v>
-      </c>
       <c r="G1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="H1" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D2">
         <v>43.117144155854902</v>
@@ -2003,24 +2049,24 @@
         <v>141.34263055353799</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="H2" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B3" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C3" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D3">
         <v>43.798536932553198</v>
@@ -2029,24 +2075,24 @@
         <v>143.89305151589099</v>
       </c>
       <c r="F3" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="H3" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B4" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C4" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D4">
         <v>43.798262677862503</v>
@@ -2055,24 +2101,24 @@
         <v>143.89294268750399</v>
       </c>
       <c r="F4" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="H4" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B5" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C5" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D5">
         <v>41.677958180979203</v>
@@ -2081,243 +2127,311 @@
         <v>140.43544688747201</v>
       </c>
       <c r="F5" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="H5" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>283</v>
+        <v>280</v>
+      </c>
+      <c r="B6" t="s">
+        <v>350</v>
+      </c>
+      <c r="C6" t="s">
+        <v>351</v>
+      </c>
+      <c r="D6">
+        <v>41.763908942913503</v>
+      </c>
+      <c r="E6">
+        <v>140.71703287116301</v>
+      </c>
+      <c r="F6" t="s">
+        <v>352</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="H6" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>284</v>
+        <v>356</v>
+      </c>
+      <c r="B7" t="s">
+        <v>360</v>
+      </c>
+      <c r="C7" t="s">
+        <v>357</v>
+      </c>
+      <c r="D7">
+        <v>44.356501773905201</v>
+      </c>
+      <c r="E7">
+        <v>143.35443317674901</v>
+      </c>
+      <c r="F7" t="s">
+        <v>361</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="H7" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>285</v>
+        <v>281</v>
+      </c>
+      <c r="B8" t="s">
+        <v>359</v>
+      </c>
+      <c r="C8" t="s">
+        <v>357</v>
+      </c>
+      <c r="D8">
+        <v>44.355980132921999</v>
+      </c>
+      <c r="E8">
+        <v>143.35417568467199</v>
+      </c>
+      <c r="F8" t="s">
+        <v>361</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="H8" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
-        <v>328</v>
+        <v>324</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" t="s">
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -2327,6 +2441,9 @@
     <hyperlink ref="G3" r:id="rId2" xr:uid="{545F60CA-AAA9-42B5-8799-42DD3AE1A4C2}"/>
     <hyperlink ref="G4" r:id="rId3" xr:uid="{5EC890F3-60CB-432F-8F74-7179DAE1E6B8}"/>
     <hyperlink ref="G5" r:id="rId4" xr:uid="{2B5D0AB2-28D9-4857-9575-7FF46B719C3B}"/>
+    <hyperlink ref="G6" r:id="rId5" xr:uid="{EAF605B9-D2BE-429C-ABEA-9EFC6329FEA5}"/>
+    <hyperlink ref="G7" r:id="rId6" xr:uid="{37041FD6-7F9F-48C8-93DD-CE1D2E8488E2}"/>
+    <hyperlink ref="G8" r:id="rId7" xr:uid="{B149A64B-0135-4626-846D-F6A181960569}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2382,10 +2499,10 @@
         <v>42461</v>
       </c>
       <c r="E2" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F2" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="G2" t="s">
         <v>11</v>
@@ -2431,7 +2548,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" t="s">
         <v>20</v>
       </c>
@@ -2442,10 +2559,10 @@
         <v>42705</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>349</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>352</v>
       </c>
       <c r="G5" t="s">
         <v>11</v>
@@ -2453,19 +2570,19 @@
     </row>
     <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D6" s="1">
         <v>43078</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G6" t="s">
         <v>11</v>
@@ -2473,19 +2590,19 @@
     </row>
     <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D7" s="1">
         <v>42828</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G7" t="s">
         <v>11</v>
@@ -2493,19 +2610,19 @@
     </row>
     <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D8" s="1">
         <v>45499</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G8" t="s">
         <v>11</v>
@@ -2513,19 +2630,19 @@
     </row>
     <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D9" s="1">
         <v>43323</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G9" t="s">
         <v>11</v>
@@ -2533,19 +2650,19 @@
     </row>
     <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D10" s="1">
         <v>43218</v>
       </c>
       <c r="E10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G10" t="s">
         <v>11</v>
@@ -2553,19 +2670,19 @@
     </row>
     <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D11" s="1">
         <v>43813</v>
       </c>
       <c r="E11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G11" t="s">
         <v>11</v>
@@ -2573,19 +2690,19 @@
     </row>
     <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D12" s="1">
         <v>45408</v>
       </c>
       <c r="E12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G12" t="s">
         <v>11</v>
@@ -2593,39 +2710,39 @@
     </row>
     <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D13" s="1">
         <v>43813</v>
       </c>
       <c r="E13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" t="s">
         <v>52</v>
       </c>
-      <c r="F13" t="s">
+    </row>
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" t="s">
         <v>53</v>
       </c>
-      <c r="G13" t="s">
+      <c r="C14" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" t="s">
-        <v>55</v>
-      </c>
-      <c r="C14" t="s">
-        <v>56</v>
       </c>
       <c r="D14" s="1">
         <v>42583</v>
       </c>
       <c r="E14" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="F14" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="G14" t="s">
         <v>11</v>
@@ -2633,19 +2750,19 @@
     </row>
     <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D15" s="1">
         <v>43684</v>
       </c>
       <c r="E15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F15" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G15" t="s">
         <v>11</v>
@@ -2653,19 +2770,19 @@
     </row>
     <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D16" s="1">
         <v>44182</v>
       </c>
       <c r="E16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G16" t="s">
         <v>11</v>
@@ -2673,19 +2790,19 @@
     </row>
     <row r="17" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D17" s="1">
         <v>42828</v>
       </c>
       <c r="E17" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F17" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G17" t="s">
         <v>11</v>
@@ -2693,19 +2810,19 @@
     </row>
     <row r="18" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D18" s="1">
         <v>42828</v>
       </c>
       <c r="E18" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F18" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G18" t="s">
         <v>11</v>
@@ -2713,19 +2830,19 @@
     </row>
     <row r="19" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C19" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D19" s="1">
         <v>44779</v>
       </c>
       <c r="E19" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F19" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G19" t="s">
         <v>11</v>
@@ -2733,19 +2850,19 @@
     </row>
     <row r="20" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B20" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C20" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D20" s="1">
         <v>46234</v>
       </c>
       <c r="E20" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F20" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G20" t="s">
         <v>11</v>
@@ -2753,19 +2870,19 @@
     </row>
     <row r="21" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C21" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D21" s="1">
         <v>42948</v>
       </c>
       <c r="E21" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F21" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G21" t="s">
         <v>11</v>
@@ -2773,39 +2890,39 @@
     </row>
     <row r="22" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C22" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D22" s="1">
         <v>42948</v>
       </c>
       <c r="E22" t="s">
+        <v>82</v>
+      </c>
+      <c r="F22" t="s">
+        <v>83</v>
+      </c>
+      <c r="G22" t="s">
         <v>84</v>
-      </c>
-      <c r="F22" t="s">
-        <v>85</v>
-      </c>
-      <c r="G22" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="23" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D23" s="1">
         <v>46136</v>
       </c>
       <c r="E23" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F23" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G23" t="s">
         <v>11</v>
@@ -2813,27 +2930,27 @@
     </row>
     <row r="24" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B24" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D24" s="1">
         <v>43684</v>
       </c>
       <c r="E24" t="s">
+        <v>90</v>
+      </c>
+      <c r="F24" t="s">
+        <v>91</v>
+      </c>
+      <c r="G24" t="s">
         <v>92</v>
       </c>
-      <c r="F24" t="s">
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B25" t="s">
         <v>93</v>
-      </c>
-      <c r="G24" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B25" t="s">
-        <v>95</v>
       </c>
       <c r="C25" t="s">
         <v>21</v>
@@ -2842,10 +2959,10 @@
         <v>42705</v>
       </c>
       <c r="E25" t="s">
-        <v>96</v>
+        <v>355</v>
       </c>
       <c r="F25" t="s">
-        <v>97</v>
+        <v>361</v>
       </c>
       <c r="G25" t="s">
         <v>11</v>
@@ -2853,19 +2970,19 @@
     </row>
     <row r="26" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B26" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C26" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D26" s="1">
         <v>45499</v>
       </c>
       <c r="E26" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F26" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G26" t="s">
         <v>11</v>
@@ -2873,19 +2990,19 @@
     </row>
     <row r="27" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B27" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C27" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D27" s="1">
         <v>43684</v>
       </c>
       <c r="E27" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F27" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G27" t="s">
         <v>11</v>
@@ -2893,19 +3010,19 @@
     </row>
     <row r="28" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C28" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D28" s="1">
         <v>43946</v>
       </c>
       <c r="E28" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F28" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G28" t="s">
         <v>11</v>
@@ -2913,19 +3030,19 @@
     </row>
     <row r="29" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C29" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D29" s="1">
         <v>44954</v>
       </c>
       <c r="E29" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F29" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G29" t="s">
         <v>11</v>
@@ -2933,19 +3050,19 @@
     </row>
     <row r="30" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B30" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C30" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D30" s="1">
         <v>43813</v>
       </c>
       <c r="E30" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F30" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G30" t="s">
         <v>11</v>
@@ -2953,19 +3070,19 @@
     </row>
     <row r="31" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B31" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C31" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D31" s="1">
         <v>43323</v>
       </c>
       <c r="E31" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F31" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="G31" t="s">
         <v>11</v>
@@ -2973,19 +3090,19 @@
     </row>
     <row r="32" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B32" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C32" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D32" s="1">
         <v>44576</v>
       </c>
       <c r="E32" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F32" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G32" t="s">
         <v>11</v>
@@ -2993,19 +3110,19 @@
     </row>
     <row r="33" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B33" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C33" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D33" s="1">
         <v>43813</v>
       </c>
       <c r="E33" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F33" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G33" t="s">
         <v>11</v>
@@ -3013,19 +3130,19 @@
     </row>
     <row r="34" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B34" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C34" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D34" s="1">
         <v>46234</v>
       </c>
       <c r="E34" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F34" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G34" t="s">
         <v>11</v>
@@ -3033,19 +3150,19 @@
     </row>
     <row r="35" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B35" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C35" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D35" s="1">
         <v>43323</v>
       </c>
       <c r="E35" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F35" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="G35" t="s">
         <v>11</v>
@@ -3053,19 +3170,19 @@
     </row>
     <row r="36" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B36" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C36" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D36" s="1">
         <v>42948</v>
       </c>
       <c r="E36" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F36" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G36" t="s">
         <v>11</v>
@@ -3073,10 +3190,10 @@
     </row>
     <row r="37" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B37" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C37" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D37" s="1">
         <v>44182</v>
@@ -3088,24 +3205,24 @@
         <v>9</v>
       </c>
       <c r="G37" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="38" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B38" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C38" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D38" s="1">
         <v>45275</v>
       </c>
       <c r="E38" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F38" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G38" t="s">
         <v>11</v>
@@ -3113,19 +3230,19 @@
     </row>
     <row r="39" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B39" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C39" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D39" s="1">
         <v>43078</v>
       </c>
       <c r="E39" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F39" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G39" t="s">
         <v>11</v>
@@ -3133,19 +3250,19 @@
     </row>
     <row r="40" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B40" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C40" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D40" s="1">
         <v>45275</v>
       </c>
       <c r="E40" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F40" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G40" t="s">
         <v>11</v>
@@ -3153,19 +3270,19 @@
     </row>
     <row r="41" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B41" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C41" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D41" s="1">
         <v>43078</v>
       </c>
       <c r="E41" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F41" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G41" t="s">
         <v>11</v>
@@ -3173,19 +3290,19 @@
     </row>
     <row r="42" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B42" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C42" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D42" s="1">
         <v>45772</v>
       </c>
       <c r="E42" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F42" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G42" t="s">
         <v>11</v>
@@ -3193,19 +3310,19 @@
     </row>
     <row r="43" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B43" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C43" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D43" s="1">
         <v>43323</v>
       </c>
       <c r="E43" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F43" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G43" t="s">
         <v>11</v>
@@ -3213,59 +3330,59 @@
     </row>
     <row r="44" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B44" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C44" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D44" s="1">
         <v>43684</v>
       </c>
       <c r="E44" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F44" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G44" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C45" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D45" s="1">
         <v>42583</v>
       </c>
       <c r="E45" t="s">
+        <v>338</v>
+      </c>
+      <c r="F45" t="s">
         <v>341</v>
       </c>
-      <c r="F45" t="s">
-        <v>344</v>
-      </c>
       <c r="G45" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="46" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B46" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C46" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D46" s="1">
         <v>44182</v>
       </c>
       <c r="E46" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F46" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G46" t="s">
         <v>11</v>
@@ -3273,19 +3390,19 @@
     </row>
     <row r="47" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B47" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C47" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D47" s="1">
         <v>43078</v>
       </c>
       <c r="E47" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F47" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G47" t="s">
         <v>11</v>
@@ -3293,39 +3410,39 @@
     </row>
     <row r="48" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B48" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C48" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D48" s="1">
         <v>43684</v>
       </c>
       <c r="E48" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F48" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G48" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="49" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B49" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C49" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D49" s="1">
         <v>43078</v>
       </c>
       <c r="E49" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F49" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G49" t="s">
         <v>11</v>
@@ -3333,39 +3450,39 @@
     </row>
     <row r="50" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B50" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C50" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D50" s="1">
         <v>43813</v>
       </c>
       <c r="E50" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F50" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G50" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="51" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B51" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C51" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D51" s="1">
         <v>44954</v>
       </c>
       <c r="E51" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F51" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G51" t="s">
         <v>11</v>
@@ -3373,19 +3490,19 @@
     </row>
     <row r="52" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B52" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C52" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D52" s="1">
         <v>44425</v>
       </c>
       <c r="E52" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F52" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G52" t="s">
         <v>11</v>
@@ -3393,19 +3510,19 @@
     </row>
     <row r="53" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B53" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C53" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D53" s="1">
         <v>43946</v>
       </c>
       <c r="E53" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F53" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G53" t="s">
         <v>11</v>
@@ -3413,47 +3530,47 @@
     </row>
     <row r="54" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B54" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C54" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D54" s="1">
         <v>42948</v>
       </c>
       <c r="E54" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F54" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G54" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="55" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B55" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C55" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D55" s="1">
         <v>42948</v>
       </c>
       <c r="E55" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F55" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G55" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="56" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B56" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C56" t="s">
         <v>13</v>
@@ -3462,10 +3579,10 @@
         <v>43448</v>
       </c>
       <c r="E56" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F56" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G56" t="s">
         <v>11</v>
@@ -3473,19 +3590,19 @@
     </row>
     <row r="57" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B57" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C57" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D57" s="1">
         <v>44779</v>
       </c>
       <c r="E57" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F57" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="G57" t="s">
         <v>11</v>
@@ -3493,19 +3610,19 @@
     </row>
     <row r="58" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B58" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C58" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D58" s="1">
         <v>45408</v>
       </c>
       <c r="E58" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F58" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G58" t="s">
         <v>11</v>
@@ -3513,19 +3630,19 @@
     </row>
     <row r="59" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B59" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C59" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D59" s="1">
         <v>43323</v>
       </c>
       <c r="E59" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F59" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="G59" t="s">
         <v>11</v>
@@ -3533,19 +3650,19 @@
     </row>
     <row r="60" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B60" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C60" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D60" s="1">
         <v>43946</v>
       </c>
       <c r="E60" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F60" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G60" t="s">
         <v>11</v>
@@ -3553,19 +3670,19 @@
     </row>
     <row r="61" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B61" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C61" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D61" s="1">
         <v>44311</v>
       </c>
       <c r="E61" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F61" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="G61" t="s">
         <v>11</v>
@@ -3573,19 +3690,19 @@
     </row>
     <row r="62" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B62" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C62" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D62" s="1">
         <v>44779</v>
       </c>
       <c r="E62" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F62" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="G62" t="s">
         <v>11</v>
@@ -3593,19 +3710,19 @@
     </row>
     <row r="63" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B63" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C63" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D63" s="1">
         <v>43946</v>
       </c>
       <c r="E63" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F63" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="G63" t="s">
         <v>11</v>
@@ -3613,59 +3730,59 @@
     </row>
     <row r="64" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B64" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C64" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D64" s="1">
         <v>46136</v>
       </c>
       <c r="E64" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F64" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="G64" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="65" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B65" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C65" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D65" s="1">
         <v>44779</v>
       </c>
       <c r="E65" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F65" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="G65" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="66" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B66" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C66" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D66" s="1">
         <v>45499</v>
       </c>
       <c r="E66" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F66" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G66" t="s">
         <v>11</v>
@@ -3673,19 +3790,19 @@
     </row>
     <row r="67" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B67" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C67" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D67" s="1">
         <v>45408</v>
       </c>
       <c r="E67" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F67" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="G67" t="s">
         <v>11</v>
@@ -3693,19 +3810,19 @@
     </row>
     <row r="68" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B68" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C68" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D68" s="1">
         <v>44954</v>
       </c>
       <c r="E68" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F68" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G68" t="s">
         <v>11</v>
@@ -3713,19 +3830,19 @@
     </row>
     <row r="69" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B69" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C69" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D69" s="1">
         <v>44311</v>
       </c>
       <c r="E69" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F69" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G69" t="s">
         <v>11</v>
@@ -3733,19 +3850,19 @@
     </row>
     <row r="70" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B70" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C70" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D70" s="1">
         <v>43684</v>
       </c>
       <c r="E70" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F70" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="G70" t="s">
         <v>11</v>
@@ -3753,19 +3870,19 @@
     </row>
     <row r="71" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B71" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C71" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D71" s="1">
         <v>43813</v>
       </c>
       <c r="E71" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F71" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G71" t="s">
         <v>11</v>
@@ -3773,19 +3890,19 @@
     </row>
     <row r="72" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B72" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C72" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D72" s="1">
         <v>46010</v>
       </c>
       <c r="E72" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F72" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="G72" t="s">
         <v>11</v>
@@ -3793,39 +3910,39 @@
     </row>
     <row r="73" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B73" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C73" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D73" s="1">
         <v>46234</v>
       </c>
       <c r="E73" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F73" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G73" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="74" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B74" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C74" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D74" s="1">
         <v>45772</v>
       </c>
       <c r="E74" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="F74" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="G74" t="s">
         <v>11</v>
@@ -3833,19 +3950,19 @@
     </row>
     <row r="75" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B75" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C75" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D75" s="1">
         <v>46136</v>
       </c>
       <c r="E75" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F75" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G75" t="s">
         <v>11</v>
@@ -3853,19 +3970,19 @@
     </row>
     <row r="76" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B76" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C76" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D76" s="1">
         <v>43684</v>
       </c>
       <c r="E76" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F76" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="G76" t="s">
         <v>11</v>
@@ -3873,19 +3990,19 @@
     </row>
     <row r="77" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B77" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C77" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D77" s="1">
         <v>44954</v>
       </c>
       <c r="E77" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F77" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="G77" t="s">
         <v>11</v>
@@ -3893,19 +4010,19 @@
     </row>
     <row r="78" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B78" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C78" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D78" s="1">
         <v>43218</v>
       </c>
       <c r="E78" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="F78" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="G78" t="s">
         <v>11</v>
@@ -3913,19 +4030,19 @@
     </row>
     <row r="79" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B79" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C79" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D79" s="1">
         <v>43813</v>
       </c>
       <c r="E79" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="F79" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G79" t="s">
         <v>11</v>
@@ -3933,19 +4050,19 @@
     </row>
     <row r="80" spans="2:7" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B80" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C80" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D80" s="1">
         <v>46234</v>
       </c>
       <c r="E80" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="F80" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="G80" t="s">
         <v>11</v>

--- a/places.xlsx
+++ b/places.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E702CA89-4571-4670-ABAD-F7320C3EE225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{5856E073-2BFD-4948-BC37-89DDE9F9B438}"/>
+    <workbookView xWindow="3500" yWindow="0" windowWidth="9600" windowHeight="10080" xr2:uid="{5856E073-2BFD-4948-BC37-89DDE9F9B438}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="3" r:id="rId1"/>

--- a/places.xlsx
+++ b/places.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hiro7\OneDrive\ドキュメント\アプリ開発\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B1147F6-8DA7-4037-B32C-D4AD8EB43496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{440D90E5-0A83-4610-8B76-46059CBF5519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{5856E073-2BFD-4948-BC37-89DDE9F9B438}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" firstSheet="1" activeTab="2" xr2:uid="{5856E073-2BFD-4948-BC37-89DDE9F9B438}"/>
   </bookViews>
   <sheets>
     <sheet name="北海道" sheetId="3" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="187">
   <si>
     <t>8:45～17:15</t>
   </si>
@@ -336,14 +336,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>(休日)紋別市役所《1階正面玄関》当直室前</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>(平日)紋別市役所 《4階》水道部窓口</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>8:45～17:30</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -380,6 +372,13 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>WEEKDAY,OFF_YEAR_END</t>
+  </si>
+  <si>
+    <t>WEEKEND,OFF_YEAR_END</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>WEEKEND,PERIOD_12/30-1/4</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -438,6 +437,266 @@
   </si>
   <si>
     <t>WEEKDAY</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OFF_YEAR_END,WEEKEND</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【平日】紋別市役所 《4階》水道部窓口</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【休日】紋別市役所《1階正面玄関》当直室前</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>chiba01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>chiba02</t>
+  </si>
+  <si>
+    <t>chiba03</t>
+  </si>
+  <si>
+    <t>chiba04</t>
+  </si>
+  <si>
+    <t>chiba05</t>
+  </si>
+  <si>
+    <t>chiba06</t>
+  </si>
+  <si>
+    <t>chiba07</t>
+  </si>
+  <si>
+    <t>chiba08</t>
+  </si>
+  <si>
+    <t>chiba09</t>
+  </si>
+  <si>
+    <t>chiba10</t>
+  </si>
+  <si>
+    <t>chiba11</t>
+  </si>
+  <si>
+    <t>chiba12</t>
+  </si>
+  <si>
+    <t>chiba13</t>
+  </si>
+  <si>
+    <t>chiba14</t>
+  </si>
+  <si>
+    <t>chiba15</t>
+  </si>
+  <si>
+    <t>chiba16</t>
+  </si>
+  <si>
+    <t>chiba17</t>
+  </si>
+  <si>
+    <t>chiba18</t>
+  </si>
+  <si>
+    <t>chiba19</t>
+  </si>
+  <si>
+    <t>chiba20</t>
+  </si>
+  <si>
+    <t>chiba21</t>
+  </si>
+  <si>
+    <t>chiba22</t>
+  </si>
+  <si>
+    <t>chiba23</t>
+  </si>
+  <si>
+    <t>chiba24</t>
+  </si>
+  <si>
+    <t>chiba25</t>
+  </si>
+  <si>
+    <t>chiba26</t>
+  </si>
+  <si>
+    <t>chiba27</t>
+  </si>
+  <si>
+    <t>chiba28</t>
+  </si>
+  <si>
+    <t>chiba29</t>
+  </si>
+  <si>
+    <t>chiba30</t>
+  </si>
+  <si>
+    <t>chiba31</t>
+  </si>
+  <si>
+    <t>chiba32</t>
+  </si>
+  <si>
+    <t>chiba33</t>
+  </si>
+  <si>
+    <t>chiba34</t>
+  </si>
+  <si>
+    <t>chiba35</t>
+  </si>
+  <si>
+    <t>chiba36</t>
+  </si>
+  <si>
+    <t>chiba37</t>
+  </si>
+  <si>
+    <t>chiba38</t>
+  </si>
+  <si>
+    <t>chiba39</t>
+  </si>
+  <si>
+    <t>chiba40</t>
+  </si>
+  <si>
+    <t>chiba41</t>
+  </si>
+  <si>
+    <t>chiba42</t>
+  </si>
+  <si>
+    <t>chiba43</t>
+  </si>
+  <si>
+    <t>chiba44</t>
+  </si>
+  <si>
+    <t>chiba45</t>
+  </si>
+  <si>
+    <t>chiba46</t>
+  </si>
+  <si>
+    <t>chiba47</t>
+  </si>
+  <si>
+    <t>chiba48</t>
+  </si>
+  <si>
+    <t>chiba49</t>
+  </si>
+  <si>
+    <t>千葉県船橋市若松2−2−1 ららテラスTOKYO-BAY 2階</t>
+  </si>
+  <si>
+    <t>千葉県船橋市湊町2-10-25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【平日】船橋市建設局 下水道部下水道河川計画課（本庁舎5階)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【土日祝日】船橋市観光協会</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10:00～18:00 ただし、年末年始はお休みです</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.city.funabashi.lg.jp/machi/gesui/003/p046506.html</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【平日】柏市上下水道局３階総務課</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>chiba02</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【土日祝】柏市観光案内所 まるっと柏</t>
+  </si>
+  <si>
+    <t>千葉県柏市千代田一丁目２番３２号</t>
+    <rPh sb="0" eb="3">
+      <t>チバケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>千葉県柏市柏1-1-11ファミリかしわ3階</t>
+    <rPh sb="0" eb="3">
+      <t>チバケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9:00～17:00　ただし、年末年始(12/29～1/3)はお休みです</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10:00～18:00　ただし、年末年始(12/27～1/4)はお休みです</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>WEEKEND,PERIOD_12/27-1/4,PAUSED</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>WEEKDAY,OFF_YEAR_END,PAUSED</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.city.kashiwa.lg.jp/somu/living_environment/gesui/1561/manholecard.html</t>
+  </si>
+  <si>
+    <t>https://www.city.kashiwa.lg.jp/somu/living_environment/gesui/1561/manholecard.html</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【平日】鎌ケ谷市役所 都市建設部 下水道課</t>
+  </si>
+  <si>
+    <t>chiba03</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>千葉県鎌ケ谷市新鎌ケ谷2-6-1（鎌ケ谷市役所4階）</t>
+  </si>
+  <si>
+    <t>千葉県鎌ケ谷市中央1-8-31</t>
+  </si>
+  <si>
+    <t>【土日】鎌ケ谷市郷土資料館</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9:00～17:00（最終入館16:45）ただし、祝日、年末年始はお休みです</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8:30～17:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.city.kamagaya.chiba.jp/smph/kurashi-tetsuzuki/gesuidou/oshirase/mhcard.html</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -850,7 +1109,7 @@
     <col min="4" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.25" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="34.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.4140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.9140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -929,7 +1188,7 @@
         <v>70</v>
       </c>
       <c r="H3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -1015,7 +1274,7 @@
         <v>80</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="C7" t="s">
         <v>81</v>
@@ -1027,13 +1286,13 @@
         <v>143.35443317674901</v>
       </c>
       <c r="F7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>82</v>
       </c>
       <c r="H7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -1041,7 +1300,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="C8" t="s">
         <v>81</v>
@@ -1053,7 +1312,7 @@
         <v>143.35417568467199</v>
       </c>
       <c r="F8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>82</v>
@@ -1067,10 +1326,10 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" t="s">
         <v>87</v>
-      </c>
-      <c r="C9" t="s">
-        <v>89</v>
       </c>
       <c r="D9">
         <v>43.781261071340197</v>
@@ -1079,13 +1338,13 @@
         <v>142.29529780575601</v>
       </c>
       <c r="F9" t="s">
+        <v>88</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="H9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -1093,10 +1352,10 @@
         <v>95</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D10">
         <v>43.780433995221401</v>
@@ -1105,10 +1364,10 @@
         <v>142.29403846130501</v>
       </c>
       <c r="F10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H10" t="s">
         <v>94</v>
@@ -1163,7 +1422,7 @@
         <v>102</v>
       </c>
       <c r="H12" t="s">
-        <v>73</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -1183,7 +1442,7 @@
         <v>141.67355374051701</v>
       </c>
       <c r="F13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>108</v>
@@ -1209,7 +1468,7 @@
         <v>141.67372003748301</v>
       </c>
       <c r="F14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>108</v>
@@ -1456,10 +1715,430 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1DB218F-5FEB-45DE-B539-2FEEADAD69CF}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D2">
+        <v>35.694698830065903</v>
+      </c>
+      <c r="E2">
+        <v>139.98258541349</v>
+      </c>
+      <c r="F2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="H2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D3">
+        <v>35.681715844643897</v>
+      </c>
+      <c r="E3">
+        <v>139.995257163221</v>
+      </c>
+      <c r="F3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="H3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D4">
+        <v>35.856399668951802</v>
+      </c>
+      <c r="E4">
+        <v>139.97543039012601</v>
+      </c>
+      <c r="F4" t="s">
+        <v>173</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="H4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D5">
+        <v>35.861262701949599</v>
+      </c>
+      <c r="E5">
+        <v>139.970762784383</v>
+      </c>
+      <c r="F5" t="s">
+        <v>174</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="H5" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D6">
+        <v>35.776736361277202</v>
+      </c>
+      <c r="E6">
+        <v>140.000808133264</v>
+      </c>
+      <c r="F6" t="s">
+        <v>185</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="H6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>180</v>
+      </c>
+      <c r="B7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C7" t="s">
+        <v>182</v>
+      </c>
+      <c r="D7">
+        <v>35.772968865287297</v>
+      </c>
+      <c r="E7">
+        <v>139.99988447518399</v>
+      </c>
+      <c r="F7" t="s">
+        <v>184</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="H7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" t="s">
+        <v>161</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{EAFA13A4-A446-4378-942C-03D02CFDB61A}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{C6EB4E96-DAF9-46BA-98E7-5A77FDD2CB51}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{FC3ECD16-4A00-4A9E-B8A5-5110B15CD99F}"/>
+    <hyperlink ref="G6" r:id="rId4" xr:uid="{02DF7576-32C8-428E-AB8C-498509C737A5}"/>
+    <hyperlink ref="G7" r:id="rId5" xr:uid="{0644E177-24FA-480D-B8B5-87FA7D87A521}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/places.xlsx
+++ b/places.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hiro7\OneDrive\ドキュメント\アプリ開発\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC3FC385-E031-42D7-94A0-15A19E3B0266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE88931F-6B00-4F5C-B41B-81899C23F889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D86ABE3D-7C83-4A60-8F91-63F1DE7794C1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5270" uniqueCount="3513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5402" uniqueCount="3647">
   <si>
     <t>id</t>
   </si>
@@ -8134,9 +8134,6 @@
     <t>神奈川県横浜市西区南幸1-1-1 JR横浜タワー２階</t>
   </si>
   <si>
-    <t>こちらからご確認ください</t>
-  </si>
-  <si>
     <t>yokohama02</t>
   </si>
   <si>
@@ -8182,9 +8179,6 @@
     <t>【平日】9：00～20：00 【休日】9：00～19：00</t>
   </si>
   <si>
-    <t>こちらからご確認ください。</t>
-  </si>
-  <si>
     <t>【平日】川崎市入江崎水処理センターtワクワクアクア</t>
   </si>
   <si>
@@ -8419,9 +8413,6 @@
     <t>神奈川県秦野市大秦町1（小田急線秦野駅改札出て左）</t>
   </si>
   <si>
-    <t>https://www.city.hadano.kanagawa.jp/kurashi/manhole.html</t>
-  </si>
-  <si>
     <t>厚木市役所 河川下水道施設課</t>
   </si>
   <si>
@@ -8581,9 +8572,6 @@
     <t>神奈川県愛甲郡愛川町角田251-1（3階）</t>
   </si>
   <si>
-    <t>046-285-2111までお問い合わせください</t>
-  </si>
-  <si>
     <t>【休日】愛川町役場 住民課窓口（1階）</t>
   </si>
   <si>
@@ -8608,9 +8596,6 @@
     <t>【平日】9：00～17：00 【休日】10：00～15：00 ただし、休日（土日、祝日、年末年始）に配布をご希望される方は、平日（9：00～17：00）に電話予約が必要です。</t>
   </si>
   <si>
-    <t>025-271-1151までお問い合わせください</t>
-  </si>
-  <si>
     <t>新潟古町まちみなと情報館</t>
   </si>
   <si>
@@ -8620,9 +8605,6 @@
     <t>10：00～17：00 ただし、毎週水曜日、年末年始はお休みです（詳しい休業期間は直接施設へお問合せください）</t>
   </si>
   <si>
-    <t>025-378-4101までお問い合わせください</t>
-  </si>
-  <si>
     <t>niigata02</t>
   </si>
   <si>
@@ -8633,9 +8615,6 @@
   </si>
   <si>
     <t>9：30～17：00 ただし、毎週火曜日（火曜が祝日の場合はその翌日）、年末年始（12/28～1/3）はお休みです</t>
-  </si>
-  <si>
-    <t>0250-24-5700までお問い合わせください</t>
   </si>
   <si>
     <t>ながおか市民協働センター</t>
@@ -10627,6 +10606,433 @@
   </si>
   <si>
     <t>nagano52</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【平日】9:00~16:00 ただし、年末年始はお休みです</t>
+  </si>
+  <si>
+    <t>【土日祝】10:00~20:30 ただし、年末年始・CiCビル休館日はお休みです</t>
+  </si>
+  <si>
+    <t>【12/1～3/15】9：00～17：00 【3/16～11/30】9：00～17：30 ただし、年末年始はお休みです</t>
+  </si>
+  <si>
+    <t>【平日】8:30～17:15</t>
+  </si>
+  <si>
+    <t>【土日祝】10:00～17:00 ただし、年末年始はお休みです（その他、臨時休館有）</t>
+  </si>
+  <si>
+    <t>9：00～17：00 ただし、元日はお休みです</t>
+  </si>
+  <si>
+    <t>9：00～17：00 年末年始（12/29～1/3）</t>
+  </si>
+  <si>
+    <t>9：00～13：30、14：30～17：00</t>
+  </si>
+  <si>
+    <t>【土日祝】10:00～20:30 ただし、年末年始はお休みです</t>
+  </si>
+  <si>
+    <t>10：00～15：30 年中無休</t>
+  </si>
+  <si>
+    <t>9：00～17：00 ただし、毎週水曜（祝日の場合は翌日）、祝日の翌平日及び年末年始はお休みです</t>
+  </si>
+  <si>
+    <t>8:30～22:00 ただし、毎週水曜日（祝日の場合は翌日）、12/31、1/1はお休みです</t>
+  </si>
+  <si>
+    <t>10:00～17:00 ただし、元旦はお休みです。</t>
+  </si>
+  <si>
+    <t>10:00～18:00 月曜日（祝日の場合は翌日）、年末年始はお休みです</t>
+  </si>
+  <si>
+    <t>8：00～17：00</t>
+  </si>
+  <si>
+    <t>【平日】9：00～17：00 ただし、年末年始・お盆などにお休みすることがあります。</t>
+  </si>
+  <si>
+    <t>【土日祝日】9：00～17：00 ただし、年末年始・お盆などにお休みすることがあります。</t>
+  </si>
+  <si>
+    <t>【休日】8：30～10：00、13：00～17：00 土日、祝日及び年末年始休業に配布します</t>
+  </si>
+  <si>
+    <t>【4月～10月】9:00～17:30 【11月～3月】9:00～17:00 ただし、年末年始はお休みです</t>
+  </si>
+  <si>
+    <t>9:00〜18:00（無休）</t>
+  </si>
+  <si>
+    <t>9：00～17：45 ただし、年末年始はお休みです</t>
+  </si>
+  <si>
+    <t>【4/1～12/28】9:00～16：00 ただし、月曜と祝日の翌日はお休みです</t>
+  </si>
+  <si>
+    <t>【12/29～3/31】9:00～16：00 平日は武石地域建設課、休日祝日は宿直室にて配布</t>
+  </si>
+  <si>
+    <t>【平日】9:00〜17:00 ただし年末年始は配布しません</t>
+  </si>
+  <si>
+    <t>【土日祝日】9:00〜17:00 ただし休館日（水曜日、祝日の翌日、年末年始）は配布しません</t>
+  </si>
+  <si>
+    <t>【休日】8：30～17：15</t>
+  </si>
+  <si>
+    <t>9:00～16:00 ただし、木曜日（祝日を除く）、年末年始（12月29日～1月3日）、祝日の翌日はお休みです</t>
+  </si>
+  <si>
+    <t>9:00～17:30 ただし、年末年始(12月29日～1月3日)はお休みです</t>
+  </si>
+  <si>
+    <t>9:00～18:00 ただし、毎週木曜日と年末年始はお休みです（木曜・年末年始は市役所等で配布）</t>
+  </si>
+  <si>
+    <t>【４月～11月】９：00～17：00 【12月～３月】９：30～16：30 ただし、年末年始はお休みです</t>
+  </si>
+  <si>
+    <t>11:00～20:00 ただし、毎月第1、3、5火曜日等はお休みです</t>
+  </si>
+  <si>
+    <t>6:00～22:00(年中無休)</t>
+  </si>
+  <si>
+    <t>8:00～17:30 ただし、年末年始はお休みです</t>
+  </si>
+  <si>
+    <t>10：00～18：30 ただし、年末年始（12月29日から1月3日）はお休みです</t>
+  </si>
+  <si>
+    <t>【土日、祝日】8:30～17:15 ただし、年末年始はお休みです</t>
+  </si>
+  <si>
+    <t>8：30～17：15 ただし、年末年始（12/30～1/3）はお休みです</t>
+  </si>
+  <si>
+    <t>【4月～11月】9:00～17:00 【12月～3月】10:00～16:00 ただし、毎週水曜日と年末年始はお休みです</t>
+  </si>
+  <si>
+    <t>9：00～17：30 ただし、年末年始（12/30～1/3）はお休みです</t>
+  </si>
+  <si>
+    <t>8:00～20:00</t>
+  </si>
+  <si>
+    <t>9:00～18：00 ただし、火曜日・年末年始はお休みです</t>
+  </si>
+  <si>
+    <t>15：30～18：00（十三くら） ただし、日・月曜日、年末年始はお休みです</t>
+  </si>
+  <si>
+    <t>9：15～18：00 ただし、年末年始（12/29～1/3）はお休みです</t>
+  </si>
+  <si>
+    <t>9:00～17:00 ただし、毎週月曜日、祝日の翌日、年末年始(12月28日～1月3日)はお休みです</t>
+  </si>
+  <si>
+    <t>9:00～17:00 ただし、毎週月曜日、休日の翌日、年末年始(12月28日～1月3日)はお休みです</t>
+  </si>
+  <si>
+    <t>9:00～17:00 ただし、毎週月曜日（祝日を除く）、休日の翌日、12/29から1/3はお休みです</t>
+  </si>
+  <si>
+    <t>8:00～18:00 ただし、年末年始はお休みです</t>
+  </si>
+  <si>
+    <t>10：00〜16：00（平日・土日祝とも）</t>
+  </si>
+  <si>
+    <t>8：30〜17：15（開庁日のみ）</t>
+  </si>
+  <si>
+    <t>9:00～17:00 ただし水曜日、年末年始はお休み（7/15～10/31は無休）</t>
+  </si>
+  <si>
+    <t>9:00～12:00、13:00～17:00（12/29～1/3は短縮営業）</t>
+  </si>
+  <si>
+    <t>9：30～16：30 ただし、水曜日及び年末年始はお休みです</t>
+  </si>
+  <si>
+    <t>【3～11月】9:00～17:00 【12～2月】9:00～16:00 ただし年末年始・冬季水曜はお休み</t>
+  </si>
+  <si>
+    <t>【3～11月】9:00～17:00 【12～2月】9:00～16:00 ただし、年末年始はお休みです</t>
+  </si>
+  <si>
+    <t>9：30 ～ 18：00 (11月～3月は17：00まで) ただし毎週水曜日と年末年始はお休み</t>
+  </si>
+  <si>
+    <t>【土日祝日】9：00～17：00</t>
+  </si>
+  <si>
+    <t>【土日祝日】10：00～18：00 ただし月曜、第1水曜、年末年始はお休み</t>
+  </si>
+  <si>
+    <t>【土日祝】8：30～17：15</t>
+  </si>
+  <si>
+    <t>【火曜日以外】10：00～20：30</t>
+  </si>
+  <si>
+    <t>【火】8：30～17：15</t>
+  </si>
+  <si>
+    <t>【休日】8:30～17:15</t>
+  </si>
+  <si>
+    <t>【土日祝日】7:00～22:00</t>
+  </si>
+  <si>
+    <t>10:00～21:00</t>
+  </si>
+  <si>
+    <t>8:30～17:15（土日祝日、年末年始を除く）</t>
+  </si>
+  <si>
+    <t>8：30～17：15 ただし、休日（土日、祝日、年末年始）に配布を希望される方は、平日（開庁日）15時までに予約が必要です。</t>
+  </si>
+  <si>
+    <t>9:00～17:00 ただし、年始及び定休日はお休みです</t>
+  </si>
+  <si>
+    <t>9：30～17：00 ただし、水曜日はお休みです</t>
+  </si>
+  <si>
+    <t>9:00～18:00（月曜日定休）</t>
+  </si>
+  <si>
+    <t>9:00～18：00 年中無休</t>
+  </si>
+  <si>
+    <t>【平日】8：30～17：15 ただし、土日、祝日、年末年始はお休みです</t>
+  </si>
+  <si>
+    <t>【土日祝日】①9:00～16:30 ②9:00～17:00 ただし、年末年始（12/29～1/3）はお休みです</t>
+  </si>
+  <si>
+    <t>9：00～16：30 ただし、年末年始（12/28～1/4）はお休みです</t>
+  </si>
+  <si>
+    <t>9：00～17：00 ただし、水曜日(祝日の場合は翌平日)、年末年始はお休みです。</t>
+  </si>
+  <si>
+    <t>9:00～16:30 ただし、水曜日(祝日の場合はその翌日)および年末年始はお休みです</t>
+  </si>
+  <si>
+    <t>9：00～17：00 ただし、月曜日、祝日の翌日、年末年始はお休みです</t>
+  </si>
+  <si>
+    <t>9：00～17：00 ただし、年末年始（12/29～1/2）はお休みです</t>
+  </si>
+  <si>
+    <t>9:00～17:00 ただし、第2・第3火曜日、年末年始（12月30日～1月1日）はお休みです</t>
+  </si>
+  <si>
+    <t>9：30～17：00 ただし、火曜日はお休みです</t>
+  </si>
+  <si>
+    <t>9：00～16：30 ただし、毎週火曜日（火曜日が国民の祝日等の場合はその翌日）、及び年末年始はお休みです</t>
+  </si>
+  <si>
+    <t>9：00～16：00 必ず休館日をご確認ください。</t>
+  </si>
+  <si>
+    <t>10：00～17：00 必ず休館日をご確認ください。</t>
+  </si>
+  <si>
+    <t>10:00～17:00 ただし、毎週火曜（祝日の場合はその翌日）、年末年始（12/29～1/3）はお休みです</t>
+  </si>
+  <si>
+    <t>【平日】8：30～17：15 ただし、年末年始(12/29～1/3)はお休みです</t>
+  </si>
+  <si>
+    <t>【土日祝日】9：00-17：30(3～11月) 9：00-17：00（12～2月） ただし、年末年始(12/31,1/1)はお休みです</t>
+  </si>
+  <si>
+    <t>【土日祝日】9：00～17：00 ただし、年末年始（12/29～1/3はお休みです</t>
+  </si>
+  <si>
+    <t>9:00～17:00 ただし、年末年始（12月29日～1月3日）は定休日です</t>
+  </si>
+  <si>
+    <t>9:30～17:00 ただし、年末年始（12月29日～1月3日）は定休日です</t>
+  </si>
+  <si>
+    <t>【土日祝】9：30～18：00 ただし、年末年始（12/29～1/3）はお休みです</t>
+  </si>
+  <si>
+    <t>【平日】10：00～19：00 【土日祝】9：00～17：00 ただし、毎週月曜日、年末年始(12/29～1/4)等はお休みです</t>
+  </si>
+  <si>
+    <t>【土日祝日】8:30～17:00 ただし、年末年始はお休みです</t>
+  </si>
+  <si>
+    <t>【平日】9：00～17：00 ただし、祝祭日、年末年始（12/29-1/3）はお休みです</t>
+  </si>
+  <si>
+    <t>【土日】9：30～17：00 ただし、年末年始（12/29-1/3）はお休みです</t>
+  </si>
+  <si>
+    <t>【平日】9：00～16：00 【土日祝日】9：00～16：30</t>
+  </si>
+  <si>
+    <t>【3/20～11/30】9:00～16:30 【12/1～3/19】9:30～16:00 ただし【12～2月】毎週水曜日及び12/31はお休みです</t>
+  </si>
+  <si>
+    <t>https://www.welcome.city.yokohama.jp/</t>
+  </si>
+  <si>
+    <t>https://www.city.yokohama.lg.jp/</t>
+  </si>
+  <si>
+    <t>https://www.city.kawasaki.jp/</t>
+  </si>
+  <si>
+    <t>https://www.city.sagamihara.kanagawa.jp/</t>
+  </si>
+  <si>
+    <t>https://www.city.yokosuka.kanagawa.jp/</t>
+  </si>
+  <si>
+    <t>https://www.city.fujisawa.kanagawa.jp/</t>
+  </si>
+  <si>
+    <t>https://www.city.odawara.kanagawa.jp/</t>
+  </si>
+  <si>
+    <t>https://www.city.chigasaki.kanagawa.jp/</t>
+  </si>
+  <si>
+    <t>https://www.city.zushi.kanagawa.jp/</t>
+  </si>
+  <si>
+    <t>https://www.city.miura.kanagawa.jp/</t>
+  </si>
+  <si>
+    <t>https://www.city.hadano.kanagawa.jp/</t>
+  </si>
+  <si>
+    <t>https://www.city.atsugi.kanagawa.jp/</t>
+  </si>
+  <si>
+    <t>https://www.city.yamato.lg.jp/</t>
+  </si>
+  <si>
+    <t>https://www.city.ishehama.kanagawa.jp/</t>
+  </si>
+  <si>
+    <t>https://www.city.isehara.kanagawa.jp/</t>
+  </si>
+  <si>
+    <t>https://www.city.ebina.kanagawa.jp/</t>
+  </si>
+  <si>
+    <t>https://www.city.zama.kanagawa.jp/</t>
+  </si>
+  <si>
+    <t>https://www.city.ayase.kanagawa.jp/</t>
+  </si>
+  <si>
+    <t>https://www.town.hayama.lg.jp/</t>
+  </si>
+  <si>
+    <t>https://www.town.ninomiya.kanagawa.jp/</t>
+  </si>
+  <si>
+    <t>https://www.town.nakai.kanagawa.jp/</t>
+  </si>
+  <si>
+    <t>https://www.town.oi.kanagawa.jp/</t>
+  </si>
+  <si>
+    <t>https://www.town.yamakita.kanagawa.jp/</t>
+  </si>
+  <si>
+    <t>https://www.town.aikawa.kanagawa.jp/</t>
+  </si>
+  <si>
+    <t>https://www.vill.kiyokawa.kanagawa.jp/</t>
+  </si>
+  <si>
+    <t>https://www.pref.niigata.lg.jp/</t>
+  </si>
+  <si>
+    <t>https://www.city.niigata.lg.jp/</t>
+  </si>
+  <si>
+    <t>https://www.city.nagaoka.niigata.jp/</t>
+  </si>
+  <si>
+    <t>https://www.city.sanjo.niigata.jp/</t>
+  </si>
+  <si>
+    <t>https://www.city.kashiwazaki.lg.jp/</t>
+  </si>
+  <si>
+    <t>https://www.city.shibata.lg.jp/</t>
+  </si>
+  <si>
+    <t>https://www.city.ojiya.niigata.jp/</t>
+  </si>
+  <si>
+    <t>https://www.city.kamo.niigata.jp/</t>
+  </si>
+  <si>
+    <t>https://www.city.tokamachi.lg.jp/</t>
+  </si>
+  <si>
+    <t>https://www.city.mitsuke.niigata.jp/</t>
+  </si>
+  <si>
+    <t>https://www.city.murakami.lg.jp/</t>
+  </si>
+  <si>
+    <t>https://www.city.tsubame.niigata.jp/</t>
+  </si>
+  <si>
+    <t>https://www.city.itoigawa.lg.jp/</t>
+  </si>
+  <si>
+    <t>https://www.city.myoko.niigata.jp/</t>
+  </si>
+  <si>
+    <t>https://www.city.sado.niigata.jp/</t>
+  </si>
+  <si>
+    <t>https://www.city.tainai.niigata.jp/</t>
+  </si>
+  <si>
+    <t>https://www.town.izumozaki.niigata.jp/</t>
+  </si>
+  <si>
+    <t>https://www.city.wajima.ishikawa.jp/</t>
+  </si>
+  <si>
+    <t>https://www.city.uenohara.yamanashi.jp/</t>
+  </si>
+  <si>
+    <t>https://www.city.toyama.lg.jp/</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.city.wajima.ishikawa.jp/</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.city.kahoku.lg.jp/</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.city.uenohara.yamanashi.jp/</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -10634,7 +11040,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -10645,6 +11051,15 @@
     </font>
     <font>
       <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="128"/>
@@ -10668,17 +11083,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -10692,6 +11114,23 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{393C521F-3F1E-4681-B334-168A7E03BE2D}" name="テーブル1" displayName="テーブル1" ref="A1:H1048576" totalsRowShown="0">
+  <autoFilter ref="A1:H1048576" xr:uid="{393C521F-3F1E-4681-B334-168A7E03BE2D}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{782ADDD7-DC62-49D1-905F-FE81F52FEA5D}" name="id"/>
+    <tableColumn id="2" xr3:uid="{17124DF4-5BB9-4DA6-9830-E68B822729B5}" name="name"/>
+    <tableColumn id="3" xr3:uid="{7AB84F3B-2CB2-4C35-8A78-AA584917A10E}" name="address"/>
+    <tableColumn id="4" xr3:uid="{8AAF715A-C076-47D3-BD7E-CD1F464CFA0A}" name="lat"/>
+    <tableColumn id="5" xr3:uid="{DDC9E73A-CAA7-43EC-AFDD-4D4DCF589F23}" name="lng"/>
+    <tableColumn id="6" xr3:uid="{6625E71E-5B23-4972-900F-C582B06C691B}" name="info"/>
+    <tableColumn id="7" xr3:uid="{64D1454F-A2AF-4668-B67D-DF92BFF96552}" name="hp"/>
+    <tableColumn id="8" xr3:uid="{CF7768BC-0A3B-4F9F-BEA7-D4E8D2B7C8D8}" name="schedule_type"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -28094,7 +28533,7 @@
         <v>9</v>
       </c>
       <c r="G657" t="s">
-        <v>2697</v>
+        <v>3599</v>
       </c>
       <c r="H657" t="s">
         <v>45</v>
@@ -28102,13 +28541,13 @@
     </row>
     <row r="658" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A658" t="s">
+        <v>2697</v>
+      </c>
+      <c r="B658" t="s">
         <v>2698</v>
       </c>
-      <c r="B658" t="s">
+      <c r="C658" t="s">
         <v>2699</v>
-      </c>
-      <c r="C658" t="s">
-        <v>2700</v>
       </c>
       <c r="D658">
         <v>35.474888</v>
@@ -28117,10 +28556,10 @@
         <v>139.54484600000001</v>
       </c>
       <c r="F658" t="s">
-        <v>2701</v>
+        <v>2700</v>
       </c>
       <c r="G658" t="s">
-        <v>2697</v>
+        <v>3600</v>
       </c>
       <c r="H658" t="s">
         <v>90</v>
@@ -28128,13 +28567,13 @@
     </row>
     <row r="659" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A659" t="s">
-        <v>2698</v>
+        <v>2697</v>
       </c>
       <c r="B659" t="s">
+        <v>2701</v>
+      </c>
+      <c r="C659" t="s">
         <v>2702</v>
-      </c>
-      <c r="C659" t="s">
-        <v>2703</v>
       </c>
       <c r="D659">
         <v>35.474730999999998</v>
@@ -28143,10 +28582,10 @@
         <v>139.55038500000001</v>
       </c>
       <c r="F659" t="s">
-        <v>2704</v>
+        <v>2703</v>
       </c>
       <c r="G659" t="s">
-        <v>2697</v>
+        <v>3600</v>
       </c>
       <c r="H659" t="s">
         <v>23</v>
@@ -28154,13 +28593,13 @@
     </row>
     <row r="660" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A660" t="s">
+        <v>2704</v>
+      </c>
+      <c r="B660" t="s">
         <v>2705</v>
       </c>
-      <c r="B660" t="s">
-        <v>2706</v>
-      </c>
       <c r="C660" t="s">
-        <v>2700</v>
+        <v>2699</v>
       </c>
       <c r="D660">
         <v>35.474888</v>
@@ -28172,7 +28611,7 @@
         <v>208</v>
       </c>
       <c r="G660" t="s">
-        <v>2697</v>
+        <v>3600</v>
       </c>
       <c r="H660" t="s">
         <v>209</v>
@@ -28180,13 +28619,13 @@
     </row>
     <row r="661" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A661" t="s">
+        <v>2706</v>
+      </c>
+      <c r="B661" t="s">
         <v>2707</v>
       </c>
-      <c r="B661" t="s">
+      <c r="C661" t="s">
         <v>2708</v>
-      </c>
-      <c r="C661" t="s">
-        <v>2709</v>
       </c>
       <c r="D661">
         <v>35.453564</v>
@@ -28198,7 +28637,7 @@
         <v>9</v>
       </c>
       <c r="G661" t="s">
-        <v>2697</v>
+        <v>3599</v>
       </c>
       <c r="H661" t="s">
         <v>45</v>
@@ -28206,13 +28645,13 @@
     </row>
     <row r="662" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A662" t="s">
-        <v>2994</v>
+        <v>2987</v>
       </c>
       <c r="B662" t="s">
+        <v>2709</v>
+      </c>
+      <c r="C662" t="s">
         <v>2710</v>
-      </c>
-      <c r="C662" t="s">
-        <v>2711</v>
       </c>
       <c r="D662">
         <v>35.530124999999998</v>
@@ -28221,10 +28660,10 @@
         <v>139.697968</v>
       </c>
       <c r="F662" t="s">
-        <v>2712</v>
+        <v>2711</v>
       </c>
       <c r="G662" t="s">
-        <v>2713</v>
+        <v>3601</v>
       </c>
       <c r="H662" t="s">
         <v>45</v>
@@ -28232,13 +28671,13 @@
     </row>
     <row r="663" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A663" t="s">
-        <v>2995</v>
+        <v>2988</v>
       </c>
       <c r="B663" t="s">
-        <v>2714</v>
+        <v>2712</v>
       </c>
       <c r="C663" t="s">
-        <v>2715</v>
+        <v>2713</v>
       </c>
       <c r="D663">
         <v>35.518639</v>
@@ -28247,10 +28686,10 @@
         <v>139.73904400000001</v>
       </c>
       <c r="F663" t="s">
-        <v>2716</v>
+        <v>2714</v>
       </c>
       <c r="G663" t="s">
-        <v>2697</v>
+        <v>3601</v>
       </c>
       <c r="H663" t="s">
         <v>90</v>
@@ -28258,13 +28697,13 @@
     </row>
     <row r="664" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A664" t="s">
-        <v>3030</v>
+        <v>3023</v>
       </c>
       <c r="B664" t="s">
-        <v>2717</v>
+        <v>2715</v>
       </c>
       <c r="C664" t="s">
-        <v>2718</v>
+        <v>2716</v>
       </c>
       <c r="D664">
         <v>35.530864999999999</v>
@@ -28273,10 +28712,10 @@
         <v>139.703033</v>
       </c>
       <c r="F664" t="s">
-        <v>2719</v>
+        <v>2717</v>
       </c>
       <c r="G664" t="s">
-        <v>2697</v>
+        <v>3601</v>
       </c>
       <c r="H664" t="s">
         <v>72</v>
@@ -28284,13 +28723,13 @@
     </row>
     <row r="665" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A665" t="s">
-        <v>2996</v>
+        <v>2989</v>
       </c>
       <c r="B665" t="s">
-        <v>2720</v>
+        <v>2718</v>
       </c>
       <c r="C665" t="s">
-        <v>2721</v>
+        <v>2719</v>
       </c>
       <c r="D665">
         <v>35.532429</v>
@@ -28299,10 +28738,10 @@
         <v>139.70309399999999</v>
       </c>
       <c r="F665" t="s">
-        <v>2722</v>
+        <v>2720</v>
       </c>
       <c r="G665" t="s">
-        <v>2697</v>
+        <v>3601</v>
       </c>
       <c r="H665" t="s">
         <v>17</v>
@@ -28310,13 +28749,13 @@
     </row>
     <row r="666" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A666" t="s">
-        <v>2997</v>
+        <v>2990</v>
       </c>
       <c r="B666" t="s">
-        <v>2723</v>
+        <v>2721</v>
       </c>
       <c r="C666" t="s">
-        <v>2724</v>
+        <v>2722</v>
       </c>
       <c r="D666">
         <v>35.571013999999998</v>
@@ -28328,7 +28767,7 @@
         <v>2042</v>
       </c>
       <c r="G666" t="s">
-        <v>2697</v>
+        <v>3602</v>
       </c>
       <c r="H666" t="s">
         <v>90</v>
@@ -28336,13 +28775,13 @@
     </row>
     <row r="667" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A667" t="s">
-        <v>2998</v>
+        <v>2991</v>
       </c>
       <c r="B667" t="s">
-        <v>2725</v>
+        <v>2723</v>
       </c>
       <c r="C667" t="s">
-        <v>2726</v>
+        <v>2724</v>
       </c>
       <c r="D667">
         <v>35.617519000000001</v>
@@ -28351,10 +28790,10 @@
         <v>139.189041</v>
       </c>
       <c r="F667" t="s">
-        <v>2727</v>
+        <v>2725</v>
       </c>
       <c r="G667" t="s">
-        <v>2697</v>
+        <v>3602</v>
       </c>
       <c r="H667" t="s">
         <v>23</v>
@@ -28362,13 +28801,13 @@
     </row>
     <row r="668" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A668" t="s">
-        <v>2999</v>
+        <v>2992</v>
       </c>
       <c r="B668" t="s">
-        <v>2728</v>
+        <v>2726</v>
       </c>
       <c r="C668" t="s">
-        <v>2729</v>
+        <v>2727</v>
       </c>
       <c r="D668">
         <v>35.558784000000003</v>
@@ -28377,10 +28816,10 @@
         <v>139.39329499999999</v>
       </c>
       <c r="F668" t="s">
-        <v>2730</v>
+        <v>2728</v>
       </c>
       <c r="G668" t="s">
-        <v>2697</v>
+        <v>3602</v>
       </c>
       <c r="H668" t="s">
         <v>17</v>
@@ -28388,13 +28827,13 @@
     </row>
     <row r="669" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A669" t="s">
-        <v>3000</v>
+        <v>2993</v>
       </c>
       <c r="B669" t="s">
-        <v>2731</v>
+        <v>2729</v>
       </c>
       <c r="C669" t="s">
-        <v>2732</v>
+        <v>2730</v>
       </c>
       <c r="D669">
         <v>35.531737999999997</v>
@@ -28403,10 +28842,10 @@
         <v>139.43524199999999</v>
       </c>
       <c r="F669" t="s">
-        <v>2733</v>
+        <v>2731</v>
       </c>
       <c r="G669" t="s">
-        <v>2697</v>
+        <v>3602</v>
       </c>
       <c r="H669" t="s">
         <v>45</v>
@@ -28414,13 +28853,13 @@
     </row>
     <row r="670" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A670" t="s">
-        <v>3001</v>
+        <v>2994</v>
       </c>
       <c r="B670" t="s">
-        <v>2734</v>
+        <v>2732</v>
       </c>
       <c r="C670" t="s">
-        <v>2735</v>
+        <v>2733</v>
       </c>
       <c r="D670">
         <v>35.278213999999998</v>
@@ -28429,10 +28868,10 @@
         <v>139.669861</v>
       </c>
       <c r="F670" t="s">
-        <v>2736</v>
+        <v>2734</v>
       </c>
       <c r="G670" t="s">
-        <v>2697</v>
+        <v>3603</v>
       </c>
       <c r="H670" t="s">
         <v>23</v>
@@ -28440,13 +28879,13 @@
     </row>
     <row r="671" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A671" t="s">
-        <v>3002</v>
+        <v>2995</v>
       </c>
       <c r="B671" t="s">
-        <v>2737</v>
+        <v>2735</v>
       </c>
       <c r="C671" t="s">
-        <v>2738</v>
+        <v>2736</v>
       </c>
       <c r="D671">
         <v>35.244213000000002</v>
@@ -28455,10 +28894,10 @@
         <v>139.71507299999999</v>
       </c>
       <c r="F671" t="s">
-        <v>2739</v>
+        <v>2737</v>
       </c>
       <c r="G671" t="s">
-        <v>2697</v>
+        <v>3603</v>
       </c>
       <c r="H671" t="s">
         <v>23</v>
@@ -28466,13 +28905,13 @@
     </row>
     <row r="672" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A672" t="s">
-        <v>3003</v>
+        <v>2996</v>
       </c>
       <c r="B672" t="s">
-        <v>2740</v>
+        <v>2738</v>
       </c>
       <c r="C672" t="s">
-        <v>2741</v>
+        <v>2739</v>
       </c>
       <c r="D672">
         <v>35.284469999999999</v>
@@ -28484,7 +28923,7 @@
         <v>80</v>
       </c>
       <c r="G672" t="s">
-        <v>2697</v>
+        <v>3603</v>
       </c>
       <c r="H672" t="s">
         <v>45</v>
@@ -28492,13 +28931,13 @@
     </row>
     <row r="673" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A673" t="s">
-        <v>3004</v>
+        <v>2997</v>
       </c>
       <c r="B673" t="s">
-        <v>2742</v>
+        <v>2740</v>
       </c>
       <c r="C673" t="s">
-        <v>2743</v>
+        <v>2741</v>
       </c>
       <c r="D673">
         <v>35.257930999999999</v>
@@ -28507,10 +28946,10 @@
         <v>139.66223099999999</v>
       </c>
       <c r="F673" t="s">
-        <v>2744</v>
+        <v>2742</v>
       </c>
       <c r="G673" t="s">
-        <v>2697</v>
+        <v>3603</v>
       </c>
       <c r="H673" t="s">
         <v>23</v>
@@ -28518,13 +28957,13 @@
     </row>
     <row r="674" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A674" t="s">
-        <v>3031</v>
+        <v>3024</v>
       </c>
       <c r="B674" t="s">
-        <v>2745</v>
+        <v>2743</v>
       </c>
       <c r="C674" t="s">
-        <v>2746</v>
+        <v>2744</v>
       </c>
       <c r="D674">
         <v>35.257277999999999</v>
@@ -28533,10 +28972,10 @@
         <v>139.662567</v>
       </c>
       <c r="F674" t="s">
-        <v>2744</v>
+        <v>2742</v>
       </c>
       <c r="G674" t="s">
-        <v>2697</v>
+        <v>3603</v>
       </c>
       <c r="H674" t="s">
         <v>23</v>
@@ -28544,13 +28983,13 @@
     </row>
     <row r="675" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A675" t="s">
-        <v>3005</v>
+        <v>2998</v>
       </c>
       <c r="B675" t="s">
-        <v>2747</v>
+        <v>2745</v>
       </c>
       <c r="C675" t="s">
-        <v>2748</v>
+        <v>2746</v>
       </c>
       <c r="D675">
         <v>35.359631</v>
@@ -28559,10 +28998,10 @@
         <v>139.36174</v>
       </c>
       <c r="F675" t="s">
-        <v>2749</v>
+        <v>2747</v>
       </c>
       <c r="G675" t="s">
-        <v>2697</v>
+        <v>3603</v>
       </c>
       <c r="H675" t="s">
         <v>17</v>
@@ -28570,13 +29009,13 @@
     </row>
     <row r="676" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A676" t="s">
-        <v>3006</v>
+        <v>2999</v>
       </c>
       <c r="B676" t="s">
-        <v>2750</v>
+        <v>2748</v>
       </c>
       <c r="C676" t="s">
-        <v>2751</v>
+        <v>2749</v>
       </c>
       <c r="D676">
         <v>35.340195000000001</v>
@@ -28585,10 +29024,10 @@
         <v>139.44790599999999</v>
       </c>
       <c r="F676" t="s">
-        <v>2752</v>
+        <v>2750</v>
       </c>
       <c r="G676" t="s">
-        <v>2697</v>
+        <v>3604</v>
       </c>
       <c r="H676" t="s">
         <v>17</v>
@@ -28596,13 +29035,13 @@
     </row>
     <row r="677" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A677" t="s">
-        <v>3007</v>
+        <v>3000</v>
       </c>
       <c r="B677" t="s">
-        <v>2753</v>
+        <v>2751</v>
       </c>
       <c r="C677" t="s">
-        <v>2754</v>
+        <v>2752</v>
       </c>
       <c r="D677">
         <v>35.346457999999998</v>
@@ -28611,10 +29050,10 @@
         <v>139.487289</v>
       </c>
       <c r="F677" t="s">
-        <v>2755</v>
+        <v>2753</v>
       </c>
       <c r="G677" t="s">
-        <v>2697</v>
+        <v>3604</v>
       </c>
       <c r="H677" t="s">
         <v>147</v>
@@ -28622,13 +29061,13 @@
     </row>
     <row r="678" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A678" t="s">
-        <v>3008</v>
+        <v>3001</v>
       </c>
       <c r="B678" t="s">
-        <v>2756</v>
+        <v>2754</v>
       </c>
       <c r="C678" t="s">
-        <v>2757</v>
+        <v>2755</v>
       </c>
       <c r="D678">
         <v>35.288764999999998</v>
@@ -28640,7 +29079,7 @@
         <v>1665</v>
       </c>
       <c r="G678" t="s">
-        <v>2697</v>
+        <v>3605</v>
       </c>
       <c r="H678" t="s">
         <v>147</v>
@@ -28648,13 +29087,13 @@
     </row>
     <row r="679" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A679" t="s">
-        <v>3032</v>
+        <v>3025</v>
       </c>
       <c r="B679" t="s">
-        <v>2758</v>
+        <v>2756</v>
       </c>
       <c r="C679" t="s">
-        <v>2759</v>
+        <v>2757</v>
       </c>
       <c r="D679">
         <v>35.248309999999996</v>
@@ -28666,7 +29105,7 @@
         <v>1665</v>
       </c>
       <c r="G679" t="s">
-        <v>2697</v>
+        <v>3605</v>
       </c>
       <c r="H679" t="s">
         <v>147</v>
@@ -28674,13 +29113,13 @@
     </row>
     <row r="680" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A680" t="s">
-        <v>3009</v>
+        <v>3002</v>
       </c>
       <c r="B680" t="s">
-        <v>2760</v>
+        <v>2758</v>
       </c>
       <c r="C680" t="s">
-        <v>2761</v>
+        <v>2759</v>
       </c>
       <c r="D680">
         <v>35.249054000000001</v>
@@ -28692,7 +29131,7 @@
         <v>2098</v>
       </c>
       <c r="G680" t="s">
-        <v>2697</v>
+        <v>3605</v>
       </c>
       <c r="H680" t="s">
         <v>23</v>
@@ -28700,13 +29139,13 @@
     </row>
     <row r="681" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A681" t="s">
-        <v>3010</v>
+        <v>3003</v>
       </c>
       <c r="B681" t="s">
-        <v>2762</v>
+        <v>2760</v>
       </c>
       <c r="C681" t="s">
-        <v>2759</v>
+        <v>2757</v>
       </c>
       <c r="D681">
         <v>35.248309999999996</v>
@@ -28718,7 +29157,7 @@
         <v>1665</v>
       </c>
       <c r="G681" t="s">
-        <v>2697</v>
+        <v>3605</v>
       </c>
       <c r="H681" t="s">
         <v>23</v>
@@ -28726,13 +29165,13 @@
     </row>
     <row r="682" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A682" t="s">
-        <v>3011</v>
+        <v>3004</v>
       </c>
       <c r="B682" t="s">
-        <v>2763</v>
+        <v>2761</v>
       </c>
       <c r="C682" t="s">
-        <v>2764</v>
+        <v>2762</v>
       </c>
       <c r="D682">
         <v>35.255634000000001</v>
@@ -28741,10 +29180,10 @@
         <v>139.15632600000001</v>
       </c>
       <c r="F682" t="s">
-        <v>2765</v>
+        <v>2763</v>
       </c>
       <c r="G682" t="s">
-        <v>2697</v>
+        <v>3605</v>
       </c>
       <c r="H682" t="s">
         <v>147</v>
@@ -28752,13 +29191,13 @@
     </row>
     <row r="683" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A683" t="s">
-        <v>3012</v>
+        <v>3005</v>
       </c>
       <c r="B683" t="s">
-        <v>2766</v>
+        <v>2764</v>
       </c>
       <c r="C683" t="s">
-        <v>2767</v>
+        <v>2765</v>
       </c>
       <c r="D683">
         <v>35.251300999999998</v>
@@ -28767,10 +29206,10 @@
         <v>139.15391500000001</v>
       </c>
       <c r="F683" t="s">
-        <v>2768</v>
+        <v>2766</v>
       </c>
       <c r="G683" t="s">
-        <v>2697</v>
+        <v>3605</v>
       </c>
       <c r="H683" t="s">
         <v>147</v>
@@ -28778,13 +29217,13 @@
     </row>
     <row r="684" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A684" t="s">
-        <v>3013</v>
+        <v>3006</v>
       </c>
       <c r="B684" t="s">
-        <v>2769</v>
+        <v>2767</v>
       </c>
       <c r="C684" t="s">
-        <v>2770</v>
+        <v>2768</v>
       </c>
       <c r="D684">
         <v>35.249099999999999</v>
@@ -28793,24 +29232,24 @@
         <v>139.14437899999999</v>
       </c>
       <c r="F684" t="s">
-        <v>2771</v>
+        <v>2769</v>
       </c>
       <c r="G684" t="s">
-        <v>2697</v>
+        <v>3605</v>
       </c>
       <c r="H684" t="s">
-        <v>2772</v>
+        <v>2770</v>
       </c>
     </row>
     <row r="685" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A685" t="s">
-        <v>3014</v>
+        <v>3007</v>
       </c>
       <c r="B685" t="s">
-        <v>2773</v>
+        <v>2771</v>
       </c>
       <c r="C685" t="s">
-        <v>2774</v>
+        <v>2772</v>
       </c>
       <c r="D685">
         <v>35.330578000000003</v>
@@ -28819,10 +29258,10 @@
         <v>139.40670800000001</v>
       </c>
       <c r="F685" t="s">
-        <v>2775</v>
+        <v>2773</v>
       </c>
       <c r="G685" t="s">
-        <v>2697</v>
+        <v>3606</v>
       </c>
       <c r="H685" t="s">
         <v>23</v>
@@ -28830,13 +29269,13 @@
     </row>
     <row r="686" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A686" t="s">
-        <v>3015</v>
+        <v>3008</v>
       </c>
       <c r="B686" t="s">
-        <v>2776</v>
+        <v>2774</v>
       </c>
       <c r="C686" t="s">
-        <v>2777</v>
+        <v>2775</v>
       </c>
       <c r="D686">
         <v>35.320404000000003</v>
@@ -28845,10 +29284,10 @@
         <v>139.37776199999999</v>
       </c>
       <c r="F686" t="s">
-        <v>2778</v>
+        <v>2776</v>
       </c>
       <c r="G686" t="s">
-        <v>2697</v>
+        <v>3606</v>
       </c>
       <c r="H686" t="s">
         <v>45</v>
@@ -28856,13 +29295,13 @@
     </row>
     <row r="687" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A687" t="s">
-        <v>3016</v>
+        <v>3009</v>
       </c>
       <c r="B687" t="s">
-        <v>2779</v>
+        <v>2777</v>
       </c>
       <c r="C687" t="s">
-        <v>2780</v>
+        <v>2778</v>
       </c>
       <c r="D687">
         <v>35.295479</v>
@@ -28871,10 +29310,10 @@
         <v>139.580658</v>
       </c>
       <c r="F687" t="s">
-        <v>2781</v>
+        <v>2779</v>
       </c>
       <c r="G687" t="s">
-        <v>2697</v>
+        <v>3607</v>
       </c>
       <c r="H687" t="s">
         <v>90</v>
@@ -28882,13 +29321,13 @@
     </row>
     <row r="688" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A688" t="s">
-        <v>3033</v>
+        <v>3026</v>
       </c>
       <c r="B688" t="s">
-        <v>2782</v>
+        <v>2780</v>
       </c>
       <c r="C688" t="s">
-        <v>2780</v>
+        <v>2778</v>
       </c>
       <c r="D688">
         <v>35.295479</v>
@@ -28897,10 +29336,10 @@
         <v>139.580658</v>
       </c>
       <c r="F688" t="s">
-        <v>2781</v>
+        <v>2779</v>
       </c>
       <c r="G688" t="s">
-        <v>2697</v>
+        <v>3607</v>
       </c>
       <c r="H688" t="s">
         <v>97</v>
@@ -28908,13 +29347,13 @@
     </row>
     <row r="689" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A689" t="s">
-        <v>3034</v>
+        <v>3027</v>
       </c>
       <c r="B689" t="s">
-        <v>2783</v>
+        <v>2781</v>
       </c>
       <c r="C689" t="s">
-        <v>2784</v>
+        <v>2782</v>
       </c>
       <c r="D689">
         <v>35.143959000000002</v>
@@ -28926,7 +29365,7 @@
         <v>2563</v>
       </c>
       <c r="G689" t="s">
-        <v>2697</v>
+        <v>3608</v>
       </c>
       <c r="H689" t="s">
         <v>90</v>
@@ -28934,13 +29373,13 @@
     </row>
     <row r="690" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A690" t="s">
-        <v>3034</v>
+        <v>3027</v>
       </c>
       <c r="B690" t="s">
-        <v>2785</v>
+        <v>2783</v>
       </c>
       <c r="C690" t="s">
-        <v>2786</v>
+        <v>2784</v>
       </c>
       <c r="D690">
         <v>35.188000000000002</v>
@@ -28949,10 +29388,10 @@
         <v>139.65678399999999</v>
       </c>
       <c r="F690" t="s">
-        <v>2787</v>
+        <v>2785</v>
       </c>
       <c r="G690" t="s">
-        <v>2697</v>
+        <v>3608</v>
       </c>
       <c r="H690" t="s">
         <v>97</v>
@@ -28960,13 +29399,13 @@
     </row>
     <row r="691" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A691" t="s">
-        <v>3035</v>
+        <v>3028</v>
       </c>
       <c r="B691" t="s">
-        <v>2788</v>
+        <v>2786</v>
       </c>
       <c r="C691" t="s">
-        <v>2789</v>
+        <v>2787</v>
       </c>
       <c r="D691">
         <v>35.364037000000003</v>
@@ -28978,7 +29417,7 @@
         <v>1995</v>
       </c>
       <c r="G691" t="s">
-        <v>2697</v>
+        <v>3609</v>
       </c>
       <c r="H691" t="s">
         <v>23</v>
@@ -28986,13 +29425,13 @@
     </row>
     <row r="692" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A692" t="s">
-        <v>3035</v>
+        <v>3028</v>
       </c>
       <c r="B692" t="s">
-        <v>2790</v>
+        <v>2788</v>
       </c>
       <c r="C692" t="s">
-        <v>2791</v>
+        <v>2789</v>
       </c>
       <c r="D692">
         <v>35.370621</v>
@@ -29004,7 +29443,7 @@
         <v>1995</v>
       </c>
       <c r="G692" t="s">
-        <v>2792</v>
+        <v>3610</v>
       </c>
       <c r="H692" t="s">
         <v>23</v>
@@ -29012,13 +29451,13 @@
     </row>
     <row r="693" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A693" t="s">
-        <v>3017</v>
+        <v>3010</v>
       </c>
       <c r="B693" t="s">
-        <v>2793</v>
+        <v>2790</v>
       </c>
       <c r="C693" t="s">
-        <v>2794</v>
+        <v>2791</v>
       </c>
       <c r="D693">
         <v>35.443375000000003</v>
@@ -29030,7 +29469,7 @@
         <v>2042</v>
       </c>
       <c r="G693" t="s">
-        <v>2697</v>
+        <v>3610</v>
       </c>
       <c r="H693" t="s">
         <v>90</v>
@@ -29038,13 +29477,13 @@
     </row>
     <row r="694" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A694" t="s">
-        <v>3018</v>
+        <v>3011</v>
       </c>
       <c r="B694" t="s">
-        <v>2795</v>
+        <v>2792</v>
       </c>
       <c r="C694" t="s">
-        <v>2796</v>
+        <v>2793</v>
       </c>
       <c r="D694">
         <v>35.442242</v>
@@ -29053,10 +29492,10 @@
         <v>139.36608899999999</v>
       </c>
       <c r="F694" t="s">
-        <v>2797</v>
+        <v>2794</v>
       </c>
       <c r="G694" t="s">
-        <v>2697</v>
+        <v>3610</v>
       </c>
       <c r="H694" t="s">
         <v>23</v>
@@ -29064,13 +29503,13 @@
     </row>
     <row r="695" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A695" t="s">
-        <v>3019</v>
+        <v>3012</v>
       </c>
       <c r="B695" t="s">
-        <v>2798</v>
+        <v>2795</v>
       </c>
       <c r="C695" t="s">
-        <v>2799</v>
+        <v>2796</v>
       </c>
       <c r="D695">
         <v>35.495289</v>
@@ -29079,10 +29518,10 @@
         <v>139.34979200000001</v>
       </c>
       <c r="F695" t="s">
-        <v>2800</v>
+        <v>2797</v>
       </c>
       <c r="G695" t="s">
-        <v>2697</v>
+        <v>3611</v>
       </c>
       <c r="H695" t="s">
         <v>17</v>
@@ -29090,13 +29529,13 @@
     </row>
     <row r="696" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A696" t="s">
-        <v>3020</v>
+        <v>3013</v>
       </c>
       <c r="B696" t="s">
-        <v>2801</v>
+        <v>2798</v>
       </c>
       <c r="C696" t="s">
-        <v>2802</v>
+        <v>2799</v>
       </c>
       <c r="D696">
         <v>35.469676999999997</v>
@@ -29105,10 +29544,10 @@
         <v>139.465881</v>
       </c>
       <c r="F696" t="s">
-        <v>2803</v>
+        <v>2800</v>
       </c>
       <c r="G696" t="s">
-        <v>2697</v>
+        <v>3612</v>
       </c>
       <c r="H696" t="s">
         <v>17</v>
@@ -29116,13 +29555,13 @@
     </row>
     <row r="697" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A697" t="s">
-        <v>3021</v>
+        <v>3014</v>
       </c>
       <c r="B697" t="s">
-        <v>2804</v>
+        <v>2801</v>
       </c>
       <c r="C697" t="s">
-        <v>2805</v>
+        <v>2802</v>
       </c>
       <c r="D697">
         <v>35.386676999999999</v>
@@ -29131,10 +29570,10 @@
         <v>139.29567</v>
       </c>
       <c r="F697" t="s">
-        <v>2806</v>
+        <v>2803</v>
       </c>
       <c r="G697" t="s">
-        <v>2697</v>
+        <v>3613</v>
       </c>
       <c r="H697" t="s">
         <v>90</v>
@@ -29142,13 +29581,13 @@
     </row>
     <row r="698" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A698" t="s">
-        <v>3036</v>
+        <v>3029</v>
       </c>
       <c r="B698" t="s">
-        <v>2807</v>
+        <v>2804</v>
       </c>
       <c r="C698" t="s">
-        <v>2808</v>
+        <v>2805</v>
       </c>
       <c r="D698">
         <v>40.539906000000002</v>
@@ -29157,10 +29596,10 @@
         <v>141.47056599999999</v>
       </c>
       <c r="F698" t="s">
-        <v>2809</v>
+        <v>2806</v>
       </c>
       <c r="G698" t="s">
-        <v>2697</v>
+        <v>3614</v>
       </c>
       <c r="H698" t="s">
         <v>97</v>
@@ -29168,13 +29607,13 @@
     </row>
     <row r="699" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A699" t="s">
-        <v>3022</v>
+        <v>3015</v>
       </c>
       <c r="B699" t="s">
-        <v>2810</v>
+        <v>2807</v>
       </c>
       <c r="C699" t="s">
-        <v>2811</v>
+        <v>2808</v>
       </c>
       <c r="D699">
         <v>35.454101999999999</v>
@@ -29183,10 +29622,10 @@
         <v>139.397491</v>
       </c>
       <c r="F699" t="s">
-        <v>2812</v>
+        <v>2809</v>
       </c>
       <c r="G699" t="s">
-        <v>2697</v>
+        <v>3615</v>
       </c>
       <c r="H699" t="s">
         <v>45</v>
@@ -29194,13 +29633,13 @@
     </row>
     <row r="700" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A700" t="s">
-        <v>3023</v>
+        <v>3016</v>
       </c>
       <c r="B700" t="s">
-        <v>2813</v>
+        <v>2810</v>
       </c>
       <c r="C700" t="s">
-        <v>2814</v>
+        <v>2811</v>
       </c>
       <c r="D700">
         <v>35.480423000000002</v>
@@ -29209,10 +29648,10 @@
         <v>139.400665</v>
       </c>
       <c r="F700" t="s">
-        <v>2815</v>
+        <v>2812</v>
       </c>
       <c r="G700" t="s">
-        <v>2697</v>
+        <v>3616</v>
       </c>
       <c r="H700" t="s">
         <v>147</v>
@@ -29220,13 +29659,13 @@
     </row>
     <row r="701" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A701" t="s">
-        <v>3024</v>
+        <v>3017</v>
       </c>
       <c r="B701" t="s">
-        <v>2816</v>
+        <v>2813</v>
       </c>
       <c r="C701" t="s">
-        <v>2817</v>
+        <v>2814</v>
       </c>
       <c r="D701">
         <v>35.437640999999999</v>
@@ -29235,10 +29674,10 @@
         <v>139.41989100000001</v>
       </c>
       <c r="F701" t="s">
-        <v>2818</v>
+        <v>2815</v>
       </c>
       <c r="G701" t="s">
-        <v>2697</v>
+        <v>3616</v>
       </c>
       <c r="H701" t="s">
         <v>23</v>
@@ -29246,13 +29685,13 @@
     </row>
     <row r="702" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A702" t="s">
-        <v>3025</v>
+        <v>3018</v>
       </c>
       <c r="B702" t="s">
-        <v>2819</v>
+        <v>2816</v>
       </c>
       <c r="C702" t="s">
-        <v>2820</v>
+        <v>2817</v>
       </c>
       <c r="D702">
         <v>35.436909</v>
@@ -29261,10 +29700,10 @@
         <v>139.42659</v>
       </c>
       <c r="F702" t="s">
-        <v>2821</v>
+        <v>2818</v>
       </c>
       <c r="G702" t="s">
-        <v>2697</v>
+        <v>3617</v>
       </c>
       <c r="H702" t="s">
         <v>147</v>
@@ -29272,13 +29711,13 @@
     </row>
     <row r="703" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A703" t="s">
-        <v>3026</v>
+        <v>3019</v>
       </c>
       <c r="B703" t="s">
-        <v>2822</v>
+        <v>2819</v>
       </c>
       <c r="C703" t="s">
-        <v>2823</v>
+        <v>2820</v>
       </c>
       <c r="D703">
         <v>35.272488000000003</v>
@@ -29287,10 +29726,10 @@
         <v>139.588852</v>
       </c>
       <c r="F703" t="s">
-        <v>2824</v>
+        <v>2821</v>
       </c>
       <c r="G703" t="s">
-        <v>2697</v>
+        <v>3617</v>
       </c>
       <c r="H703" t="s">
         <v>90</v>
@@ -29298,13 +29737,13 @@
     </row>
     <row r="704" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A704" t="s">
-        <v>3037</v>
+        <v>3030</v>
       </c>
       <c r="B704" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
       <c r="C704" t="s">
-        <v>2826</v>
+        <v>2823</v>
       </c>
       <c r="D704">
         <v>35.262512000000001</v>
@@ -29313,10 +29752,10 @@
         <v>139.57759100000001</v>
       </c>
       <c r="F704" t="s">
-        <v>2824</v>
+        <v>2821</v>
       </c>
       <c r="G704" t="s">
-        <v>2697</v>
+        <v>3617</v>
       </c>
       <c r="H704" t="s">
         <v>97</v>
@@ -29324,13 +29763,13 @@
     </row>
     <row r="705" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A705" t="s">
-        <v>3027</v>
+        <v>3020</v>
       </c>
       <c r="B705" t="s">
-        <v>2827</v>
+        <v>2824</v>
       </c>
       <c r="C705" t="s">
-        <v>2828</v>
+        <v>2825</v>
       </c>
       <c r="D705">
         <v>35.286968000000002</v>
@@ -29339,10 +29778,10 @@
         <v>139.59394800000001</v>
       </c>
       <c r="F705" t="s">
-        <v>2829</v>
+        <v>2826</v>
       </c>
       <c r="G705" t="s">
-        <v>2697</v>
+        <v>3618</v>
       </c>
       <c r="H705" t="s">
         <v>147</v>
@@ -29350,13 +29789,13 @@
     </row>
     <row r="706" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A706" t="s">
-        <v>3028</v>
+        <v>3021</v>
       </c>
       <c r="B706" t="s">
-        <v>2830</v>
+        <v>2827</v>
       </c>
       <c r="C706" t="s">
-        <v>2831</v>
+        <v>2828</v>
       </c>
       <c r="D706">
         <v>35.285164000000002</v>
@@ -29365,10 +29804,10 @@
         <v>139.60153199999999</v>
       </c>
       <c r="F706" t="s">
-        <v>2832</v>
+        <v>2829</v>
       </c>
       <c r="G706" t="s">
-        <v>2697</v>
+        <v>3619</v>
       </c>
       <c r="H706" t="s">
         <v>147</v>
@@ -29376,13 +29815,13 @@
     </row>
     <row r="707" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A707" t="s">
-        <v>3029</v>
+        <v>3022</v>
       </c>
       <c r="B707" t="s">
-        <v>2833</v>
+        <v>2830</v>
       </c>
       <c r="C707" t="s">
-        <v>2834</v>
+        <v>2831</v>
       </c>
       <c r="D707">
         <v>35.330719000000002</v>
@@ -29391,10 +29830,10 @@
         <v>139.218842</v>
       </c>
       <c r="F707" t="s">
-        <v>2835</v>
+        <v>2832</v>
       </c>
       <c r="G707" t="s">
-        <v>2697</v>
+        <v>3619</v>
       </c>
       <c r="H707" t="s">
         <v>70</v>
@@ -29402,13 +29841,13 @@
     </row>
     <row r="708" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A708" t="s">
-        <v>3038</v>
+        <v>3031</v>
       </c>
       <c r="B708" t="s">
-        <v>2836</v>
+        <v>2833</v>
       </c>
       <c r="C708" t="s">
-        <v>2837</v>
+        <v>2834</v>
       </c>
       <c r="D708">
         <v>35.330719000000002</v>
@@ -29417,10 +29856,10 @@
         <v>139.218842</v>
       </c>
       <c r="F708" t="s">
-        <v>2835</v>
+        <v>2832</v>
       </c>
       <c r="G708" t="s">
-        <v>2697</v>
+        <v>3620</v>
       </c>
       <c r="H708" t="s">
         <v>72</v>
@@ -29428,13 +29867,13 @@
     </row>
     <row r="709" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A709" t="s">
-        <v>3039</v>
+        <v>3032</v>
       </c>
       <c r="B709" t="s">
-        <v>2838</v>
+        <v>2835</v>
       </c>
       <c r="C709" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
       <c r="D709">
         <v>35.326065</v>
@@ -29446,7 +29885,7 @@
         <v>2020</v>
       </c>
       <c r="G709" t="s">
-        <v>2697</v>
+        <v>3620</v>
       </c>
       <c r="H709" t="s">
         <v>90</v>
@@ -29454,13 +29893,13 @@
     </row>
     <row r="710" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A710" t="s">
-        <v>3039</v>
+        <v>3032</v>
       </c>
       <c r="B710" t="s">
-        <v>2840</v>
+        <v>2837</v>
       </c>
       <c r="C710" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
       <c r="D710">
         <v>35.326065</v>
@@ -29472,7 +29911,7 @@
         <v>2020</v>
       </c>
       <c r="G710" t="s">
-        <v>2697</v>
+        <v>3621</v>
       </c>
       <c r="H710" t="s">
         <v>97</v>
@@ -29480,13 +29919,13 @@
     </row>
     <row r="711" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A711" t="s">
-        <v>3040</v>
+        <v>3033</v>
       </c>
       <c r="B711" t="s">
-        <v>2841</v>
+        <v>2838</v>
       </c>
       <c r="C711" t="s">
-        <v>2842</v>
+        <v>2839</v>
       </c>
       <c r="D711">
         <v>35.360813</v>
@@ -29495,10 +29934,10 @@
         <v>139.081039</v>
       </c>
       <c r="F711" t="s">
-        <v>2843</v>
+        <v>2840</v>
       </c>
       <c r="G711" t="s">
-        <v>2697</v>
+        <v>3622</v>
       </c>
       <c r="H711" t="s">
         <v>23</v>
@@ -29506,13 +29945,13 @@
     </row>
     <row r="712" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A712" t="s">
-        <v>3041</v>
+        <v>3034</v>
       </c>
       <c r="B712" t="s">
-        <v>2844</v>
+        <v>2841</v>
       </c>
       <c r="C712" t="s">
-        <v>2845</v>
+        <v>2842</v>
       </c>
       <c r="D712">
         <v>35.529007</v>
@@ -29524,7 +29963,7 @@
         <v>267</v>
       </c>
       <c r="G712" t="s">
-        <v>2846</v>
+        <v>3622</v>
       </c>
       <c r="H712" t="s">
         <v>70</v>
@@ -29532,13 +29971,13 @@
     </row>
     <row r="713" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A713" t="s">
-        <v>3041</v>
+        <v>3034</v>
       </c>
       <c r="B713" t="s">
-        <v>2847</v>
+        <v>2843</v>
       </c>
       <c r="C713" t="s">
-        <v>2848</v>
+        <v>2844</v>
       </c>
       <c r="D713">
         <v>35.529007</v>
@@ -29550,7 +29989,7 @@
         <v>822</v>
       </c>
       <c r="G713" t="s">
-        <v>2846</v>
+        <v>3623</v>
       </c>
       <c r="H713" t="s">
         <v>72</v>
@@ -29558,13 +29997,13 @@
     </row>
     <row r="714" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A714" t="s">
-        <v>3042</v>
+        <v>3035</v>
       </c>
       <c r="B714" t="s">
-        <v>2849</v>
+        <v>2845</v>
       </c>
       <c r="C714" t="s">
-        <v>2850</v>
+        <v>2846</v>
       </c>
       <c r="D714">
         <v>35.484276000000001</v>
@@ -29576,7 +30015,7 @@
         <v>288</v>
       </c>
       <c r="G714" t="s">
-        <v>2697</v>
+        <v>3623</v>
       </c>
       <c r="H714" t="s">
         <v>70</v>
@@ -29584,13 +30023,13 @@
     </row>
     <row r="715" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A715" t="s">
-        <v>3042</v>
+        <v>3035</v>
       </c>
       <c r="B715" t="s">
-        <v>2851</v>
+        <v>2847</v>
       </c>
       <c r="C715" t="s">
-        <v>2850</v>
+        <v>2846</v>
       </c>
       <c r="D715">
         <v>35.484276000000001</v>
@@ -29602,7 +30041,7 @@
         <v>288</v>
       </c>
       <c r="G715" t="s">
-        <v>2697</v>
+        <v>3624</v>
       </c>
       <c r="H715" t="s">
         <v>72</v>
@@ -29610,13 +30049,13 @@
     </row>
     <row r="716" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A716" t="s">
-        <v>3043</v>
+        <v>3036</v>
       </c>
       <c r="B716" t="s">
-        <v>2852</v>
+        <v>2848</v>
       </c>
       <c r="C716" t="s">
-        <v>2853</v>
+        <v>2849</v>
       </c>
       <c r="D716">
         <v>37.950588000000003</v>
@@ -29625,10 +30064,10 @@
         <v>139.12301600000001</v>
       </c>
       <c r="F716" t="s">
-        <v>2854</v>
+        <v>2850</v>
       </c>
       <c r="G716" t="s">
-        <v>2855</v>
+        <v>3625</v>
       </c>
       <c r="H716" t="s">
         <v>23</v>
@@ -29636,13 +30075,13 @@
     </row>
     <row r="717" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A717" t="s">
-        <v>2860</v>
+        <v>2854</v>
       </c>
       <c r="B717" t="s">
-        <v>2856</v>
+        <v>2851</v>
       </c>
       <c r="C717" t="s">
-        <v>2857</v>
+        <v>2852</v>
       </c>
       <c r="D717">
         <v>37.922381999999999</v>
@@ -29651,10 +30090,10 @@
         <v>139.04513499999999</v>
       </c>
       <c r="F717" t="s">
-        <v>2858</v>
+        <v>2853</v>
       </c>
       <c r="G717" t="s">
-        <v>2859</v>
+        <v>3625</v>
       </c>
       <c r="H717" t="s">
         <v>23</v>
@@ -29662,13 +30101,13 @@
     </row>
     <row r="718" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A718" t="s">
-        <v>3044</v>
+        <v>3037</v>
       </c>
       <c r="B718" t="s">
-        <v>2861</v>
+        <v>2855</v>
       </c>
       <c r="C718" t="s">
-        <v>2862</v>
+        <v>2856</v>
       </c>
       <c r="D718">
         <v>37.802371999999998</v>
@@ -29677,10 +30116,10 @@
         <v>139.141739</v>
       </c>
       <c r="F718" t="s">
-        <v>2863</v>
+        <v>2857</v>
       </c>
       <c r="G718" t="s">
-        <v>2864</v>
+        <v>3626</v>
       </c>
       <c r="H718" t="s">
         <v>959</v>
@@ -29688,13 +30127,13 @@
     </row>
     <row r="719" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A719" t="s">
-        <v>3045</v>
+        <v>3038</v>
       </c>
       <c r="B719" t="s">
-        <v>2865</v>
+        <v>2858</v>
       </c>
       <c r="C719" t="s">
-        <v>2866</v>
+        <v>2859</v>
       </c>
       <c r="D719">
         <v>37.446818999999998</v>
@@ -29703,10 +30142,10 @@
         <v>138.85137900000001</v>
       </c>
       <c r="F719" t="s">
-        <v>2867</v>
+        <v>2860</v>
       </c>
       <c r="G719" t="s">
-        <v>2697</v>
+        <v>3626</v>
       </c>
       <c r="H719" t="s">
         <v>23</v>
@@ -29714,13 +30153,13 @@
     </row>
     <row r="720" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A720" t="s">
-        <v>3046</v>
+        <v>3039</v>
       </c>
       <c r="B720" t="s">
-        <v>2868</v>
+        <v>2861</v>
       </c>
       <c r="C720" t="s">
-        <v>2869</v>
+        <v>2862</v>
       </c>
       <c r="D720">
         <v>37.451694000000003</v>
@@ -29729,10 +30168,10 @@
         <v>138.80682400000001</v>
       </c>
       <c r="F720" t="s">
-        <v>2870</v>
+        <v>2863</v>
       </c>
       <c r="G720" t="s">
-        <v>2697</v>
+        <v>3626</v>
       </c>
       <c r="H720" t="s">
         <v>23</v>
@@ -29740,13 +30179,13 @@
     </row>
     <row r="721" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A721" t="s">
-        <v>3047</v>
+        <v>3040</v>
       </c>
       <c r="B721" t="s">
-        <v>2871</v>
+        <v>2864</v>
       </c>
       <c r="C721" t="s">
-        <v>2872</v>
+        <v>2865</v>
       </c>
       <c r="D721">
         <v>37.44849</v>
@@ -29755,10 +30194,10 @@
         <v>138.848648</v>
       </c>
       <c r="F721" t="s">
-        <v>2873</v>
+        <v>2866</v>
       </c>
       <c r="G721" t="s">
-        <v>2697</v>
+        <v>3626</v>
       </c>
       <c r="H721" t="s">
         <v>45</v>
@@ -29766,13 +30205,13 @@
     </row>
     <row r="722" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A722" t="s">
-        <v>3048</v>
+        <v>3041</v>
       </c>
       <c r="B722" t="s">
-        <v>2874</v>
+        <v>2867</v>
       </c>
       <c r="C722" t="s">
-        <v>2875</v>
+        <v>2868</v>
       </c>
       <c r="D722">
         <v>37.261681000000003</v>
@@ -29781,10 +30220,10 @@
         <v>138.86717200000001</v>
       </c>
       <c r="F722" t="s">
-        <v>2876</v>
+        <v>2869</v>
       </c>
       <c r="G722" t="s">
-        <v>2697</v>
+        <v>3626</v>
       </c>
       <c r="H722" t="s">
         <v>968</v>
@@ -29792,13 +30231,13 @@
     </row>
     <row r="723" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A723" t="s">
-        <v>3049</v>
+        <v>3042</v>
       </c>
       <c r="B723" t="s">
-        <v>2877</v>
+        <v>2870</v>
       </c>
       <c r="C723" t="s">
-        <v>2878</v>
+        <v>2871</v>
       </c>
       <c r="D723">
         <v>37.459778</v>
@@ -29807,10 +30246,10 @@
         <v>139.007431</v>
       </c>
       <c r="F723" t="s">
-        <v>2879</v>
+        <v>2872</v>
       </c>
       <c r="G723" t="s">
-        <v>2697</v>
+        <v>3626</v>
       </c>
       <c r="H723" t="s">
         <v>23</v>
@@ -29818,13 +30257,13 @@
     </row>
     <row r="724" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A724" t="s">
-        <v>3050</v>
+        <v>3043</v>
       </c>
       <c r="B724" t="s">
-        <v>2880</v>
+        <v>2873</v>
       </c>
       <c r="C724" t="s">
-        <v>2881</v>
+        <v>2874</v>
       </c>
       <c r="D724">
         <v>37.44849</v>
@@ -29833,10 +30272,10 @@
         <v>138.848648</v>
       </c>
       <c r="F724" t="s">
-        <v>2882</v>
+        <v>2875</v>
       </c>
       <c r="G724" t="s">
-        <v>2697</v>
+        <v>3626</v>
       </c>
       <c r="H724" t="s">
         <v>23</v>
@@ -29844,13 +30283,13 @@
     </row>
     <row r="725" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A725" t="s">
-        <v>3051</v>
+        <v>3044</v>
       </c>
       <c r="B725" t="s">
-        <v>2880</v>
+        <v>2873</v>
       </c>
       <c r="C725" t="s">
-        <v>2881</v>
+        <v>2874</v>
       </c>
       <c r="D725">
         <v>37.44849</v>
@@ -29859,10 +30298,10 @@
         <v>138.848648</v>
       </c>
       <c r="F725" t="s">
-        <v>2883</v>
+        <v>2876</v>
       </c>
       <c r="G725" t="s">
-        <v>2697</v>
+        <v>3627</v>
       </c>
       <c r="H725" t="s">
         <v>23</v>
@@ -29870,13 +30309,13 @@
     </row>
     <row r="726" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A726" t="s">
-        <v>3052</v>
+        <v>3045</v>
       </c>
       <c r="B726" t="s">
-        <v>2884</v>
+        <v>2877</v>
       </c>
       <c r="C726" t="s">
-        <v>2885</v>
+        <v>2878</v>
       </c>
       <c r="D726">
         <v>37.633040999999999</v>
@@ -29885,10 +30324,10 @@
         <v>138.953857</v>
       </c>
       <c r="F726" t="s">
-        <v>2886</v>
+        <v>2879</v>
       </c>
       <c r="G726" t="s">
-        <v>2697</v>
+        <v>3627</v>
       </c>
       <c r="H726" t="s">
         <v>17</v>
@@ -29896,13 +30335,13 @@
     </row>
     <row r="727" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A727" t="s">
-        <v>3053</v>
+        <v>3046</v>
       </c>
       <c r="B727" t="s">
-        <v>2887</v>
+        <v>2880</v>
       </c>
       <c r="C727" t="s">
-        <v>2888</v>
+        <v>2881</v>
       </c>
       <c r="D727">
         <v>37.657519999999998</v>
@@ -29911,10 +30350,10 @@
         <v>138.97358700000001</v>
       </c>
       <c r="F727" t="s">
-        <v>2889</v>
+        <v>2882</v>
       </c>
       <c r="G727" t="s">
-        <v>2697</v>
+        <v>3627</v>
       </c>
       <c r="H727" t="s">
         <v>23</v>
@@ -29922,13 +30361,13 @@
     </row>
     <row r="728" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A728" t="s">
-        <v>3054</v>
+        <v>3047</v>
       </c>
       <c r="B728" t="s">
-        <v>2890</v>
+        <v>2883</v>
       </c>
       <c r="C728" t="s">
-        <v>2891</v>
+        <v>2884</v>
       </c>
       <c r="D728">
         <v>37.630909000000003</v>
@@ -29937,10 +30376,10 @@
         <v>138.95387299999999</v>
       </c>
       <c r="F728" t="s">
-        <v>2892</v>
+        <v>2885</v>
       </c>
       <c r="G728" t="s">
-        <v>2697</v>
+        <v>3628</v>
       </c>
       <c r="H728" t="s">
         <v>23</v>
@@ -29948,13 +30387,13 @@
     </row>
     <row r="729" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A729" t="s">
-        <v>3055</v>
+        <v>3048</v>
       </c>
       <c r="B729" t="s">
-        <v>2893</v>
+        <v>2886</v>
       </c>
       <c r="C729" t="s">
-        <v>2894</v>
+        <v>2887</v>
       </c>
       <c r="D729">
         <v>37.367213999999997</v>
@@ -29963,10 +30402,10 @@
         <v>138.54660000000001</v>
       </c>
       <c r="F729" t="s">
-        <v>2895</v>
+        <v>2888</v>
       </c>
       <c r="G729" t="s">
-        <v>2697</v>
+        <v>3628</v>
       </c>
       <c r="H729" t="s">
         <v>959</v>
@@ -29974,13 +30413,13 @@
     </row>
     <row r="730" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A730" t="s">
-        <v>3056</v>
+        <v>3049</v>
       </c>
       <c r="B730" t="s">
-        <v>2896</v>
+        <v>2889</v>
       </c>
       <c r="C730" t="s">
-        <v>2897</v>
+        <v>2890</v>
       </c>
       <c r="D730">
         <v>37.372421000000003</v>
@@ -29989,10 +30428,10 @@
         <v>138.55276499999999</v>
       </c>
       <c r="F730" t="s">
-        <v>2898</v>
+        <v>2891</v>
       </c>
       <c r="G730" t="s">
-        <v>2697</v>
+        <v>3629</v>
       </c>
       <c r="H730" t="s">
         <v>959</v>
@@ -30000,13 +30439,13 @@
     </row>
     <row r="731" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A731" t="s">
-        <v>3057</v>
+        <v>3050</v>
       </c>
       <c r="B731" t="s">
-        <v>2899</v>
+        <v>2892</v>
       </c>
       <c r="C731" t="s">
-        <v>2900</v>
+        <v>2893</v>
       </c>
       <c r="D731">
         <v>37.944583999999999</v>
@@ -30015,10 +30454,10 @@
         <v>139.33389299999999</v>
       </c>
       <c r="F731" t="s">
-        <v>2781</v>
+        <v>2779</v>
       </c>
       <c r="G731" t="s">
-        <v>2697</v>
+        <v>3629</v>
       </c>
       <c r="H731" t="s">
         <v>23</v>
@@ -30026,13 +30465,13 @@
     </row>
     <row r="732" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A732" t="s">
-        <v>3058</v>
+        <v>3051</v>
       </c>
       <c r="B732" t="s">
-        <v>2901</v>
+        <v>2894</v>
       </c>
       <c r="C732" t="s">
-        <v>2902</v>
+        <v>2895</v>
       </c>
       <c r="D732">
         <v>37.945765999999999</v>
@@ -30041,10 +30480,10 @@
         <v>139.32925399999999</v>
       </c>
       <c r="F732" t="s">
-        <v>2903</v>
+        <v>2896</v>
       </c>
       <c r="G732" t="s">
-        <v>2697</v>
+        <v>3629</v>
       </c>
       <c r="H732" t="s">
         <v>23</v>
@@ -30052,13 +30491,13 @@
     </row>
     <row r="733" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A733" t="s">
-        <v>3059</v>
+        <v>3052</v>
       </c>
       <c r="B733" t="s">
-        <v>2904</v>
+        <v>2897</v>
       </c>
       <c r="C733" t="s">
-        <v>2905</v>
+        <v>2898</v>
       </c>
       <c r="D733">
         <v>37.879471000000002</v>
@@ -30067,10 +30506,10 @@
         <v>139.308807</v>
       </c>
       <c r="F733" t="s">
-        <v>2906</v>
+        <v>2899</v>
       </c>
       <c r="G733" t="s">
-        <v>2697</v>
+        <v>3630</v>
       </c>
       <c r="H733" t="s">
         <v>23</v>
@@ -30078,13 +30517,13 @@
     </row>
     <row r="734" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A734" t="s">
-        <v>3060</v>
+        <v>3053</v>
       </c>
       <c r="B734" t="s">
-        <v>2907</v>
+        <v>2900</v>
       </c>
       <c r="C734" t="s">
-        <v>2908</v>
+        <v>2901</v>
       </c>
       <c r="D734">
         <v>37.944125999999997</v>
@@ -30093,10 +30532,10 @@
         <v>139.331558</v>
       </c>
       <c r="F734" t="s">
-        <v>2909</v>
+        <v>2902</v>
       </c>
       <c r="G734" t="s">
-        <v>2697</v>
+        <v>3630</v>
       </c>
       <c r="H734" t="s">
         <v>23</v>
@@ -30104,13 +30543,13 @@
     </row>
     <row r="735" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A735" t="s">
-        <v>3061</v>
+        <v>3054</v>
       </c>
       <c r="B735" t="s">
-        <v>2910</v>
+        <v>2903</v>
       </c>
       <c r="C735" t="s">
-        <v>2911</v>
+        <v>2904</v>
       </c>
       <c r="D735">
         <v>37.311385999999999</v>
@@ -30122,7 +30561,7 @@
         <v>1995</v>
       </c>
       <c r="G735" t="s">
-        <v>2697</v>
+        <v>3630</v>
       </c>
       <c r="H735" t="s">
         <v>23</v>
@@ -30130,13 +30569,13 @@
     </row>
     <row r="736" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A736" t="s">
-        <v>3062</v>
+        <v>3055</v>
       </c>
       <c r="B736" t="s">
-        <v>2912</v>
+        <v>2905</v>
       </c>
       <c r="C736" t="s">
-        <v>2913</v>
+        <v>2906</v>
       </c>
       <c r="D736">
         <v>37.310958999999997</v>
@@ -30145,10 +30584,10 @@
         <v>138.79669200000001</v>
       </c>
       <c r="F736" t="s">
-        <v>2914</v>
+        <v>2907</v>
       </c>
       <c r="G736" t="s">
-        <v>2697</v>
+        <v>3631</v>
       </c>
       <c r="H736" t="s">
         <v>23</v>
@@ -30156,13 +30595,13 @@
     </row>
     <row r="737" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A737" t="s">
-        <v>3063</v>
+        <v>3056</v>
       </c>
       <c r="B737" t="s">
-        <v>2915</v>
+        <v>2908</v>
       </c>
       <c r="C737" t="s">
-        <v>2916</v>
+        <v>2909</v>
       </c>
       <c r="D737">
         <v>37.583412000000003</v>
@@ -30171,10 +30610,10 @@
         <v>139.16561899999999</v>
       </c>
       <c r="F737" t="s">
-        <v>2917</v>
+        <v>2910</v>
       </c>
       <c r="G737" t="s">
-        <v>2697</v>
+        <v>3632</v>
       </c>
       <c r="H737" t="s">
         <v>45</v>
@@ -30182,13 +30621,13 @@
     </row>
     <row r="738" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A738" t="s">
-        <v>3064</v>
+        <v>3057</v>
       </c>
       <c r="B738" t="s">
-        <v>2918</v>
+        <v>2911</v>
       </c>
       <c r="C738" t="s">
-        <v>2919</v>
+        <v>2912</v>
       </c>
       <c r="D738">
         <v>37.133778</v>
@@ -30200,7 +30639,7 @@
         <v>1995</v>
       </c>
       <c r="G738" t="s">
-        <v>2697</v>
+        <v>3632</v>
       </c>
       <c r="H738" t="s">
         <v>23</v>
@@ -30208,13 +30647,13 @@
     </row>
     <row r="739" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A739" t="s">
-        <v>3065</v>
+        <v>3058</v>
       </c>
       <c r="B739" t="s">
-        <v>2920</v>
+        <v>2913</v>
       </c>
       <c r="C739" t="s">
-        <v>2921</v>
+        <v>2914</v>
       </c>
       <c r="D739">
         <v>37.069274999999998</v>
@@ -30223,10 +30662,10 @@
         <v>138.690979</v>
       </c>
       <c r="F739" t="s">
-        <v>2922</v>
+        <v>2915</v>
       </c>
       <c r="G739" t="s">
-        <v>2697</v>
+        <v>3632</v>
       </c>
       <c r="H739" t="s">
         <v>45</v>
@@ -30234,13 +30673,13 @@
     </row>
     <row r="740" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A740" t="s">
-        <v>3066</v>
+        <v>3059</v>
       </c>
       <c r="B740" t="s">
-        <v>2923</v>
+        <v>2916</v>
       </c>
       <c r="C740" t="s">
-        <v>2924</v>
+        <v>2917</v>
       </c>
       <c r="D740">
         <v>37.140957</v>
@@ -30249,10 +30688,10 @@
         <v>138.75588999999999</v>
       </c>
       <c r="F740" t="s">
-        <v>2925</v>
+        <v>2918</v>
       </c>
       <c r="G740" t="s">
-        <v>2697</v>
+        <v>3633</v>
       </c>
       <c r="H740" t="s">
         <v>17</v>
@@ -30260,13 +30699,13 @@
     </row>
     <row r="741" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A741" t="s">
-        <v>3067</v>
+        <v>3060</v>
       </c>
       <c r="B741" t="s">
-        <v>2926</v>
+        <v>2919</v>
       </c>
       <c r="C741" t="s">
-        <v>2927</v>
+        <v>2920</v>
       </c>
       <c r="D741">
         <v>37.531471000000003</v>
@@ -30275,10 +30714,10 @@
         <v>138.914658</v>
       </c>
       <c r="F741" t="s">
-        <v>2928</v>
+        <v>2921</v>
       </c>
       <c r="G741" t="s">
-        <v>2697</v>
+        <v>3634</v>
       </c>
       <c r="H741" t="s">
         <v>23</v>
@@ -30286,13 +30725,13 @@
     </row>
     <row r="742" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A742" t="s">
-        <v>3068</v>
+        <v>3061</v>
       </c>
       <c r="B742" t="s">
-        <v>2929</v>
+        <v>2922</v>
       </c>
       <c r="C742" t="s">
-        <v>2930</v>
+        <v>2923</v>
       </c>
       <c r="D742">
         <v>38.225628</v>
@@ -30301,10 +30740,10 @@
         <v>139.48075900000001</v>
       </c>
       <c r="F742" t="s">
-        <v>2931</v>
+        <v>2924</v>
       </c>
       <c r="G742" t="s">
-        <v>2697</v>
+        <v>3634</v>
       </c>
       <c r="H742" t="s">
         <v>23</v>
@@ -30312,13 +30751,13 @@
     </row>
     <row r="743" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A743" t="s">
-        <v>3069</v>
+        <v>3062</v>
       </c>
       <c r="B743" t="s">
-        <v>2932</v>
+        <v>2925</v>
       </c>
       <c r="C743" t="s">
-        <v>2933</v>
+        <v>2926</v>
       </c>
       <c r="D743">
         <v>38.372920999999998</v>
@@ -30327,10 +30766,10 @@
         <v>139.45756499999999</v>
       </c>
       <c r="F743" t="s">
-        <v>2934</v>
+        <v>2927</v>
       </c>
       <c r="G743" t="s">
-        <v>2697</v>
+        <v>3634</v>
       </c>
       <c r="H743" t="s">
         <v>23</v>
@@ -30338,13 +30777,13 @@
     </row>
     <row r="744" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A744" t="s">
-        <v>3070</v>
+        <v>3063</v>
       </c>
       <c r="B744" t="s">
-        <v>2935</v>
+        <v>2928</v>
       </c>
       <c r="C744" t="s">
-        <v>2936</v>
+        <v>2929</v>
       </c>
       <c r="D744">
         <v>38.125416000000001</v>
@@ -30356,7 +30795,7 @@
         <v>1995</v>
       </c>
       <c r="G744" t="s">
-        <v>2697</v>
+        <v>3634</v>
       </c>
       <c r="H744" t="s">
         <v>23</v>
@@ -30364,13 +30803,13 @@
     </row>
     <row r="745" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A745" t="s">
-        <v>3071</v>
+        <v>3064</v>
       </c>
       <c r="B745" t="s">
-        <v>2937</v>
+        <v>2930</v>
       </c>
       <c r="C745" t="s">
-        <v>2938</v>
+        <v>2931</v>
       </c>
       <c r="D745">
         <v>38.28257</v>
@@ -30379,10 +30818,10 @@
         <v>139.52316300000001</v>
       </c>
       <c r="F745" t="s">
-        <v>2939</v>
+        <v>2932</v>
       </c>
       <c r="G745" t="s">
-        <v>2697</v>
+        <v>3634</v>
       </c>
       <c r="H745" t="s">
         <v>23</v>
@@ -30390,13 +30829,13 @@
     </row>
     <row r="746" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A746" t="s">
-        <v>3072</v>
+        <v>3065</v>
       </c>
       <c r="B746" t="s">
-        <v>2940</v>
+        <v>2933</v>
       </c>
       <c r="C746" t="s">
-        <v>2941</v>
+        <v>2934</v>
       </c>
       <c r="D746">
         <v>38.172798</v>
@@ -30405,10 +30844,10 @@
         <v>139.460556</v>
       </c>
       <c r="F746" t="s">
-        <v>2942</v>
+        <v>2935</v>
       </c>
       <c r="G746" t="s">
-        <v>2697</v>
+        <v>3635</v>
       </c>
       <c r="H746" t="s">
         <v>23</v>
@@ -30416,13 +30855,13 @@
     </row>
     <row r="747" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A747" t="s">
-        <v>3073</v>
+        <v>3066</v>
       </c>
       <c r="B747" t="s">
-        <v>2943</v>
+        <v>2936</v>
       </c>
       <c r="C747" t="s">
-        <v>2944</v>
+        <v>2937</v>
       </c>
       <c r="D747">
         <v>37.630692000000003</v>
@@ -30431,10 +30870,10 @@
         <v>138.843369</v>
       </c>
       <c r="F747" t="s">
-        <v>2945</v>
+        <v>2938</v>
       </c>
       <c r="G747" t="s">
-        <v>2713</v>
+        <v>3635</v>
       </c>
       <c r="H747" t="s">
         <v>17</v>
@@ -30442,13 +30881,13 @@
     </row>
     <row r="748" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A748" t="s">
-        <v>3074</v>
+        <v>3067</v>
       </c>
       <c r="B748" t="s">
-        <v>2946</v>
+        <v>2939</v>
       </c>
       <c r="C748" t="s">
-        <v>2947</v>
+        <v>2940</v>
       </c>
       <c r="D748">
         <v>37.652434999999997</v>
@@ -30457,10 +30896,10 @@
         <v>138.919724</v>
       </c>
       <c r="F748" t="s">
-        <v>2945</v>
+        <v>2938</v>
       </c>
       <c r="G748" t="s">
-        <v>2697</v>
+        <v>3635</v>
       </c>
       <c r="H748" t="s">
         <v>17</v>
@@ -30468,13 +30907,13 @@
     </row>
     <row r="749" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A749" t="s">
-        <v>3075</v>
+        <v>3068</v>
       </c>
       <c r="B749" t="s">
-        <v>2948</v>
+        <v>2941</v>
       </c>
       <c r="C749" t="s">
-        <v>2949</v>
+        <v>2942</v>
       </c>
       <c r="D749">
         <v>37.651608000000003</v>
@@ -30483,10 +30922,10 @@
         <v>138.86930799999999</v>
       </c>
       <c r="F749" t="s">
-        <v>2950</v>
+        <v>2943</v>
       </c>
       <c r="G749" t="s">
-        <v>2697</v>
+        <v>3635</v>
       </c>
       <c r="H749" t="s">
         <v>17</v>
@@ -30494,13 +30933,13 @@
     </row>
     <row r="750" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A750" t="s">
-        <v>3076</v>
+        <v>3069</v>
       </c>
       <c r="B750" t="s">
-        <v>2951</v>
+        <v>2944</v>
       </c>
       <c r="C750" t="s">
-        <v>2952</v>
+        <v>2945</v>
       </c>
       <c r="D750">
         <v>37.66301</v>
@@ -30509,10 +30948,10 @@
         <v>138.82467700000001</v>
       </c>
       <c r="F750" t="s">
-        <v>2953</v>
+        <v>2946</v>
       </c>
       <c r="G750" t="s">
-        <v>2697</v>
+        <v>3635</v>
       </c>
       <c r="H750" t="s">
         <v>45</v>
@@ -30520,13 +30959,13 @@
     </row>
     <row r="751" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A751" t="s">
-        <v>3091</v>
+        <v>3084</v>
       </c>
       <c r="B751" t="s">
-        <v>2954</v>
+        <v>2947</v>
       </c>
       <c r="C751" t="s">
-        <v>2955</v>
+        <v>2948</v>
       </c>
       <c r="D751">
         <v>37.672702999999998</v>
@@ -30535,10 +30974,10 @@
         <v>138.88287399999999</v>
       </c>
       <c r="F751" t="s">
-        <v>2956</v>
+        <v>2949</v>
       </c>
       <c r="G751" t="s">
-        <v>2697</v>
+        <v>3635</v>
       </c>
       <c r="H751" t="s">
         <v>90</v>
@@ -30546,13 +30985,13 @@
     </row>
     <row r="752" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A752" t="s">
-        <v>3091</v>
+        <v>3084</v>
       </c>
       <c r="B752" t="s">
-        <v>2957</v>
+        <v>2950</v>
       </c>
       <c r="C752" t="s">
-        <v>2955</v>
+        <v>2948</v>
       </c>
       <c r="D752">
         <v>37.672702999999998</v>
@@ -30561,10 +31000,10 @@
         <v>138.88287399999999</v>
       </c>
       <c r="F752" t="s">
-        <v>2958</v>
+        <v>2951</v>
       </c>
       <c r="G752" t="s">
-        <v>2697</v>
+        <v>3636</v>
       </c>
       <c r="H752" t="s">
         <v>97</v>
@@ -30572,13 +31011,13 @@
     </row>
     <row r="753" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A753" t="s">
-        <v>3077</v>
+        <v>3070</v>
       </c>
       <c r="B753" t="s">
-        <v>2959</v>
+        <v>2952</v>
       </c>
       <c r="C753" t="s">
-        <v>2960</v>
+        <v>2953</v>
       </c>
       <c r="D753">
         <v>37.04504</v>
@@ -30587,10 +31026,10 @@
         <v>137.85907</v>
       </c>
       <c r="F753" t="s">
-        <v>2961</v>
+        <v>2954</v>
       </c>
       <c r="G753" t="s">
-        <v>2697</v>
+        <v>3637</v>
       </c>
       <c r="H753" t="s">
         <v>23</v>
@@ -30598,13 +31037,13 @@
     </row>
     <row r="754" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A754" t="s">
-        <v>3078</v>
+        <v>3071</v>
       </c>
       <c r="B754" t="s">
-        <v>2962</v>
+        <v>2955</v>
       </c>
       <c r="C754" t="s">
-        <v>2963</v>
+        <v>2956</v>
       </c>
       <c r="D754">
         <v>37.802802999999997</v>
@@ -30613,10 +31052,10 @@
         <v>139.28681900000001</v>
       </c>
       <c r="F754" t="s">
-        <v>2964</v>
+        <v>2957</v>
       </c>
       <c r="G754" t="s">
-        <v>2697</v>
+        <v>3638</v>
       </c>
       <c r="H754" t="s">
         <v>959</v>
@@ -30624,13 +31063,13 @@
     </row>
     <row r="755" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A755" t="s">
-        <v>3079</v>
+        <v>3072</v>
       </c>
       <c r="B755" t="s">
-        <v>2965</v>
+        <v>2958</v>
       </c>
       <c r="C755" t="s">
-        <v>2966</v>
+        <v>2959</v>
       </c>
       <c r="D755">
         <v>38.029784999999997</v>
@@ -30642,7 +31081,7 @@
         <v>1324</v>
       </c>
       <c r="G755" t="s">
-        <v>2697</v>
+        <v>3638</v>
       </c>
       <c r="H755" t="s">
         <v>23</v>
@@ -30650,13 +31089,13 @@
     </row>
     <row r="756" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A756" t="s">
-        <v>3080</v>
+        <v>3073</v>
       </c>
       <c r="B756" t="s">
-        <v>2967</v>
+        <v>2960</v>
       </c>
       <c r="C756" t="s">
-        <v>2968</v>
+        <v>2961</v>
       </c>
       <c r="D756">
         <v>38.017375999999999</v>
@@ -30668,7 +31107,7 @@
         <v>822</v>
       </c>
       <c r="G756" t="s">
-        <v>2697</v>
+        <v>3638</v>
       </c>
       <c r="H756" t="s">
         <v>70</v>
@@ -30676,13 +31115,13 @@
     </row>
     <row r="757" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A757" t="s">
-        <v>3092</v>
+        <v>3085</v>
       </c>
       <c r="B757" t="s">
-        <v>2969</v>
+        <v>2962</v>
       </c>
       <c r="C757" t="s">
-        <v>2968</v>
+        <v>2961</v>
       </c>
       <c r="D757">
         <v>38.017375999999999</v>
@@ -30694,7 +31133,7 @@
         <v>822</v>
       </c>
       <c r="G757" t="s">
-        <v>2697</v>
+        <v>3638</v>
       </c>
       <c r="H757" t="s">
         <v>72</v>
@@ -30702,13 +31141,13 @@
     </row>
     <row r="758" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A758" t="s">
-        <v>3081</v>
+        <v>3074</v>
       </c>
       <c r="B758" t="s">
-        <v>2970</v>
+        <v>2963</v>
       </c>
       <c r="C758" t="s">
-        <v>2971</v>
+        <v>2964</v>
       </c>
       <c r="D758">
         <v>37.819813000000003</v>
@@ -30720,7 +31159,7 @@
         <v>2396</v>
       </c>
       <c r="G758" t="s">
-        <v>2697</v>
+        <v>3638</v>
       </c>
       <c r="H758" t="s">
         <v>23</v>
@@ -30728,13 +31167,13 @@
     </row>
     <row r="759" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A759" t="s">
-        <v>3082</v>
+        <v>3075</v>
       </c>
       <c r="B759" t="s">
-        <v>2972</v>
+        <v>2965</v>
       </c>
       <c r="C759" t="s">
-        <v>2973</v>
+        <v>2966</v>
       </c>
       <c r="D759">
         <v>37.988770000000002</v>
@@ -30746,7 +31185,7 @@
         <v>822</v>
       </c>
       <c r="G759" t="s">
-        <v>2697</v>
+        <v>3638</v>
       </c>
       <c r="H759" t="s">
         <v>45</v>
@@ -30754,13 +31193,13 @@
     </row>
     <row r="760" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A760" t="s">
-        <v>3083</v>
+        <v>3076</v>
       </c>
       <c r="B760" t="s">
-        <v>2974</v>
+        <v>2967</v>
       </c>
       <c r="C760" t="s">
-        <v>2975</v>
+        <v>2968</v>
       </c>
       <c r="D760">
         <v>37.878563</v>
@@ -30772,7 +31211,7 @@
         <v>822</v>
       </c>
       <c r="G760" t="s">
-        <v>2697</v>
+        <v>3638</v>
       </c>
       <c r="H760" t="s">
         <v>45</v>
@@ -30780,13 +31219,13 @@
     </row>
     <row r="761" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A761" t="s">
-        <v>3084</v>
+        <v>3077</v>
       </c>
       <c r="B761" t="s">
-        <v>2976</v>
+        <v>2969</v>
       </c>
       <c r="C761" t="s">
-        <v>2977</v>
+        <v>2970</v>
       </c>
       <c r="D761">
         <v>38.013241000000001</v>
@@ -30798,7 +31237,7 @@
         <v>822</v>
       </c>
       <c r="G761" t="s">
-        <v>2697</v>
+        <v>3638</v>
       </c>
       <c r="H761" t="s">
         <v>45</v>
@@ -30806,13 +31245,13 @@
     </row>
     <row r="762" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A762" t="s">
-        <v>3085</v>
+        <v>3078</v>
       </c>
       <c r="B762" t="s">
-        <v>2978</v>
+        <v>2971</v>
       </c>
       <c r="C762" t="s">
-        <v>2979</v>
+        <v>2972</v>
       </c>
       <c r="D762">
         <v>37.998202999999997</v>
@@ -30824,7 +31263,7 @@
         <v>1324</v>
       </c>
       <c r="G762" t="s">
-        <v>2697</v>
+        <v>3638</v>
       </c>
       <c r="H762" t="s">
         <v>23</v>
@@ -30832,13 +31271,13 @@
     </row>
     <row r="763" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A763" t="s">
-        <v>3086</v>
+        <v>3079</v>
       </c>
       <c r="B763" t="s">
-        <v>2980</v>
+        <v>2973</v>
       </c>
       <c r="C763" t="s">
-        <v>2981</v>
+        <v>2974</v>
       </c>
       <c r="D763">
         <v>38.078834999999998</v>
@@ -30850,7 +31289,7 @@
         <v>628</v>
       </c>
       <c r="G763" t="s">
-        <v>2697</v>
+        <v>3638</v>
       </c>
       <c r="H763" t="s">
         <v>45</v>
@@ -30858,13 +31297,13 @@
     </row>
     <row r="764" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A764" t="s">
-        <v>3087</v>
+        <v>3080</v>
       </c>
       <c r="B764" t="s">
-        <v>2978</v>
+        <v>2971</v>
       </c>
       <c r="C764" t="s">
-        <v>2979</v>
+        <v>2972</v>
       </c>
       <c r="D764">
         <v>37.998202999999997</v>
@@ -30876,7 +31315,7 @@
         <v>628</v>
       </c>
       <c r="G764" t="s">
-        <v>2697</v>
+        <v>3639</v>
       </c>
       <c r="H764" t="s">
         <v>45</v>
@@ -30884,13 +31323,13 @@
     </row>
     <row r="765" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A765" t="s">
-        <v>3088</v>
+        <v>3081</v>
       </c>
       <c r="B765" t="s">
-        <v>2982</v>
+        <v>2975</v>
       </c>
       <c r="C765" t="s">
-        <v>2983</v>
+        <v>2976</v>
       </c>
       <c r="D765">
         <v>38.061923999999998</v>
@@ -30899,10 +31338,10 @@
         <v>139.45710800000001</v>
       </c>
       <c r="F765" t="s">
-        <v>2984</v>
+        <v>2977</v>
       </c>
       <c r="G765" t="s">
-        <v>2697</v>
+        <v>3639</v>
       </c>
       <c r="H765" t="s">
         <v>45</v>
@@ -30910,13 +31349,13 @@
     </row>
     <row r="766" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A766" t="s">
-        <v>3089</v>
+        <v>3082</v>
       </c>
       <c r="B766" t="s">
-        <v>2985</v>
+        <v>2978</v>
       </c>
       <c r="C766" t="s">
-        <v>2986</v>
+        <v>2979</v>
       </c>
       <c r="D766">
         <v>38.031841</v>
@@ -30925,10 +31364,10 @@
         <v>139.49603300000001</v>
       </c>
       <c r="F766" t="s">
-        <v>2987</v>
+        <v>2980</v>
       </c>
       <c r="G766" t="s">
-        <v>2697</v>
+        <v>3640</v>
       </c>
       <c r="H766" t="s">
         <v>45</v>
@@ -30936,13 +31375,13 @@
     </row>
     <row r="767" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A767" t="s">
-        <v>3090</v>
+        <v>3083</v>
       </c>
       <c r="B767" t="s">
-        <v>2988</v>
+        <v>2981</v>
       </c>
       <c r="C767" t="s">
-        <v>2989</v>
+        <v>2982</v>
       </c>
       <c r="D767">
         <v>37.536971999999999</v>
@@ -30951,10 +31390,10 @@
         <v>138.67962600000001</v>
       </c>
       <c r="F767" t="s">
-        <v>2990</v>
+        <v>2983</v>
       </c>
       <c r="G767" t="s">
-        <v>2697</v>
+        <v>3640</v>
       </c>
       <c r="H767" t="s">
         <v>23</v>
@@ -30962,13 +31401,13 @@
     </row>
     <row r="768" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A768" t="s">
-        <v>3093</v>
+        <v>3086</v>
       </c>
       <c r="B768" t="s">
-        <v>2991</v>
+        <v>2984</v>
       </c>
       <c r="C768" t="s">
-        <v>2992</v>
+        <v>2985</v>
       </c>
       <c r="D768">
         <v>37.527447000000002</v>
@@ -30977,24 +31416,24 @@
         <v>138.70774800000001</v>
       </c>
       <c r="F768" t="s">
-        <v>2993</v>
+        <v>2986</v>
       </c>
       <c r="G768" t="s">
-        <v>2697</v>
+        <v>3640</v>
       </c>
       <c r="H768" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="769" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="769" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A769" t="s">
-        <v>3401</v>
+        <v>3394</v>
       </c>
       <c r="B769" t="s">
-        <v>3094</v>
+        <v>3087</v>
       </c>
       <c r="C769" t="s">
-        <v>3095</v>
+        <v>3088</v>
       </c>
       <c r="D769">
         <v>36.695351000000002</v>
@@ -31003,21 +31442,24 @@
         <v>137.213165</v>
       </c>
       <c r="F769" t="s">
-        <v>3096</v>
-      </c>
-      <c r="G769" t="s">
+        <v>3506</v>
+      </c>
+      <c r="G769" s="1" t="s">
+        <v>3643</v>
+      </c>
+      <c r="H769" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="770" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="770" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A770" t="s">
-        <v>3401</v>
+        <v>3394</v>
       </c>
       <c r="B770" t="s">
-        <v>3097</v>
+        <v>3090</v>
       </c>
       <c r="C770" t="s">
-        <v>3098</v>
+        <v>3091</v>
       </c>
       <c r="D770">
         <v>36.700111</v>
@@ -31026,21 +31468,24 @@
         <v>137.21260100000001</v>
       </c>
       <c r="F770" t="s">
-        <v>3096</v>
+        <v>3507</v>
       </c>
       <c r="G770" t="s">
+        <v>3089</v>
+      </c>
+      <c r="H770" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="771" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="771" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A771" t="s">
-        <v>3099</v>
+        <v>3092</v>
       </c>
       <c r="B771" t="s">
-        <v>3100</v>
+        <v>3093</v>
       </c>
       <c r="C771" t="s">
-        <v>3101</v>
+        <v>3094</v>
       </c>
       <c r="D771">
         <v>36.693409000000003</v>
@@ -31049,21 +31494,24 @@
         <v>137.21258499999999</v>
       </c>
       <c r="F771" t="s">
+        <v>3508</v>
+      </c>
+      <c r="G771" t="s">
+        <v>3089</v>
+      </c>
+      <c r="H771" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="772" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A772" t="s">
+        <v>3395</v>
+      </c>
+      <c r="B772" t="s">
+        <v>3095</v>
+      </c>
+      <c r="C772" t="s">
         <v>3096</v>
-      </c>
-      <c r="G771" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="772" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A772" t="s">
-        <v>3402</v>
-      </c>
-      <c r="B772" t="s">
-        <v>3102</v>
-      </c>
-      <c r="C772" t="s">
-        <v>3103</v>
       </c>
       <c r="D772">
         <v>36.710132999999999</v>
@@ -31072,21 +31520,24 @@
         <v>137.20954900000001</v>
       </c>
       <c r="F772" t="s">
-        <v>3096</v>
+        <v>3509</v>
       </c>
       <c r="G772" t="s">
+        <v>3089</v>
+      </c>
+      <c r="H772" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="773" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="773" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A773" t="s">
-        <v>3402</v>
+        <v>3395</v>
       </c>
       <c r="B773" t="s">
-        <v>3104</v>
+        <v>3097</v>
       </c>
       <c r="C773" t="s">
-        <v>3105</v>
+        <v>3098</v>
       </c>
       <c r="D773">
         <v>36.716774000000001</v>
@@ -31095,21 +31546,24 @@
         <v>137.16447400000001</v>
       </c>
       <c r="F773" t="s">
-        <v>3096</v>
+        <v>3510</v>
       </c>
       <c r="G773" t="s">
+        <v>3089</v>
+      </c>
+      <c r="H773" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="774" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="774" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A774" t="s">
-        <v>3106</v>
+        <v>3099</v>
       </c>
       <c r="B774" t="s">
-        <v>3107</v>
+        <v>3100</v>
       </c>
       <c r="C774" t="s">
-        <v>3108</v>
+        <v>3101</v>
       </c>
       <c r="D774">
         <v>36.690559</v>
@@ -31118,21 +31572,24 @@
         <v>137.211365</v>
       </c>
       <c r="F774" t="s">
-        <v>3096</v>
+        <v>3511</v>
       </c>
       <c r="G774" t="s">
+        <v>3089</v>
+      </c>
+      <c r="H774" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="775" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="775" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A775" t="s">
-        <v>3109</v>
+        <v>3102</v>
       </c>
       <c r="B775" t="s">
-        <v>3110</v>
+        <v>3103</v>
       </c>
       <c r="C775" t="s">
-        <v>3111</v>
+        <v>3104</v>
       </c>
       <c r="D775">
         <v>36.759396000000002</v>
@@ -31141,21 +31598,24 @@
         <v>137.23440600000001</v>
       </c>
       <c r="F775" t="s">
-        <v>3096</v>
+        <v>1995</v>
       </c>
       <c r="G775" t="s">
+        <v>3089</v>
+      </c>
+      <c r="H775" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="776" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="776" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A776" t="s">
-        <v>3112</v>
+        <v>3105</v>
       </c>
       <c r="B776" t="s">
-        <v>3113</v>
+        <v>3106</v>
       </c>
       <c r="C776" t="s">
-        <v>3113</v>
+        <v>3106</v>
       </c>
       <c r="D776">
         <v>24.925609000000001</v>
@@ -31164,21 +31624,24 @@
         <v>125.274123</v>
       </c>
       <c r="F776" t="s">
-        <v>3113</v>
+        <v>208</v>
       </c>
       <c r="G776" t="s">
+        <v>3106</v>
+      </c>
+      <c r="H776" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="777" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="777" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A777" t="s">
-        <v>3114</v>
+        <v>3107</v>
       </c>
       <c r="B777" t="s">
-        <v>3115</v>
+        <v>3108</v>
       </c>
       <c r="C777" t="s">
-        <v>3116</v>
+        <v>3109</v>
       </c>
       <c r="D777">
         <v>36.576369999999997</v>
@@ -31187,21 +31650,24 @@
         <v>137.13017300000001</v>
       </c>
       <c r="F777" t="s">
-        <v>3096</v>
+        <v>3512</v>
       </c>
       <c r="G777" t="s">
+        <v>3089</v>
+      </c>
+      <c r="H777" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="778" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="778" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A778" t="s">
-        <v>3117</v>
+        <v>3110</v>
       </c>
       <c r="B778" t="s">
-        <v>3118</v>
+        <v>3111</v>
       </c>
       <c r="C778" t="s">
-        <v>3119</v>
+        <v>3112</v>
       </c>
       <c r="D778">
         <v>36.702044999999998</v>
@@ -31210,21 +31676,24 @@
         <v>137.211761</v>
       </c>
       <c r="F778" t="s">
-        <v>3096</v>
+        <v>3513</v>
       </c>
       <c r="G778" t="s">
+        <v>3089</v>
+      </c>
+      <c r="H778" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="779" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="779" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A779" t="s">
-        <v>3403</v>
+        <v>3396</v>
       </c>
       <c r="B779" t="s">
-        <v>3094</v>
+        <v>3087</v>
       </c>
       <c r="C779" t="s">
-        <v>3095</v>
+        <v>3088</v>
       </c>
       <c r="D779">
         <v>36.695351000000002</v>
@@ -31233,21 +31702,24 @@
         <v>137.213165</v>
       </c>
       <c r="F779" t="s">
+        <v>1230</v>
+      </c>
+      <c r="G779" t="s">
+        <v>3089</v>
+      </c>
+      <c r="H779" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="780" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A780" t="s">
+        <v>3396</v>
+      </c>
+      <c r="B780" t="s">
+        <v>3090</v>
+      </c>
+      <c r="C780" t="s">
         <v>3113</v>
-      </c>
-      <c r="G779" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="780" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A780" t="s">
-        <v>3403</v>
-      </c>
-      <c r="B780" t="s">
-        <v>3097</v>
-      </c>
-      <c r="C780" t="s">
-        <v>3120</v>
       </c>
       <c r="D780">
         <v>36.700111</v>
@@ -31256,21 +31728,24 @@
         <v>137.21260100000001</v>
       </c>
       <c r="F780" t="s">
-        <v>3113</v>
-      </c>
-      <c r="G780" t="s">
+        <v>3514</v>
+      </c>
+      <c r="G780" s="1" t="s">
+        <v>3643</v>
+      </c>
+      <c r="H780" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="781" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="781" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A781" t="s">
-        <v>3404</v>
+        <v>3397</v>
       </c>
       <c r="B781" t="s">
-        <v>3121</v>
+        <v>3114</v>
       </c>
       <c r="C781" t="s">
-        <v>3122</v>
+        <v>3115</v>
       </c>
       <c r="D781">
         <v>36.815005999999997</v>
@@ -31279,21 +31754,24 @@
         <v>137.03362999999999</v>
       </c>
       <c r="F781" t="s">
-        <v>3123</v>
+        <v>519</v>
       </c>
       <c r="G781" t="s">
+        <v>3116</v>
+      </c>
+      <c r="H781" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="782" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="782" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A782" t="s">
-        <v>3405</v>
+        <v>3398</v>
       </c>
       <c r="B782" t="s">
-        <v>3124</v>
+        <v>3117</v>
       </c>
       <c r="C782" t="s">
-        <v>3125</v>
+        <v>3118</v>
       </c>
       <c r="D782">
         <v>36.792870000000001</v>
@@ -31302,21 +31780,24 @@
         <v>137.05281099999999</v>
       </c>
       <c r="F782" t="s">
-        <v>3123</v>
+        <v>3515</v>
       </c>
       <c r="G782" t="s">
+        <v>3116</v>
+      </c>
+      <c r="H782" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="783" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="783" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A783" t="s">
-        <v>3406</v>
+        <v>3399</v>
       </c>
       <c r="B783" t="s">
-        <v>3126</v>
+        <v>3119</v>
       </c>
       <c r="C783" t="s">
-        <v>3127</v>
+        <v>3120</v>
       </c>
       <c r="D783">
         <v>36.861485000000002</v>
@@ -31325,21 +31806,24 @@
         <v>136.98739599999999</v>
       </c>
       <c r="F783" t="s">
-        <v>3128</v>
+        <v>3516</v>
       </c>
       <c r="G783" t="s">
+        <v>3121</v>
+      </c>
+      <c r="H783" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="784" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="784" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A784" t="s">
-        <v>3407</v>
+        <v>3400</v>
       </c>
       <c r="B784" t="s">
-        <v>3129</v>
+        <v>3122</v>
       </c>
       <c r="C784" t="s">
-        <v>3130</v>
+        <v>3123</v>
       </c>
       <c r="D784">
         <v>36.767574000000003</v>
@@ -31348,21 +31832,24 @@
         <v>137.34429900000001</v>
       </c>
       <c r="F784" t="s">
-        <v>3131</v>
+        <v>3517</v>
       </c>
       <c r="G784" t="s">
+        <v>3124</v>
+      </c>
+      <c r="H784" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="785" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="785" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A785" t="s">
-        <v>3408</v>
+        <v>3401</v>
       </c>
       <c r="B785" t="s">
-        <v>3132</v>
+        <v>3125</v>
       </c>
       <c r="C785" t="s">
-        <v>3133</v>
+        <v>3126</v>
       </c>
       <c r="D785">
         <v>36.641731</v>
@@ -31371,21 +31858,24 @@
         <v>136.959732</v>
       </c>
       <c r="F785" t="s">
-        <v>3134</v>
+        <v>996</v>
       </c>
       <c r="G785" t="s">
+        <v>3127</v>
+      </c>
+      <c r="H785" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="786" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="786" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A786" t="s">
-        <v>3409</v>
+        <v>3402</v>
       </c>
       <c r="B786" t="s">
-        <v>3135</v>
+        <v>3128</v>
       </c>
       <c r="C786" t="s">
-        <v>3136</v>
+        <v>3129</v>
       </c>
       <c r="D786">
         <v>36.689357999999999</v>
@@ -31394,21 +31884,24 @@
         <v>136.87655599999999</v>
       </c>
       <c r="F786" t="s">
-        <v>3137</v>
+        <v>3518</v>
       </c>
       <c r="G786" t="s">
+        <v>3130</v>
+      </c>
+      <c r="H786" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="787" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="787" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A787" t="s">
-        <v>3410</v>
+        <v>3403</v>
       </c>
       <c r="B787" t="s">
-        <v>3138</v>
+        <v>3131</v>
       </c>
       <c r="C787" t="s">
-        <v>3139</v>
+        <v>3132</v>
       </c>
       <c r="D787">
         <v>36.672890000000002</v>
@@ -31417,21 +31910,24 @@
         <v>136.86531099999999</v>
       </c>
       <c r="F787" t="s">
-        <v>3137</v>
+        <v>3519</v>
       </c>
       <c r="G787" t="s">
+        <v>3130</v>
+      </c>
+      <c r="H787" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="788" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="788" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A788" t="s">
-        <v>3411</v>
+        <v>3404</v>
       </c>
       <c r="B788" t="s">
-        <v>3140</v>
+        <v>3133</v>
       </c>
       <c r="C788" t="s">
-        <v>3141</v>
+        <v>3134</v>
       </c>
       <c r="D788">
         <v>36.752097999999997</v>
@@ -31440,21 +31936,24 @@
         <v>137.08442700000001</v>
       </c>
       <c r="F788" t="s">
-        <v>3142</v>
+        <v>3520</v>
       </c>
       <c r="G788" t="s">
+        <v>3135</v>
+      </c>
+      <c r="H788" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="789" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="789" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A789" t="s">
-        <v>3412</v>
+        <v>3405</v>
       </c>
       <c r="B789" t="s">
-        <v>3143</v>
+        <v>3136</v>
       </c>
       <c r="C789" t="s">
-        <v>3144</v>
+        <v>3137</v>
       </c>
       <c r="D789">
         <v>36.710182000000003</v>
@@ -31463,21 +31962,24 @@
         <v>137.30216999999999</v>
       </c>
       <c r="F789" t="s">
-        <v>3145</v>
+        <v>3521</v>
       </c>
       <c r="G789" t="s">
+        <v>3138</v>
+      </c>
+      <c r="H789" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="790" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="790" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A790" t="s">
-        <v>3413</v>
+        <v>3406</v>
       </c>
       <c r="B790" t="s">
-        <v>3146</v>
+        <v>3139</v>
       </c>
       <c r="C790" t="s">
-        <v>3147</v>
+        <v>3140</v>
       </c>
       <c r="D790">
         <v>36.701450000000001</v>
@@ -31486,21 +31988,24 @@
         <v>137.30715900000001</v>
       </c>
       <c r="F790" t="s">
-        <v>3145</v>
+        <v>3522</v>
       </c>
       <c r="G790" t="s">
+        <v>3138</v>
+      </c>
+      <c r="H790" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="791" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="791" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A791" t="s">
-        <v>3414</v>
+        <v>3407</v>
       </c>
       <c r="B791" t="s">
-        <v>3148</v>
+        <v>3141</v>
       </c>
       <c r="C791" t="s">
-        <v>3149</v>
+        <v>3142</v>
       </c>
       <c r="D791">
         <v>36.566273000000002</v>
@@ -31509,21 +32014,24 @@
         <v>136.653717</v>
       </c>
       <c r="F791" t="s">
-        <v>3150</v>
+        <v>3567</v>
       </c>
       <c r="G791" t="s">
+        <v>3143</v>
+      </c>
+      <c r="H791" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="792" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="792" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A792" t="s">
-        <v>3415</v>
+        <v>3408</v>
       </c>
       <c r="B792" t="s">
-        <v>3151</v>
+        <v>3144</v>
       </c>
       <c r="C792" t="s">
-        <v>3152</v>
+        <v>3145</v>
       </c>
       <c r="D792">
         <v>37.388992000000002</v>
@@ -31532,21 +32040,24 @@
         <v>136.90368699999999</v>
       </c>
       <c r="F792" t="s">
-        <v>3113</v>
-      </c>
-      <c r="G792" t="s">
+        <v>3568</v>
+      </c>
+      <c r="G792" s="1" t="s">
+        <v>3644</v>
+      </c>
+      <c r="H792" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="793" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="793" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A793" t="s">
-        <v>3416</v>
+        <v>3409</v>
       </c>
       <c r="B793" t="s">
-        <v>3151</v>
+        <v>3144</v>
       </c>
       <c r="C793" t="s">
-        <v>3152</v>
+        <v>3145</v>
       </c>
       <c r="D793">
         <v>37.388992000000002</v>
@@ -31555,21 +32066,24 @@
         <v>136.90368699999999</v>
       </c>
       <c r="F793" t="s">
-        <v>3113</v>
+        <v>3568</v>
       </c>
       <c r="G793" t="s">
+        <v>3641</v>
+      </c>
+      <c r="H793" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="794" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="794" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A794" t="s">
-        <v>3417</v>
+        <v>3410</v>
       </c>
       <c r="B794" t="s">
-        <v>3153</v>
+        <v>3146</v>
       </c>
       <c r="C794" t="s">
-        <v>3154</v>
+        <v>3147</v>
       </c>
       <c r="D794">
         <v>36.716704999999997</v>
@@ -31578,21 +32092,24 @@
         <v>136.70399499999999</v>
       </c>
       <c r="F794" t="s">
-        <v>3113</v>
-      </c>
-      <c r="G794" t="s">
+        <v>3569</v>
+      </c>
+      <c r="G794" s="1" t="s">
+        <v>3645</v>
+      </c>
+      <c r="H794" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="795" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="795" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A795" t="s">
-        <v>3418</v>
+        <v>3411</v>
       </c>
       <c r="B795" t="s">
-        <v>3155</v>
+        <v>3148</v>
       </c>
       <c r="C795" t="s">
-        <v>3156</v>
+        <v>3149</v>
       </c>
       <c r="D795">
         <v>37.006329000000001</v>
@@ -31601,21 +32118,24 @@
         <v>136.77804599999999</v>
       </c>
       <c r="F795" t="s">
-        <v>3157</v>
+        <v>267</v>
       </c>
       <c r="G795" t="s">
+        <v>3150</v>
+      </c>
+      <c r="H795" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="796" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="796" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A796" t="s">
-        <v>3425</v>
+        <v>3418</v>
       </c>
       <c r="B796" t="s">
-        <v>3158</v>
+        <v>3151</v>
       </c>
       <c r="C796" t="s">
-        <v>3156</v>
+        <v>3149</v>
       </c>
       <c r="D796">
         <v>37.006329000000001</v>
@@ -31624,21 +32144,24 @@
         <v>136.77804599999999</v>
       </c>
       <c r="F796" t="s">
-        <v>3157</v>
+        <v>267</v>
       </c>
       <c r="G796" t="s">
+        <v>3150</v>
+      </c>
+      <c r="H796" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="797" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="797" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A797" t="s">
-        <v>3419</v>
+        <v>3412</v>
       </c>
       <c r="B797" t="s">
-        <v>3159</v>
+        <v>3152</v>
       </c>
       <c r="C797" t="s">
-        <v>3160</v>
+        <v>3153</v>
       </c>
       <c r="D797">
         <v>36.957988999999998</v>
@@ -31647,21 +32170,24 @@
         <v>136.91511499999999</v>
       </c>
       <c r="F797" t="s">
-        <v>3161</v>
+        <v>3570</v>
       </c>
       <c r="G797" t="s">
+        <v>3154</v>
+      </c>
+      <c r="H797" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="798" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="798" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A798" t="s">
-        <v>3420</v>
+        <v>3413</v>
       </c>
       <c r="B798" t="s">
-        <v>3162</v>
+        <v>3155</v>
       </c>
       <c r="C798" t="s">
-        <v>3163</v>
+        <v>3156</v>
       </c>
       <c r="D798">
         <v>37.228527</v>
@@ -31670,21 +32196,24 @@
         <v>136.90115399999999</v>
       </c>
       <c r="F798" t="s">
-        <v>3164</v>
+        <v>357</v>
       </c>
       <c r="G798" t="s">
+        <v>3157</v>
+      </c>
+      <c r="H798" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="799" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="799" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A799" t="s">
-        <v>3421</v>
+        <v>3414</v>
       </c>
       <c r="B799" t="s">
-        <v>3165</v>
+        <v>3158</v>
       </c>
       <c r="C799" t="s">
-        <v>3166</v>
+        <v>3159</v>
       </c>
       <c r="D799">
         <v>37.228920000000002</v>
@@ -31693,21 +32222,24 @@
         <v>136.91378800000001</v>
       </c>
       <c r="F799" t="s">
-        <v>3164</v>
+        <v>288</v>
       </c>
       <c r="G799" t="s">
+        <v>3157</v>
+      </c>
+      <c r="H799" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="800" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="800" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A800" t="s">
-        <v>3422</v>
+        <v>3415</v>
       </c>
       <c r="B800" t="s">
-        <v>3167</v>
+        <v>3160</v>
       </c>
       <c r="C800" t="s">
-        <v>3168</v>
+        <v>3161</v>
       </c>
       <c r="D800">
         <v>37.311176000000003</v>
@@ -31716,21 +32248,24 @@
         <v>137.23782299999999</v>
       </c>
       <c r="F800" t="s">
-        <v>3169</v>
+        <v>3571</v>
       </c>
       <c r="G800" t="s">
+        <v>3162</v>
+      </c>
+      <c r="H800" t="s">
         <v>862</v>
       </c>
     </row>
-    <row r="801" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="801" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A801" t="s">
-        <v>3423</v>
+        <v>3416</v>
       </c>
       <c r="B801" t="s">
-        <v>3170</v>
+        <v>3163</v>
       </c>
       <c r="C801" t="s">
-        <v>3171</v>
+        <v>3164</v>
       </c>
       <c r="D801">
         <v>37.309986000000002</v>
@@ -31739,21 +32274,24 @@
         <v>137.14810199999999</v>
       </c>
       <c r="F801" t="s">
-        <v>3169</v>
+        <v>3572</v>
       </c>
       <c r="G801" t="s">
+        <v>3162</v>
+      </c>
+      <c r="H801" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="802" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="802" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A802" t="s">
-        <v>3424</v>
+        <v>3417</v>
       </c>
       <c r="B802" t="s">
-        <v>3172</v>
+        <v>3165</v>
       </c>
       <c r="C802" t="s">
-        <v>3173</v>
+        <v>3166</v>
       </c>
       <c r="D802">
         <v>37.367263999999999</v>
@@ -31762,21 +32300,24 @@
         <v>137.24252300000001</v>
       </c>
       <c r="F802" t="s">
-        <v>3169</v>
+        <v>3573</v>
       </c>
       <c r="G802" t="s">
+        <v>3162</v>
+      </c>
+      <c r="H802" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="803" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="803" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A803" t="s">
-        <v>3426</v>
+        <v>3419</v>
       </c>
       <c r="B803" t="s">
-        <v>3174</v>
+        <v>3167</v>
       </c>
       <c r="C803" t="s">
-        <v>3175</v>
+        <v>3168</v>
       </c>
       <c r="D803">
         <v>36.065750000000001</v>
@@ -31785,21 +32326,24 @@
         <v>136.21850599999999</v>
       </c>
       <c r="F803" t="s">
-        <v>3176</v>
+        <v>3574</v>
       </c>
       <c r="G803" t="s">
+        <v>3169</v>
+      </c>
+      <c r="H803" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="804" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="804" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A804" t="s">
-        <v>3426</v>
+        <v>3419</v>
       </c>
       <c r="B804" t="s">
-        <v>3177</v>
+        <v>3170</v>
       </c>
       <c r="C804" t="s">
-        <v>3178</v>
+        <v>3171</v>
       </c>
       <c r="D804">
         <v>36.058903000000001</v>
@@ -31808,21 +32352,24 @@
         <v>136.21156300000001</v>
       </c>
       <c r="F804" t="s">
-        <v>3176</v>
+        <v>3575</v>
       </c>
       <c r="G804" t="s">
+        <v>3169</v>
+      </c>
+      <c r="H804" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="805" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="805" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A805" t="s">
-        <v>3179</v>
+        <v>3172</v>
       </c>
       <c r="B805" t="s">
-        <v>3180</v>
+        <v>3173</v>
       </c>
       <c r="C805" t="s">
-        <v>3181</v>
+        <v>3174</v>
       </c>
       <c r="D805">
         <v>36.000743999999997</v>
@@ -31831,21 +32378,24 @@
         <v>136.29626500000001</v>
       </c>
       <c r="F805" t="s">
+        <v>3576</v>
+      </c>
+      <c r="G805" t="s">
+        <v>3169</v>
+      </c>
+      <c r="H805" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="806" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A806" t="s">
+        <v>3420</v>
+      </c>
+      <c r="B806" t="s">
+        <v>3175</v>
+      </c>
+      <c r="C806" t="s">
         <v>3176</v>
-      </c>
-      <c r="G805" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="806" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A806" t="s">
-        <v>3427</v>
-      </c>
-      <c r="B806" t="s">
-        <v>3182</v>
-      </c>
-      <c r="C806" t="s">
-        <v>3183</v>
       </c>
       <c r="D806">
         <v>35.660693999999999</v>
@@ -31854,21 +32404,24 @@
         <v>136.072891</v>
       </c>
       <c r="F806" t="s">
-        <v>3184</v>
+        <v>3577</v>
       </c>
       <c r="G806" t="s">
+        <v>3177</v>
+      </c>
+      <c r="H806" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="807" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="807" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A807" t="s">
-        <v>3428</v>
+        <v>3421</v>
       </c>
       <c r="B807" t="s">
-        <v>3185</v>
+        <v>3178</v>
       </c>
       <c r="C807" t="s">
-        <v>3186</v>
+        <v>3179</v>
       </c>
       <c r="D807">
         <v>35.666046000000001</v>
@@ -31877,21 +32430,24 @@
         <v>136.06636</v>
       </c>
       <c r="F807" t="s">
-        <v>3184</v>
+        <v>3578</v>
       </c>
       <c r="G807" t="s">
+        <v>3177</v>
+      </c>
+      <c r="H807" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="808" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="808" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A808" t="s">
-        <v>3429</v>
+        <v>3422</v>
       </c>
       <c r="B808" t="s">
-        <v>3187</v>
+        <v>3180</v>
       </c>
       <c r="C808" t="s">
-        <v>3188</v>
+        <v>3181</v>
       </c>
       <c r="D808">
         <v>35.976005999999998</v>
@@ -31900,21 +32456,24 @@
         <v>136.490387</v>
       </c>
       <c r="F808" t="s">
-        <v>3189</v>
+        <v>3579</v>
       </c>
       <c r="G808" t="s">
+        <v>3182</v>
+      </c>
+      <c r="H808" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="809" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="809" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A809" t="s">
-        <v>3430</v>
+        <v>3423</v>
       </c>
       <c r="B809" t="s">
-        <v>3190</v>
+        <v>3183</v>
       </c>
       <c r="C809" t="s">
-        <v>3191</v>
+        <v>3184</v>
       </c>
       <c r="D809">
         <v>36.081305999999998</v>
@@ -31923,21 +32482,24 @@
         <v>136.50621000000001</v>
       </c>
       <c r="F809" t="s">
-        <v>3113</v>
+        <v>3580</v>
       </c>
       <c r="G809" t="s">
+        <v>3187</v>
+      </c>
+      <c r="H809" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="810" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="810" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A810" t="s">
-        <v>3431</v>
+        <v>3424</v>
       </c>
       <c r="B810" t="s">
-        <v>3192</v>
+        <v>3185</v>
       </c>
       <c r="C810" t="s">
-        <v>3193</v>
+        <v>3186</v>
       </c>
       <c r="D810">
         <v>36.073559000000003</v>
@@ -31946,21 +32508,24 @@
         <v>136.474503</v>
       </c>
       <c r="F810" t="s">
-        <v>3194</v>
+        <v>3581</v>
       </c>
       <c r="G810" t="s">
+        <v>3187</v>
+      </c>
+      <c r="H810" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="811" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="811" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A811" t="s">
-        <v>3432</v>
+        <v>3425</v>
       </c>
       <c r="B811" t="s">
-        <v>3195</v>
+        <v>3188</v>
       </c>
       <c r="C811" t="s">
-        <v>3196</v>
+        <v>3189</v>
       </c>
       <c r="D811">
         <v>35.911617</v>
@@ -31969,21 +32534,24 @@
         <v>136.24588</v>
       </c>
       <c r="F811" t="s">
-        <v>3197</v>
+        <v>3582</v>
       </c>
       <c r="G811" t="s">
+        <v>3190</v>
+      </c>
+      <c r="H811" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="812" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="812" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A812" t="s">
-        <v>3433</v>
+        <v>3426</v>
       </c>
       <c r="B812" t="s">
-        <v>3198</v>
+        <v>3191</v>
       </c>
       <c r="C812" t="s">
-        <v>3199</v>
+        <v>3192</v>
       </c>
       <c r="D812">
         <v>35.488815000000002</v>
@@ -31992,21 +32560,24 @@
         <v>135.52037000000001</v>
       </c>
       <c r="F812" t="s">
-        <v>3200</v>
+        <v>68</v>
       </c>
       <c r="G812" t="s">
+        <v>3193</v>
+      </c>
+      <c r="H812" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="813" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="813" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A813" t="s">
-        <v>3434</v>
+        <v>3427</v>
       </c>
       <c r="B813" t="s">
-        <v>3201</v>
+        <v>3194</v>
       </c>
       <c r="C813" t="s">
-        <v>3202</v>
+        <v>3195</v>
       </c>
       <c r="D813">
         <v>35.558791999999997</v>
@@ -32015,21 +32586,24 @@
         <v>135.8965</v>
       </c>
       <c r="F813" t="s">
-        <v>3203</v>
+        <v>3583</v>
       </c>
       <c r="G813" t="s">
+        <v>3196</v>
+      </c>
+      <c r="H813" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="814" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="814" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A814" t="s">
-        <v>3435</v>
+        <v>3428</v>
       </c>
       <c r="B814" t="s">
-        <v>3204</v>
+        <v>3197</v>
       </c>
       <c r="C814" t="s">
-        <v>3205</v>
+        <v>3198</v>
       </c>
       <c r="D814">
         <v>35.685462999999999</v>
@@ -32038,21 +32612,24 @@
         <v>138.57690400000001</v>
       </c>
       <c r="F814" t="s">
-        <v>3206</v>
+        <v>3584</v>
       </c>
       <c r="G814" t="s">
+        <v>3199</v>
+      </c>
+      <c r="H814" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="815" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="815" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A815" t="s">
-        <v>3436</v>
+        <v>3429</v>
       </c>
       <c r="B815" t="s">
-        <v>3207</v>
+        <v>3200</v>
       </c>
       <c r="C815" t="s">
-        <v>3208</v>
+        <v>3201</v>
       </c>
       <c r="D815">
         <v>35.65963</v>
@@ -32061,21 +32638,24 @@
         <v>138.580963</v>
       </c>
       <c r="F815" t="s">
-        <v>3206</v>
+        <v>3585</v>
       </c>
       <c r="G815" t="s">
+        <v>3199</v>
+      </c>
+      <c r="H815" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="816" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="816" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A816" t="s">
-        <v>3437</v>
+        <v>3430</v>
       </c>
       <c r="B816" t="s">
-        <v>3209</v>
+        <v>3202</v>
       </c>
       <c r="C816" t="s">
-        <v>3210</v>
+        <v>3203</v>
       </c>
       <c r="D816">
         <v>35.663482999999999</v>
@@ -32084,21 +32664,24 @@
         <v>138.57115200000001</v>
       </c>
       <c r="F816" t="s">
-        <v>3206</v>
+        <v>3586</v>
       </c>
       <c r="G816" t="s">
+        <v>3199</v>
+      </c>
+      <c r="H816" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="817" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="817" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A817" t="s">
-        <v>3438</v>
+        <v>3431</v>
       </c>
       <c r="B817" t="s">
-        <v>3211</v>
+        <v>3204</v>
       </c>
       <c r="C817" t="s">
-        <v>3212</v>
+        <v>3205</v>
       </c>
       <c r="D817">
         <v>35.552021000000003</v>
@@ -32107,21 +32690,24 @@
         <v>138.90588399999999</v>
       </c>
       <c r="F817" t="s">
-        <v>3213</v>
+        <v>3587</v>
       </c>
       <c r="G817" t="s">
+        <v>3206</v>
+      </c>
+      <c r="H817" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="818" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="818" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A818" t="s">
-        <v>3447</v>
+        <v>3440</v>
       </c>
       <c r="B818" t="s">
-        <v>3214</v>
+        <v>3207</v>
       </c>
       <c r="C818" t="s">
-        <v>3215</v>
+        <v>3208</v>
       </c>
       <c r="D818">
         <v>35.583351</v>
@@ -32130,21 +32716,24 @@
         <v>138.931702</v>
       </c>
       <c r="F818" t="s">
-        <v>3213</v>
+        <v>3588</v>
       </c>
       <c r="G818" t="s">
+        <v>3206</v>
+      </c>
+      <c r="H818" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="819" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="819" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A819" t="s">
-        <v>3448</v>
+        <v>3441</v>
       </c>
       <c r="B819" t="s">
-        <v>3216</v>
+        <v>3209</v>
       </c>
       <c r="C819" t="s">
-        <v>3212</v>
+        <v>3205</v>
       </c>
       <c r="D819">
         <v>35.552021000000003</v>
@@ -32153,21 +32742,24 @@
         <v>138.90588399999999</v>
       </c>
       <c r="F819" t="s">
-        <v>3213</v>
+        <v>3587</v>
       </c>
       <c r="G819" t="s">
+        <v>3206</v>
+      </c>
+      <c r="H819" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="820" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="820" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A820" t="s">
-        <v>3448</v>
+        <v>3441</v>
       </c>
       <c r="B820" t="s">
-        <v>3214</v>
+        <v>3207</v>
       </c>
       <c r="C820" t="s">
-        <v>3215</v>
+        <v>3208</v>
       </c>
       <c r="D820">
         <v>35.583351</v>
@@ -32176,21 +32768,24 @@
         <v>138.931702</v>
       </c>
       <c r="F820" t="s">
-        <v>3213</v>
+        <v>3588</v>
       </c>
       <c r="G820" t="s">
+        <v>3206</v>
+      </c>
+      <c r="H820" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="821" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="821" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A821" t="s">
-        <v>3449</v>
+        <v>3442</v>
       </c>
       <c r="B821" t="s">
-        <v>3217</v>
+        <v>3210</v>
       </c>
       <c r="C821" t="s">
-        <v>3218</v>
+        <v>3211</v>
       </c>
       <c r="D821">
         <v>35.6068</v>
@@ -32199,21 +32794,24 @@
         <v>138.93249499999999</v>
       </c>
       <c r="F821" t="s">
-        <v>3219</v>
+        <v>1006</v>
       </c>
       <c r="G821" t="s">
+        <v>3212</v>
+      </c>
+      <c r="H821" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="822" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="822" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A822" t="s">
-        <v>3449</v>
+        <v>3442</v>
       </c>
       <c r="B822" t="s">
-        <v>3220</v>
+        <v>3213</v>
       </c>
       <c r="C822" t="s">
-        <v>3221</v>
+        <v>3214</v>
       </c>
       <c r="D822">
         <v>35.613219999999998</v>
@@ -32222,21 +32820,24 @@
         <v>138.942474</v>
       </c>
       <c r="F822" t="s">
-        <v>3219</v>
+        <v>3589</v>
       </c>
       <c r="G822" t="s">
+        <v>3212</v>
+      </c>
+      <c r="H822" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="823" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="823" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A823" t="s">
-        <v>3439</v>
+        <v>3432</v>
       </c>
       <c r="B823" t="s">
-        <v>3222</v>
+        <v>3215</v>
       </c>
       <c r="C823" t="s">
-        <v>3223</v>
+        <v>3216</v>
       </c>
       <c r="D823">
         <v>35.637886000000002</v>
@@ -32245,21 +32846,24 @@
         <v>138.47065699999999</v>
       </c>
       <c r="F823" t="s">
-        <v>3224</v>
+        <v>3590</v>
       </c>
       <c r="G823" t="s">
+        <v>3217</v>
+      </c>
+      <c r="H823" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="824" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="824" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A824" t="s">
-        <v>3440</v>
+        <v>3433</v>
       </c>
       <c r="B824" t="s">
-        <v>3225</v>
+        <v>3218</v>
       </c>
       <c r="C824" t="s">
-        <v>3226</v>
+        <v>3219</v>
       </c>
       <c r="D824">
         <v>35.612910999999997</v>
@@ -32268,21 +32872,24 @@
         <v>138.48001099999999</v>
       </c>
       <c r="F824" t="s">
-        <v>3224</v>
+        <v>3591</v>
       </c>
       <c r="G824" t="s">
+        <v>3217</v>
+      </c>
+      <c r="H824" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="825" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="825" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A825" t="s">
-        <v>3441</v>
+        <v>3434</v>
       </c>
       <c r="B825" t="s">
-        <v>3227</v>
+        <v>3220</v>
       </c>
       <c r="C825" t="s">
-        <v>3228</v>
+        <v>3221</v>
       </c>
       <c r="D825">
         <v>35.659934999999997</v>
@@ -32291,21 +32898,24 @@
         <v>138.51589999999999</v>
       </c>
       <c r="F825" t="s">
-        <v>3229</v>
+        <v>1006</v>
       </c>
       <c r="G825" t="s">
+        <v>3222</v>
+      </c>
+      <c r="H825" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="826" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="826" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A826" t="s">
-        <v>3450</v>
+        <v>3443</v>
       </c>
       <c r="B826" t="s">
-        <v>3230</v>
+        <v>3223</v>
       </c>
       <c r="C826" t="s">
-        <v>3231</v>
+        <v>3224</v>
       </c>
       <c r="D826">
         <v>35.660328</v>
@@ -32314,21 +32924,24 @@
         <v>138.51542699999999</v>
       </c>
       <c r="F826" t="s">
-        <v>3229</v>
+        <v>3592</v>
       </c>
       <c r="G826" t="s">
+        <v>3222</v>
+      </c>
+      <c r="H826" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="827" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="827" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A827" t="s">
-        <v>3442</v>
+        <v>3435</v>
       </c>
       <c r="B827" t="s">
-        <v>3232</v>
+        <v>3225</v>
       </c>
       <c r="C827" t="s">
-        <v>3233</v>
+        <v>3226</v>
       </c>
       <c r="D827">
         <v>35.686141999999997</v>
@@ -32337,21 +32950,24 @@
         <v>138.48696899999999</v>
       </c>
       <c r="F827" t="s">
-        <v>3229</v>
+        <v>3593</v>
       </c>
       <c r="G827" t="s">
+        <v>3222</v>
+      </c>
+      <c r="H827" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="828" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="828" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A828" t="s">
-        <v>3443</v>
+        <v>3436</v>
       </c>
       <c r="B828" t="s">
-        <v>3234</v>
+        <v>3227</v>
       </c>
       <c r="C828" t="s">
-        <v>3235</v>
+        <v>3228</v>
       </c>
       <c r="D828">
         <v>35.629981999999998</v>
@@ -32360,21 +32976,24 @@
         <v>139.108566</v>
       </c>
       <c r="F828" t="s">
-        <v>3113</v>
-      </c>
-      <c r="G828" t="s">
+        <v>1794</v>
+      </c>
+      <c r="G828" s="1" t="s">
+        <v>3646</v>
+      </c>
+      <c r="H828" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="829" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="829" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A829" t="s">
-        <v>3451</v>
+        <v>3444</v>
       </c>
       <c r="B829" t="s">
-        <v>3236</v>
+        <v>3229</v>
       </c>
       <c r="C829" t="s">
-        <v>3235</v>
+        <v>3228</v>
       </c>
       <c r="D829">
         <v>35.629981999999998</v>
@@ -32383,21 +33002,24 @@
         <v>139.108566</v>
       </c>
       <c r="F829" t="s">
-        <v>3113</v>
+        <v>3594</v>
       </c>
       <c r="G829" t="s">
+        <v>3642</v>
+      </c>
+      <c r="H829" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="830" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="830" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A830" t="s">
-        <v>3444</v>
+        <v>3437</v>
       </c>
       <c r="B830" t="s">
-        <v>3237</v>
+        <v>3230</v>
       </c>
       <c r="C830" t="s">
-        <v>3238</v>
+        <v>3231</v>
       </c>
       <c r="D830">
         <v>35.599975999999998</v>
@@ -32406,21 +33028,24 @@
         <v>138.51719700000001</v>
       </c>
       <c r="F830" t="s">
-        <v>3239</v>
+        <v>2563</v>
       </c>
       <c r="G830" t="s">
+        <v>3232</v>
+      </c>
+      <c r="H830" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="831" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="831" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A831" t="s">
-        <v>3452</v>
+        <v>3445</v>
       </c>
       <c r="B831" t="s">
-        <v>3240</v>
+        <v>3233</v>
       </c>
       <c r="C831" t="s">
-        <v>3241</v>
+        <v>3234</v>
       </c>
       <c r="D831">
         <v>35.497008999999998</v>
@@ -32429,21 +33054,24 @@
         <v>138.75479100000001</v>
       </c>
       <c r="F831" t="s">
-        <v>3242</v>
+        <v>3595</v>
       </c>
       <c r="G831" t="s">
+        <v>3235</v>
+      </c>
+      <c r="H831" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="832" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="832" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A832" t="s">
-        <v>3452</v>
+        <v>3445</v>
       </c>
       <c r="B832" t="s">
-        <v>3243</v>
+        <v>3236</v>
       </c>
       <c r="C832" t="s">
-        <v>3244</v>
+        <v>3237</v>
       </c>
       <c r="D832">
         <v>35.497008999999998</v>
@@ -32452,21 +33080,24 @@
         <v>138.75479100000001</v>
       </c>
       <c r="F832" t="s">
-        <v>3242</v>
+        <v>3596</v>
       </c>
       <c r="G832" t="s">
+        <v>3235</v>
+      </c>
+      <c r="H832" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="833" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="833" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A833" t="s">
-        <v>3445</v>
+        <v>3438</v>
       </c>
       <c r="B833" t="s">
-        <v>3245</v>
+        <v>3238</v>
       </c>
       <c r="C833" t="s">
-        <v>3246</v>
+        <v>3239</v>
       </c>
       <c r="D833">
         <v>35.504157999999997</v>
@@ -32475,21 +33106,24 @@
         <v>138.734467</v>
       </c>
       <c r="F833" t="s">
-        <v>3242</v>
+        <v>3597</v>
       </c>
       <c r="G833" t="s">
+        <v>3235</v>
+      </c>
+      <c r="H833" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="834" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="834" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A834" t="s">
-        <v>3446</v>
+        <v>3439</v>
       </c>
       <c r="B834" t="s">
-        <v>3247</v>
+        <v>3240</v>
       </c>
       <c r="C834" t="s">
-        <v>3248</v>
+        <v>3241</v>
       </c>
       <c r="D834">
         <v>35.494380999999997</v>
@@ -32498,21 +33132,24 @@
         <v>138.66804500000001</v>
       </c>
       <c r="F834" t="s">
+        <v>3598</v>
+      </c>
+      <c r="G834" t="s">
+        <v>3235</v>
+      </c>
+      <c r="H834" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="835" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A835" t="s">
+        <v>3446</v>
+      </c>
+      <c r="B835" t="s">
         <v>3242</v>
       </c>
-      <c r="G834" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="835" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A835" t="s">
-        <v>3453</v>
-      </c>
-      <c r="B835" t="s">
-        <v>3249</v>
-      </c>
       <c r="C835" t="s">
-        <v>3250</v>
+        <v>3243</v>
       </c>
       <c r="D835">
         <v>36.006774999999998</v>
@@ -32521,21 +33158,24 @@
         <v>138.056183</v>
       </c>
       <c r="F835" t="s">
-        <v>3251</v>
+        <v>1006</v>
       </c>
       <c r="G835" t="s">
+        <v>3244</v>
+      </c>
+      <c r="H835" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="836" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="836" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A836" t="s">
-        <v>3453</v>
+        <v>3446</v>
       </c>
       <c r="B836" t="s">
-        <v>3252</v>
+        <v>3245</v>
       </c>
       <c r="C836" t="s">
-        <v>3250</v>
+        <v>3243</v>
       </c>
       <c r="D836">
         <v>36.006774999999998</v>
@@ -32544,21 +33184,24 @@
         <v>138.056183</v>
       </c>
       <c r="F836" t="s">
-        <v>3251</v>
+        <v>3523</v>
       </c>
       <c r="G836" t="s">
+        <v>3244</v>
+      </c>
+      <c r="H836" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="837" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="837" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A837" t="s">
-        <v>3454</v>
+        <v>3447</v>
       </c>
       <c r="B837" t="s">
-        <v>3253</v>
+        <v>3246</v>
       </c>
       <c r="C837" t="s">
-        <v>3254</v>
+        <v>3247</v>
       </c>
       <c r="D837">
         <v>36.302154999999999</v>
@@ -32567,21 +33210,24 @@
         <v>137.93270899999999</v>
       </c>
       <c r="F837" t="s">
-        <v>3113</v>
+        <v>267</v>
       </c>
       <c r="G837" t="s">
+        <v>3244</v>
+      </c>
+      <c r="H837" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="838" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="838" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A838" t="s">
-        <v>3455</v>
+        <v>3448</v>
       </c>
       <c r="B838" t="s">
-        <v>3255</v>
+        <v>3248</v>
       </c>
       <c r="C838" t="s">
-        <v>3256</v>
+        <v>3249</v>
       </c>
       <c r="D838">
         <v>36.611030999999997</v>
@@ -32590,21 +33236,24 @@
         <v>138.22316000000001</v>
       </c>
       <c r="F838" t="s">
-        <v>3113</v>
+        <v>68</v>
       </c>
       <c r="G838" t="s">
+        <v>3244</v>
+      </c>
+      <c r="H838" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="839" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="839" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A839" t="s">
-        <v>3456</v>
+        <v>3449</v>
       </c>
       <c r="B839" t="s">
-        <v>3257</v>
+        <v>3250</v>
       </c>
       <c r="C839" t="s">
-        <v>3258</v>
+        <v>3251</v>
       </c>
       <c r="D839">
         <v>36.340176</v>
@@ -32613,21 +33262,24 @@
         <v>137.88252299999999</v>
       </c>
       <c r="F839" t="s">
-        <v>3251</v>
+        <v>3524</v>
       </c>
       <c r="G839" t="s">
+        <v>3244</v>
+      </c>
+      <c r="H839" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="840" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="840" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A840" t="s">
-        <v>3457</v>
+        <v>3450</v>
       </c>
       <c r="B840" t="s">
-        <v>3259</v>
+        <v>3252</v>
       </c>
       <c r="C840" t="s">
-        <v>3260</v>
+        <v>3253</v>
       </c>
       <c r="D840">
         <v>36.700901000000002</v>
@@ -32636,21 +33288,24 @@
         <v>138.27557400000001</v>
       </c>
       <c r="F840" t="s">
-        <v>3251</v>
+        <v>68</v>
       </c>
       <c r="G840" t="s">
+        <v>3244</v>
+      </c>
+      <c r="H840" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="841" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="841" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A841" t="s">
-        <v>3498</v>
+        <v>3491</v>
       </c>
       <c r="B841" t="s">
-        <v>3261</v>
+        <v>3254</v>
       </c>
       <c r="C841" t="s">
-        <v>3260</v>
+        <v>3253</v>
       </c>
       <c r="D841">
         <v>36.700901000000002</v>
@@ -32659,21 +33314,24 @@
         <v>138.27557400000001</v>
       </c>
       <c r="F841" t="s">
-        <v>3251</v>
+        <v>68</v>
       </c>
       <c r="G841" t="s">
+        <v>3244</v>
+      </c>
+      <c r="H841" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="842" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="842" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A842" t="s">
-        <v>3458</v>
+        <v>3451</v>
       </c>
       <c r="B842" t="s">
-        <v>3262</v>
+        <v>3255</v>
       </c>
       <c r="C842" t="s">
-        <v>3263</v>
+        <v>3256</v>
       </c>
       <c r="D842">
         <v>36.638415999999999</v>
@@ -32682,21 +33340,24 @@
         <v>138.19426000000001</v>
       </c>
       <c r="F842" t="s">
-        <v>3264</v>
+        <v>3525</v>
       </c>
       <c r="G842" t="s">
+        <v>3257</v>
+      </c>
+      <c r="H842" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="843" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="843" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A843" t="s">
-        <v>3459</v>
+        <v>3452</v>
       </c>
       <c r="B843" t="s">
-        <v>3265</v>
+        <v>3258</v>
       </c>
       <c r="C843" t="s">
-        <v>3266</v>
+        <v>3259</v>
       </c>
       <c r="D843">
         <v>36.236614000000003</v>
@@ -32705,21 +33366,24 @@
         <v>137.969818</v>
       </c>
       <c r="F843" t="s">
-        <v>3267</v>
+        <v>3526</v>
       </c>
       <c r="G843" t="s">
+        <v>3260</v>
+      </c>
+      <c r="H843" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="844" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="844" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A844" t="s">
-        <v>3460</v>
+        <v>3453</v>
       </c>
       <c r="B844" t="s">
-        <v>3268</v>
+        <v>3261</v>
       </c>
       <c r="C844" t="s">
-        <v>3269</v>
+        <v>3262</v>
       </c>
       <c r="D844">
         <v>36.402808999999998</v>
@@ -32728,21 +33392,24 @@
         <v>138.247131</v>
       </c>
       <c r="F844" t="s">
-        <v>3270</v>
+        <v>2098</v>
       </c>
       <c r="G844" t="s">
+        <v>3263</v>
+      </c>
+      <c r="H844" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="845" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="845" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A845" t="s">
-        <v>3461</v>
+        <v>3454</v>
       </c>
       <c r="B845" t="s">
-        <v>3271</v>
+        <v>3264</v>
       </c>
       <c r="C845" t="s">
-        <v>3272</v>
+        <v>3265</v>
       </c>
       <c r="D845">
         <v>36.492019999999997</v>
@@ -32751,21 +33418,24 @@
         <v>138.37451200000001</v>
       </c>
       <c r="F845" t="s">
-        <v>3270</v>
+        <v>1995</v>
       </c>
       <c r="G845" t="s">
+        <v>3263</v>
+      </c>
+      <c r="H845" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="846" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="846" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A846" t="s">
-        <v>3462</v>
+        <v>3455</v>
       </c>
       <c r="B846" t="s">
-        <v>3273</v>
+        <v>3266</v>
       </c>
       <c r="C846" t="s">
-        <v>3274</v>
+        <v>3267</v>
       </c>
       <c r="D846">
         <v>36.286594000000001</v>
@@ -32774,21 +33444,24 @@
         <v>138.23909</v>
       </c>
       <c r="F846" t="s">
+        <v>3527</v>
+      </c>
+      <c r="G846" t="s">
+        <v>3263</v>
+      </c>
+      <c r="H846" t="s">
+        <v>3268</v>
+      </c>
+    </row>
+    <row r="847" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A847" t="s">
+        <v>3456</v>
+      </c>
+      <c r="B847" t="s">
+        <v>3269</v>
+      </c>
+      <c r="C847" t="s">
         <v>3270</v>
-      </c>
-      <c r="G846" t="s">
-        <v>3275</v>
-      </c>
-    </row>
-    <row r="847" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A847" t="s">
-        <v>3463</v>
-      </c>
-      <c r="B847" t="s">
-        <v>3276</v>
-      </c>
-      <c r="C847" t="s">
-        <v>3277</v>
       </c>
       <c r="D847">
         <v>36.286594000000001</v>
@@ -32797,21 +33470,24 @@
         <v>138.23909</v>
       </c>
       <c r="F847" t="s">
-        <v>3270</v>
+        <v>3528</v>
       </c>
       <c r="G847" t="s">
-        <v>3278</v>
-      </c>
-    </row>
-    <row r="848" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+        <v>3263</v>
+      </c>
+      <c r="H847" t="s">
+        <v>3271</v>
+      </c>
+    </row>
+    <row r="848" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A848" t="s">
-        <v>3464</v>
+        <v>3457</v>
       </c>
       <c r="B848" t="s">
-        <v>3279</v>
+        <v>3272</v>
       </c>
       <c r="C848" t="s">
-        <v>3280</v>
+        <v>3273</v>
       </c>
       <c r="D848">
         <v>36.402808999999998</v>
@@ -32820,21 +33496,24 @@
         <v>138.247131</v>
       </c>
       <c r="F848" t="s">
-        <v>3270</v>
+        <v>2098</v>
       </c>
       <c r="G848" t="s">
+        <v>3263</v>
+      </c>
+      <c r="H848" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="849" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="849" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A849" t="s">
-        <v>3465</v>
+        <v>3458</v>
       </c>
       <c r="B849" t="s">
-        <v>3281</v>
+        <v>3274</v>
       </c>
       <c r="C849" t="s">
-        <v>3282</v>
+        <v>3275</v>
       </c>
       <c r="D849">
         <v>36.066673000000002</v>
@@ -32843,21 +33522,24 @@
         <v>138.051041</v>
       </c>
       <c r="F849" t="s">
-        <v>3283</v>
+        <v>3529</v>
       </c>
       <c r="G849" t="s">
+        <v>3276</v>
+      </c>
+      <c r="H849" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="850" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="850" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A850" t="s">
-        <v>3499</v>
+        <v>3492</v>
       </c>
       <c r="B850" t="s">
-        <v>3284</v>
+        <v>3277</v>
       </c>
       <c r="C850" t="s">
-        <v>3285</v>
+        <v>3278</v>
       </c>
       <c r="D850">
         <v>36.069308999999997</v>
@@ -32866,21 +33548,24 @@
         <v>138.05003400000001</v>
       </c>
       <c r="F850" t="s">
-        <v>3283</v>
+        <v>3530</v>
       </c>
       <c r="G850" t="s">
-        <v>3286</v>
-      </c>
-    </row>
-    <row r="851" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+        <v>3276</v>
+      </c>
+      <c r="H850" t="s">
+        <v>3279</v>
+      </c>
+    </row>
+    <row r="851" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A851" t="s">
-        <v>3500</v>
+        <v>3493</v>
       </c>
       <c r="B851" t="s">
-        <v>3287</v>
+        <v>3280</v>
       </c>
       <c r="C851" t="s">
-        <v>3288</v>
+        <v>3281</v>
       </c>
       <c r="D851">
         <v>35.514476999999999</v>
@@ -32889,21 +33574,24 @@
         <v>137.821899</v>
       </c>
       <c r="F851" t="s">
-        <v>3289</v>
+        <v>1006</v>
       </c>
       <c r="G851" t="s">
+        <v>3282</v>
+      </c>
+      <c r="H851" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="852" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="852" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A852" t="s">
-        <v>3500</v>
+        <v>3493</v>
       </c>
       <c r="B852" t="s">
-        <v>3290</v>
+        <v>3283</v>
       </c>
       <c r="C852" t="s">
-        <v>3288</v>
+        <v>3281</v>
       </c>
       <c r="D852">
         <v>35.514476999999999</v>
@@ -32912,21 +33600,24 @@
         <v>137.821899</v>
       </c>
       <c r="F852" t="s">
-        <v>3289</v>
+        <v>3531</v>
       </c>
       <c r="G852" t="s">
+        <v>3282</v>
+      </c>
+      <c r="H852" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="853" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="853" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A853" t="s">
-        <v>3466</v>
+        <v>3459</v>
       </c>
       <c r="B853" t="s">
-        <v>3291</v>
+        <v>3284</v>
       </c>
       <c r="C853" t="s">
-        <v>3292</v>
+        <v>3285</v>
       </c>
       <c r="D853">
         <v>35.326019000000002</v>
@@ -32935,21 +33626,24 @@
         <v>137.96987899999999</v>
       </c>
       <c r="F853" t="s">
-        <v>3289</v>
+        <v>3532</v>
       </c>
       <c r="G853" t="s">
-        <v>3293</v>
-      </c>
-    </row>
-    <row r="854" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+        <v>3282</v>
+      </c>
+      <c r="H853" t="s">
+        <v>3286</v>
+      </c>
+    </row>
+    <row r="854" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A854" t="s">
-        <v>3467</v>
+        <v>3460</v>
       </c>
       <c r="B854" t="s">
-        <v>3294</v>
+        <v>3287</v>
       </c>
       <c r="C854" t="s">
-        <v>3295</v>
+        <v>3288</v>
       </c>
       <c r="D854">
         <v>36.046714999999999</v>
@@ -32958,21 +33652,24 @@
         <v>138.11679100000001</v>
       </c>
       <c r="F854" t="s">
-        <v>3296</v>
+        <v>3533</v>
       </c>
       <c r="G854" t="s">
+        <v>3289</v>
+      </c>
+      <c r="H854" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="855" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="855" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A855" t="s">
-        <v>3468</v>
+        <v>3461</v>
       </c>
       <c r="B855" t="s">
-        <v>3297</v>
+        <v>3290</v>
       </c>
       <c r="C855" t="s">
-        <v>3298</v>
+        <v>3291</v>
       </c>
       <c r="D855">
         <v>36.327145000000002</v>
@@ -32981,21 +33678,24 @@
         <v>138.4254</v>
       </c>
       <c r="F855" t="s">
-        <v>3299</v>
+        <v>1006</v>
       </c>
       <c r="G855" t="s">
+        <v>3292</v>
+      </c>
+      <c r="H855" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="856" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="856" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A856" t="s">
-        <v>3501</v>
+        <v>3494</v>
       </c>
       <c r="B856" t="s">
-        <v>3300</v>
+        <v>3293</v>
       </c>
       <c r="C856" t="s">
-        <v>3298</v>
+        <v>3291</v>
       </c>
       <c r="D856">
         <v>36.327145000000002</v>
@@ -33004,21 +33704,24 @@
         <v>138.4254</v>
       </c>
       <c r="F856" t="s">
-        <v>3299</v>
+        <v>3531</v>
       </c>
       <c r="G856" t="s">
+        <v>3292</v>
+      </c>
+      <c r="H856" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="857" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="857" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A857" t="s">
-        <v>3469</v>
+        <v>3462</v>
       </c>
       <c r="B857" t="s">
-        <v>3301</v>
+        <v>3294</v>
       </c>
       <c r="C857" t="s">
-        <v>3302</v>
+        <v>3295</v>
       </c>
       <c r="D857">
         <v>36.327145000000002</v>
@@ -33027,21 +33730,24 @@
         <v>138.4254</v>
       </c>
       <c r="F857" t="s">
-        <v>3299</v>
+        <v>3534</v>
       </c>
       <c r="G857" t="s">
-        <v>3293</v>
-      </c>
-    </row>
-    <row r="858" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+        <v>3292</v>
+      </c>
+      <c r="H857" t="s">
+        <v>3286</v>
+      </c>
+    </row>
+    <row r="858" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A858" t="s">
-        <v>3470</v>
+        <v>3463</v>
       </c>
       <c r="B858" t="s">
-        <v>3303</v>
+        <v>3296</v>
       </c>
       <c r="C858" t="s">
-        <v>3304</v>
+        <v>3297</v>
       </c>
       <c r="D858">
         <v>36.326756000000003</v>
@@ -33050,21 +33756,24 @@
         <v>138.421707</v>
       </c>
       <c r="F858" t="s">
+        <v>3535</v>
+      </c>
+      <c r="G858" t="s">
+        <v>3292</v>
+      </c>
+      <c r="H858" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="859" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A859" t="s">
+        <v>3464</v>
+      </c>
+      <c r="B859" t="s">
+        <v>3298</v>
+      </c>
+      <c r="C859" t="s">
         <v>3299</v>
-      </c>
-      <c r="G858" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="859" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A859" t="s">
-        <v>3471</v>
-      </c>
-      <c r="B859" t="s">
-        <v>3305</v>
-      </c>
-      <c r="C859" t="s">
-        <v>3306</v>
       </c>
       <c r="D859">
         <v>35.882446000000002</v>
@@ -33073,21 +33782,24 @@
         <v>137.904526</v>
       </c>
       <c r="F859" t="s">
-        <v>3307</v>
+        <v>3536</v>
       </c>
       <c r="G859" t="s">
+        <v>3300</v>
+      </c>
+      <c r="H859" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="860" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="860" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A860" t="s">
-        <v>3472</v>
+        <v>3465</v>
       </c>
       <c r="B860" t="s">
-        <v>3308</v>
+        <v>3301</v>
       </c>
       <c r="C860" t="s">
-        <v>3309</v>
+        <v>3302</v>
       </c>
       <c r="D860">
         <v>35.824646000000001</v>
@@ -33096,21 +33808,24 @@
         <v>138.067566</v>
       </c>
       <c r="F860" t="s">
-        <v>3307</v>
+        <v>3537</v>
       </c>
       <c r="G860" t="s">
+        <v>3300</v>
+      </c>
+      <c r="H860" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="861" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="861" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A861" t="s">
-        <v>3473</v>
+        <v>3466</v>
       </c>
       <c r="B861" t="s">
-        <v>3310</v>
+        <v>3303</v>
       </c>
       <c r="C861" t="s">
-        <v>3311</v>
+        <v>3304</v>
       </c>
       <c r="D861">
         <v>35.813918999999999</v>
@@ -33119,21 +33834,24 @@
         <v>138.104309</v>
       </c>
       <c r="F861" t="s">
-        <v>3307</v>
+        <v>3538</v>
       </c>
       <c r="G861" t="s">
+        <v>3300</v>
+      </c>
+      <c r="H861" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="862" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="862" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A862" t="s">
-        <v>3474</v>
+        <v>3467</v>
       </c>
       <c r="B862" t="s">
-        <v>3312</v>
+        <v>3305</v>
       </c>
       <c r="C862" t="s">
-        <v>3313</v>
+        <v>3306</v>
       </c>
       <c r="D862">
         <v>35.736355000000003</v>
@@ -33142,21 +33860,24 @@
         <v>137.93679800000001</v>
       </c>
       <c r="F862" t="s">
-        <v>3314</v>
+        <v>3539</v>
       </c>
       <c r="G862" t="s">
+        <v>3307</v>
+      </c>
+      <c r="H862" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="863" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="863" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A863" t="s">
-        <v>3475</v>
+        <v>3468</v>
       </c>
       <c r="B863" t="s">
-        <v>3315</v>
+        <v>3308</v>
       </c>
       <c r="C863" t="s">
-        <v>3316</v>
+        <v>3309</v>
       </c>
       <c r="D863">
         <v>36.741664999999998</v>
@@ -33165,21 +33886,24 @@
         <v>138.36982699999999</v>
       </c>
       <c r="F863" t="s">
-        <v>3317</v>
+        <v>1253</v>
       </c>
       <c r="G863" t="s">
+        <v>3310</v>
+      </c>
+      <c r="H863" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="864" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="864" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A864" t="s">
-        <v>3502</v>
+        <v>3495</v>
       </c>
       <c r="B864" t="s">
-        <v>3318</v>
+        <v>3311</v>
       </c>
       <c r="C864" t="s">
-        <v>3316</v>
+        <v>3309</v>
       </c>
       <c r="D864">
         <v>36.741664999999998</v>
@@ -33188,21 +33912,24 @@
         <v>138.36982699999999</v>
       </c>
       <c r="F864" t="s">
-        <v>3317</v>
+        <v>3540</v>
       </c>
       <c r="G864" t="s">
+        <v>3310</v>
+      </c>
+      <c r="H864" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="865" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="865" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A865" t="s">
-        <v>3476</v>
+        <v>3469</v>
       </c>
       <c r="B865" t="s">
-        <v>3319</v>
+        <v>3312</v>
       </c>
       <c r="C865" t="s">
-        <v>3320</v>
+        <v>3313</v>
       </c>
       <c r="D865">
         <v>36.524631999999997</v>
@@ -33211,21 +33938,24 @@
         <v>137.870621</v>
       </c>
       <c r="F865" t="s">
-        <v>3321</v>
+        <v>3541</v>
       </c>
       <c r="G865" t="s">
+        <v>3314</v>
+      </c>
+      <c r="H865" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="866" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="866" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A866" t="s">
-        <v>3477</v>
+        <v>3470</v>
       </c>
       <c r="B866" t="s">
-        <v>3322</v>
+        <v>3315</v>
       </c>
       <c r="C866" t="s">
-        <v>3323</v>
+        <v>3316</v>
       </c>
       <c r="D866">
         <v>36.855927000000001</v>
@@ -33234,21 +33964,24 @@
         <v>138.36248800000001</v>
       </c>
       <c r="F866" t="s">
-        <v>3324</v>
+        <v>3542</v>
       </c>
       <c r="G866" t="s">
+        <v>3317</v>
+      </c>
+      <c r="H866" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="867" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="867" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A867" t="s">
-        <v>3478</v>
+        <v>3471</v>
       </c>
       <c r="B867" t="s">
-        <v>3325</v>
+        <v>3318</v>
       </c>
       <c r="C867" t="s">
-        <v>3326</v>
+        <v>3319</v>
       </c>
       <c r="D867">
         <v>35.994553000000003</v>
@@ -33257,21 +33990,24 @@
         <v>138.151962</v>
       </c>
       <c r="F867" t="s">
-        <v>3327</v>
+        <v>3543</v>
       </c>
       <c r="G867" t="s">
+        <v>3320</v>
+      </c>
+      <c r="H867" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="868" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="868" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A868" t="s">
-        <v>3479</v>
+        <v>3472</v>
       </c>
       <c r="B868" t="s">
-        <v>3328</v>
+        <v>3321</v>
       </c>
       <c r="C868" t="s">
-        <v>3329</v>
+        <v>3322</v>
       </c>
       <c r="D868">
         <v>36.277763</v>
@@ -33280,21 +34016,24 @@
         <v>138.464539</v>
       </c>
       <c r="F868" t="s">
-        <v>3330</v>
+        <v>3544</v>
       </c>
       <c r="G868" t="s">
+        <v>3323</v>
+      </c>
+      <c r="H868" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="869" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="869" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A869" t="s">
-        <v>3480</v>
+        <v>3473</v>
       </c>
       <c r="B869" t="s">
-        <v>3331</v>
+        <v>3324</v>
       </c>
       <c r="C869" t="s">
-        <v>3332</v>
+        <v>3325</v>
       </c>
       <c r="D869">
         <v>36.25761</v>
@@ -33303,21 +34042,24 @@
         <v>138.40432699999999</v>
       </c>
       <c r="F869" t="s">
-        <v>3330</v>
+        <v>3545</v>
       </c>
       <c r="G869" t="s">
+        <v>3323</v>
+      </c>
+      <c r="H869" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="870" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="870" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A870" t="s">
-        <v>3481</v>
+        <v>3474</v>
       </c>
       <c r="B870" t="s">
-        <v>3333</v>
+        <v>3326</v>
       </c>
       <c r="C870" t="s">
-        <v>3334</v>
+        <v>3327</v>
       </c>
       <c r="D870">
         <v>36.241836999999997</v>
@@ -33326,21 +34068,24 @@
         <v>138.436295</v>
       </c>
       <c r="F870" t="s">
-        <v>3330</v>
+        <v>161</v>
       </c>
       <c r="G870" t="s">
+        <v>3323</v>
+      </c>
+      <c r="H870" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="871" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="871" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A871" t="s">
-        <v>3482</v>
+        <v>3475</v>
       </c>
       <c r="B871" t="s">
-        <v>3335</v>
+        <v>3328</v>
       </c>
       <c r="C871" t="s">
-        <v>3336</v>
+        <v>3329</v>
       </c>
       <c r="D871">
         <v>36.273308</v>
@@ -33349,21 +34094,24 @@
         <v>138.47868299999999</v>
       </c>
       <c r="F871" t="s">
+        <v>3546</v>
+      </c>
+      <c r="G871" t="s">
+        <v>3323</v>
+      </c>
+      <c r="H871" t="s">
         <v>3330</v>
       </c>
-      <c r="G871" t="s">
-        <v>3337</v>
-      </c>
-    </row>
-    <row r="872" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="872" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A872" t="s">
-        <v>3483</v>
+        <v>3476</v>
       </c>
       <c r="B872" t="s">
-        <v>3338</v>
+        <v>3331</v>
       </c>
       <c r="C872" t="s">
-        <v>3339</v>
+        <v>3332</v>
       </c>
       <c r="D872">
         <v>36.478619000000002</v>
@@ -33372,21 +34120,24 @@
         <v>138.144485</v>
       </c>
       <c r="F872" t="s">
-        <v>3340</v>
+        <v>3547</v>
       </c>
       <c r="G872" t="s">
+        <v>3333</v>
+      </c>
+      <c r="H872" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="873" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="873" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A873" t="s">
-        <v>3484</v>
+        <v>3477</v>
       </c>
       <c r="B873" t="s">
-        <v>3341</v>
+        <v>3334</v>
       </c>
       <c r="C873" t="s">
-        <v>3342</v>
+        <v>3335</v>
       </c>
       <c r="D873">
         <v>36.530093999999998</v>
@@ -33395,21 +34146,24 @@
         <v>138.117142</v>
       </c>
       <c r="F873" t="s">
-        <v>3340</v>
+        <v>3548</v>
       </c>
       <c r="G873" t="s">
+        <v>3333</v>
+      </c>
+      <c r="H873" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="874" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="874" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A874" t="s">
-        <v>3485</v>
+        <v>3478</v>
       </c>
       <c r="B874" t="s">
-        <v>3343</v>
+        <v>3336</v>
       </c>
       <c r="C874" t="s">
-        <v>3344</v>
+        <v>3337</v>
       </c>
       <c r="D874">
         <v>36.486725</v>
@@ -33418,21 +34172,24 @@
         <v>138.14802599999999</v>
       </c>
       <c r="F874" t="s">
-        <v>3340</v>
+        <v>3549</v>
       </c>
       <c r="G874" t="s">
+        <v>3333</v>
+      </c>
+      <c r="H874" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="875" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="875" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A875" t="s">
-        <v>3486</v>
+        <v>3479</v>
       </c>
       <c r="B875" t="s">
-        <v>3345</v>
+        <v>3338</v>
       </c>
       <c r="C875" t="s">
-        <v>3346</v>
+        <v>3339</v>
       </c>
       <c r="D875">
         <v>36.478214000000001</v>
@@ -33441,21 +34198,24 @@
         <v>138.14567600000001</v>
       </c>
       <c r="F875" t="s">
+        <v>3550</v>
+      </c>
+      <c r="G875" t="s">
+        <v>3333</v>
+      </c>
+      <c r="H875" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="876" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A876" t="s">
+        <v>3480</v>
+      </c>
+      <c r="B876" t="s">
         <v>3340</v>
       </c>
-      <c r="G875" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="876" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A876" t="s">
-        <v>3487</v>
-      </c>
-      <c r="B876" t="s">
-        <v>3347</v>
-      </c>
       <c r="C876" t="s">
-        <v>3348</v>
+        <v>3341</v>
       </c>
       <c r="D876">
         <v>36.355643999999998</v>
@@ -33464,21 +34224,24 @@
         <v>138.37425200000001</v>
       </c>
       <c r="F876" t="s">
-        <v>3349</v>
+        <v>3551</v>
       </c>
       <c r="G876" t="s">
+        <v>3342</v>
+      </c>
+      <c r="H876" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="877" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="877" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A877" t="s">
-        <v>3488</v>
+        <v>3481</v>
       </c>
       <c r="B877" t="s">
-        <v>3350</v>
+        <v>3343</v>
       </c>
       <c r="C877" t="s">
-        <v>3351</v>
+        <v>3344</v>
       </c>
       <c r="D877">
         <v>36.288673000000003</v>
@@ -33487,21 +34250,24 @@
         <v>137.90901199999999</v>
       </c>
       <c r="F877" t="s">
-        <v>3352</v>
+        <v>1006</v>
       </c>
       <c r="G877" t="s">
+        <v>3345</v>
+      </c>
+      <c r="H877" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="878" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="878" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A878" t="s">
-        <v>3503</v>
+        <v>3496</v>
       </c>
       <c r="B878" t="s">
-        <v>3353</v>
+        <v>3346</v>
       </c>
       <c r="C878" t="s">
-        <v>3351</v>
+        <v>3344</v>
       </c>
       <c r="D878">
         <v>36.288673000000003</v>
@@ -33510,21 +34276,24 @@
         <v>137.90901199999999</v>
       </c>
       <c r="F878" t="s">
-        <v>3352</v>
+        <v>1178</v>
       </c>
       <c r="G878" t="s">
+        <v>3345</v>
+      </c>
+      <c r="H878" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="879" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="879" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A879" t="s">
-        <v>3489</v>
+        <v>3482</v>
       </c>
       <c r="B879" t="s">
-        <v>3354</v>
+        <v>3347</v>
       </c>
       <c r="C879" t="s">
-        <v>3355</v>
+        <v>3348</v>
       </c>
       <c r="D879">
         <v>36.342827</v>
@@ -33533,21 +34302,24 @@
         <v>138.63467399999999</v>
       </c>
       <c r="F879" t="s">
-        <v>3356</v>
+        <v>3552</v>
       </c>
       <c r="G879" t="s">
+        <v>3349</v>
+      </c>
+      <c r="H879" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="880" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="880" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A880" t="s">
-        <v>3504</v>
+        <v>3497</v>
       </c>
       <c r="B880" t="s">
-        <v>3357</v>
+        <v>3350</v>
       </c>
       <c r="C880" t="s">
-        <v>3358</v>
+        <v>3351</v>
       </c>
       <c r="D880">
         <v>36.348480000000002</v>
@@ -33556,21 +34328,24 @@
         <v>138.59617600000001</v>
       </c>
       <c r="F880" t="s">
-        <v>3356</v>
+        <v>3553</v>
       </c>
       <c r="G880" t="s">
+        <v>3349</v>
+      </c>
+      <c r="H880" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="881" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="881" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A881" t="s">
-        <v>3505</v>
+        <v>3498</v>
       </c>
       <c r="B881" t="s">
-        <v>3359</v>
+        <v>3352</v>
       </c>
       <c r="C881" t="s">
-        <v>3360</v>
+        <v>3353</v>
       </c>
       <c r="D881">
         <v>36.341034000000001</v>
@@ -33579,21 +34354,24 @@
         <v>138.54686000000001</v>
       </c>
       <c r="F881" t="s">
-        <v>3356</v>
+        <v>3554</v>
       </c>
       <c r="G881" t="s">
+        <v>3349</v>
+      </c>
+      <c r="H881" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="882" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="882" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A882" t="s">
-        <v>3505</v>
+        <v>3498</v>
       </c>
       <c r="B882" t="s">
-        <v>3361</v>
+        <v>3354</v>
       </c>
       <c r="C882" t="s">
-        <v>3362</v>
+        <v>3355</v>
       </c>
       <c r="D882">
         <v>36.348129</v>
@@ -33602,21 +34380,24 @@
         <v>138.59079</v>
       </c>
       <c r="F882" t="s">
+        <v>3555</v>
+      </c>
+      <c r="G882" t="s">
+        <v>3349</v>
+      </c>
+      <c r="H882" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="883" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A883" t="s">
+        <v>3483</v>
+      </c>
+      <c r="B883" t="s">
         <v>3356</v>
       </c>
-      <c r="G882" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="883" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A883" t="s">
-        <v>3490</v>
-      </c>
-      <c r="B883" t="s">
-        <v>3363</v>
-      </c>
       <c r="C883" t="s">
-        <v>3364</v>
+        <v>3357</v>
       </c>
       <c r="D883">
         <v>36.069519</v>
@@ -33625,21 +34406,24 @@
         <v>138.080231</v>
       </c>
       <c r="F883" t="s">
-        <v>3365</v>
+        <v>3556</v>
       </c>
       <c r="G883" t="s">
+        <v>3358</v>
+      </c>
+      <c r="H883" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="884" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="884" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A884" t="s">
-        <v>3491</v>
+        <v>3484</v>
       </c>
       <c r="B884" t="s">
-        <v>3366</v>
+        <v>3359</v>
       </c>
       <c r="C884" t="s">
-        <v>3367</v>
+        <v>3360</v>
       </c>
       <c r="D884">
         <v>36.069519</v>
@@ -33648,21 +34432,24 @@
         <v>138.080231</v>
       </c>
       <c r="F884" t="s">
-        <v>3365</v>
+        <v>3557</v>
       </c>
       <c r="G884" t="s">
+        <v>3358</v>
+      </c>
+      <c r="H884" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="885" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="885" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A885" t="s">
-        <v>3492</v>
+        <v>3485</v>
       </c>
       <c r="B885" t="s">
-        <v>3368</v>
+        <v>3361</v>
       </c>
       <c r="C885" t="s">
-        <v>3369</v>
+        <v>3362</v>
       </c>
       <c r="D885">
         <v>36.069519</v>
@@ -33671,21 +34458,24 @@
         <v>138.080231</v>
       </c>
       <c r="F885" t="s">
-        <v>3365</v>
+        <v>3558</v>
       </c>
       <c r="G885" t="s">
+        <v>3358</v>
+      </c>
+      <c r="H885" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="886" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="886" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A886" t="s">
-        <v>3493</v>
+        <v>3486</v>
       </c>
       <c r="B886" t="s">
-        <v>3370</v>
+        <v>3363</v>
       </c>
       <c r="C886" t="s">
-        <v>3371</v>
+        <v>3364</v>
       </c>
       <c r="D886">
         <v>35.872897999999999</v>
@@ -33694,21 +34484,24 @@
         <v>137.97508199999999</v>
       </c>
       <c r="F886" t="s">
-        <v>3372</v>
+        <v>3559</v>
       </c>
       <c r="G886" t="s">
+        <v>3365</v>
+      </c>
+      <c r="H886" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="887" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="887" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A887" t="s">
-        <v>3494</v>
+        <v>3487</v>
       </c>
       <c r="B887" t="s">
-        <v>3373</v>
+        <v>3366</v>
       </c>
       <c r="C887" t="s">
-        <v>3374</v>
+        <v>3367</v>
       </c>
       <c r="D887">
         <v>35.552311000000003</v>
@@ -33717,21 +34510,24 @@
         <v>137.877655</v>
       </c>
       <c r="F887" t="s">
-        <v>3375</v>
+        <v>1408</v>
       </c>
       <c r="G887" t="s">
+        <v>3368</v>
+      </c>
+      <c r="H887" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="888" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="888" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A888" t="s">
-        <v>3506</v>
+        <v>3499</v>
       </c>
       <c r="B888" t="s">
-        <v>3376</v>
+        <v>3369</v>
       </c>
       <c r="C888" t="s">
-        <v>3374</v>
+        <v>3367</v>
       </c>
       <c r="D888">
         <v>35.552311000000003</v>
@@ -33740,21 +34536,24 @@
         <v>137.877655</v>
       </c>
       <c r="F888" t="s">
-        <v>3375</v>
+        <v>3560</v>
       </c>
       <c r="G888" t="s">
+        <v>3368</v>
+      </c>
+      <c r="H888" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="889" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="889" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A889" t="s">
-        <v>3507</v>
+        <v>3500</v>
       </c>
       <c r="B889" t="s">
-        <v>3377</v>
+        <v>3370</v>
       </c>
       <c r="C889" t="s">
-        <v>3374</v>
+        <v>3367</v>
       </c>
       <c r="D889">
         <v>35.552311000000003</v>
@@ -33763,21 +34562,24 @@
         <v>137.877655</v>
       </c>
       <c r="F889" t="s">
-        <v>3375</v>
+        <v>1408</v>
       </c>
       <c r="G889" t="s">
+        <v>3368</v>
+      </c>
+      <c r="H889" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="890" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="890" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A890" t="s">
-        <v>3507</v>
+        <v>3500</v>
       </c>
       <c r="B890" t="s">
-        <v>3378</v>
+        <v>3371</v>
       </c>
       <c r="C890" t="s">
-        <v>3374</v>
+        <v>3367</v>
       </c>
       <c r="D890">
         <v>35.552311000000003</v>
@@ -33786,21 +34588,24 @@
         <v>137.877655</v>
       </c>
       <c r="F890" t="s">
-        <v>3375</v>
+        <v>3561</v>
       </c>
       <c r="G890" t="s">
-        <v>3379</v>
-      </c>
-    </row>
-    <row r="891" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+        <v>3368</v>
+      </c>
+      <c r="H890" t="s">
+        <v>3372</v>
+      </c>
+    </row>
+    <row r="891" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A891" t="s">
-        <v>3495</v>
+        <v>3488</v>
       </c>
       <c r="B891" t="s">
-        <v>3380</v>
+        <v>3373</v>
       </c>
       <c r="C891" t="s">
-        <v>3381</v>
+        <v>3374</v>
       </c>
       <c r="D891">
         <v>35.565105000000003</v>
@@ -33809,21 +34614,24 @@
         <v>137.60395800000001</v>
       </c>
       <c r="F891" t="s">
-        <v>3382</v>
+        <v>535</v>
       </c>
       <c r="G891" t="s">
+        <v>3375</v>
+      </c>
+      <c r="H891" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="892" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="892" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A892" t="s">
-        <v>3496</v>
+        <v>3489</v>
       </c>
       <c r="B892" t="s">
-        <v>3383</v>
+        <v>3376</v>
       </c>
       <c r="C892" t="s">
-        <v>3384</v>
+        <v>3377</v>
       </c>
       <c r="D892">
         <v>35.696078999999997</v>
@@ -33832,21 +34640,24 @@
         <v>137.766953</v>
       </c>
       <c r="F892" t="s">
-        <v>3385</v>
+        <v>770</v>
       </c>
       <c r="G892" t="s">
+        <v>3378</v>
+      </c>
+      <c r="H892" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="893" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="893" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A893" t="s">
-        <v>3497</v>
+        <v>3490</v>
       </c>
       <c r="B893" t="s">
-        <v>3386</v>
+        <v>3379</v>
       </c>
       <c r="C893" t="s">
-        <v>3387</v>
+        <v>3380</v>
       </c>
       <c r="D893">
         <v>36.102406000000002</v>
@@ -33855,21 +34666,24 @@
         <v>137.803391</v>
       </c>
       <c r="F893" t="s">
-        <v>3388</v>
+        <v>1006</v>
       </c>
       <c r="G893" t="s">
+        <v>3381</v>
+      </c>
+      <c r="H893" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="894" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="894" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A894" t="s">
-        <v>3508</v>
+        <v>3501</v>
       </c>
       <c r="B894" t="s">
-        <v>3389</v>
+        <v>3382</v>
       </c>
       <c r="C894" t="s">
-        <v>3387</v>
+        <v>3380</v>
       </c>
       <c r="D894">
         <v>36.102406000000002</v>
@@ -33878,21 +34692,24 @@
         <v>137.803391</v>
       </c>
       <c r="F894" t="s">
-        <v>3388</v>
+        <v>3562</v>
       </c>
       <c r="G894" t="s">
+        <v>3381</v>
+      </c>
+      <c r="H894" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="895" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="895" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A895" t="s">
-        <v>3509</v>
+        <v>3502</v>
       </c>
       <c r="B895" t="s">
-        <v>3390</v>
+        <v>3383</v>
       </c>
       <c r="C895" t="s">
-        <v>3391</v>
+        <v>3384</v>
       </c>
       <c r="D895">
         <v>36.403267</v>
@@ -33901,21 +34718,24 @@
         <v>137.99475100000001</v>
       </c>
       <c r="F895" t="s">
-        <v>3392</v>
+        <v>3563</v>
       </c>
       <c r="G895" t="s">
+        <v>3385</v>
+      </c>
+      <c r="H895" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="896" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="896" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A896" t="s">
-        <v>3509</v>
+        <v>3502</v>
       </c>
       <c r="B896" t="s">
-        <v>3393</v>
+        <v>3386</v>
       </c>
       <c r="C896" t="s">
-        <v>3394</v>
+        <v>3387</v>
       </c>
       <c r="D896">
         <v>36.403267</v>
@@ -33924,21 +34744,24 @@
         <v>137.99475100000001</v>
       </c>
       <c r="F896" t="s">
-        <v>3392</v>
+        <v>3564</v>
       </c>
       <c r="G896" t="s">
+        <v>3385</v>
+      </c>
+      <c r="H896" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="897" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="897" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A897" t="s">
-        <v>3510</v>
+        <v>3503</v>
       </c>
       <c r="B897" t="s">
-        <v>3395</v>
+        <v>3388</v>
       </c>
       <c r="C897" t="s">
-        <v>3396</v>
+        <v>3389</v>
       </c>
       <c r="D897">
         <v>36.697670000000002</v>
@@ -33947,21 +34770,24 @@
         <v>138.313568</v>
       </c>
       <c r="F897" t="s">
-        <v>3397</v>
+        <v>3509</v>
       </c>
       <c r="G897" t="s">
+        <v>3390</v>
+      </c>
+      <c r="H897" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="898" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="898" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A898" t="s">
-        <v>3510</v>
+        <v>3503</v>
       </c>
       <c r="B898" t="s">
-        <v>3398</v>
+        <v>3391</v>
       </c>
       <c r="C898" t="s">
-        <v>3396</v>
+        <v>3389</v>
       </c>
       <c r="D898">
         <v>36.697670000000002</v>
@@ -33970,21 +34796,24 @@
         <v>138.313568</v>
       </c>
       <c r="F898" t="s">
-        <v>3397</v>
+        <v>3565</v>
       </c>
       <c r="G898" t="s">
+        <v>3390</v>
+      </c>
+      <c r="H898" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="899" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="899" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A899" t="s">
-        <v>3511</v>
+        <v>3504</v>
       </c>
       <c r="B899" t="s">
-        <v>3399</v>
+        <v>3392</v>
       </c>
       <c r="C899" t="s">
-        <v>3396</v>
+        <v>3389</v>
       </c>
       <c r="D899">
         <v>36.697670000000002</v>
@@ -33993,21 +34822,24 @@
         <v>138.313568</v>
       </c>
       <c r="F899" t="s">
-        <v>3397</v>
+        <v>3509</v>
       </c>
       <c r="G899" t="s">
+        <v>3390</v>
+      </c>
+      <c r="H899" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="900" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="900" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A900" t="s">
-        <v>3512</v>
+        <v>3505</v>
       </c>
       <c r="B900" t="s">
-        <v>3400</v>
+        <v>3393</v>
       </c>
       <c r="C900" t="s">
-        <v>3396</v>
+        <v>3389</v>
       </c>
       <c r="D900">
         <v>36.697670000000002</v>
@@ -34016,14 +34848,27 @@
         <v>138.313568</v>
       </c>
       <c r="F900" t="s">
-        <v>3397</v>
+        <v>3566</v>
       </c>
       <c r="G900" t="s">
+        <v>3390</v>
+      </c>
+      <c r="H900" t="s">
         <v>72</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="G780" r:id="rId1" xr:uid="{6E95B594-FEAF-4588-BD02-E381E79A50DD}"/>
+    <hyperlink ref="G792" r:id="rId2" xr:uid="{BCD151FC-A40A-4CBF-A9A0-4A640977AE11}"/>
+    <hyperlink ref="G794" r:id="rId3" xr:uid="{5F60447F-42F9-4101-B286-CC9FB95A725E}"/>
+    <hyperlink ref="G828" r:id="rId4" xr:uid="{DB1ED563-AE55-40CB-B80F-55FB209EE855}"/>
+    <hyperlink ref="G769" r:id="rId5" xr:uid="{E7378500-56B4-4BCA-9320-BC3D4CD0E59C}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId6"/>
+  </tableParts>
 </worksheet>
 </file>